--- a/upload/dados_gerais_emendas.xlsx
+++ b/upload/dados_gerais_emendas.xlsx
@@ -1,25 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD498E18-3193-4CA0-89F3-C7C3208E1681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19755" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dados_emendas_gerais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3422" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="793">
   <si>
     <t>FEDERAL</t>
   </si>
@@ -2386,13 +2400,40 @@
   </si>
   <si>
     <t>Aquisição de equipamentos para Universidade do Estado de Minas Gerais - nas Unidades Acadêmicas de Campanha, Ibirité, Ituiutaba, Poços de Caldas e Ubá.</t>
+  </si>
+  <si>
+    <t>957138/2024</t>
+  </si>
+  <si>
+    <t>Estruturação da EMATER-MG</t>
+  </si>
+  <si>
+    <t>ZE SILVA</t>
+  </si>
+  <si>
+    <t>956843/2024</t>
+  </si>
+  <si>
+    <t>Aquisição de Kits Feira Livre</t>
+  </si>
+  <si>
+    <t>961915/2024</t>
+  </si>
+  <si>
+    <t>Adquirir sementes de qualidade de Milho, feijão e Sorgo para distribuir aos Agricultores familiares do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>988741/2025</t>
+  </si>
+  <si>
+    <t>Apoio à Realização dos Jogos do Interior de Minas Geriais - JIMI 2026, no Estado de Minas Gerais.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2892,7 +2933,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2921,7 +2962,6 @@
     <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2957,11 +2997,11 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="42"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -3301,11 +3341,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z813"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.25">
+    <row r="1" spans="1:26" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>754</v>
       </c>
@@ -3361,7 +3401,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -3393,7 +3433,7 @@
         <v>5664000</v>
       </c>
       <c r="K2" s="8">
-        <f t="shared" ref="K2:K417" si="0">IF(MATCH(G2,G$2:G2,0)=ROW(G2)-ROW(G$2)+1,J2,0)</f>
+        <f t="shared" ref="K2:K256" si="0">IF(MATCH(G2,G$2:G2,0)=ROW(G2)-ROW(G$2)+1,J2,0)</f>
         <v>5664000</v>
       </c>
       <c r="L2" s="9" t="s">
@@ -3418,7 +3458,7 @@
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
-    <row r="3" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -3456,7 +3496,7 @@
       <c r="L3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>35</v>
       </c>
       <c r="N3" s="7" t="s">
@@ -3475,7 +3515,7 @@
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
-    <row r="4" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -3513,7 +3553,7 @@
       <c r="L4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N4" s="7" t="s">
@@ -3532,7 +3572,7 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
     </row>
-    <row r="5" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>0</v>
       </c>
@@ -3589,7 +3629,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
-    <row r="6" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
@@ -3646,7 +3686,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
     </row>
-    <row r="7" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -3703,7 +3743,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
     </row>
-    <row r="8" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>0</v>
       </c>
@@ -3760,7 +3800,7 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
     </row>
-    <row r="9" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>0</v>
       </c>
@@ -3798,7 +3838,7 @@
       <c r="L9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N9" s="7" t="s">
@@ -3817,7 +3857,7 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
     </row>
-    <row r="10" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>0</v>
       </c>
@@ -3855,7 +3895,7 @@
       <c r="L10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N10" s="7" t="s">
@@ -3874,7 +3914,7 @@
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
     </row>
-    <row r="11" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>0</v>
       </c>
@@ -3912,7 +3952,7 @@
       <c r="L11" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N11" s="7" t="s">
@@ -3931,7 +3971,7 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
     </row>
-    <row r="12" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>0</v>
       </c>
@@ -3969,7 +4009,7 @@
       <c r="L12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N12" s="7" t="s">
@@ -3988,7 +4028,7 @@
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
     </row>
-    <row r="13" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>0</v>
       </c>
@@ -4026,7 +4066,7 @@
       <c r="L13" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N13" s="7" t="s">
@@ -4045,7 +4085,7 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
     </row>
-    <row r="14" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>0</v>
       </c>
@@ -4102,7 +4142,7 @@
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
     </row>
-    <row r="15" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -4159,7 +4199,7 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
     </row>
-    <row r="16" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4237,7 @@
       <c r="L16" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N16" s="7" t="s">
@@ -4216,7 +4256,7 @@
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
     </row>
-    <row r="17" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>0</v>
       </c>
@@ -4254,7 +4294,7 @@
       <c r="L17" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N17" s="7" t="s">
@@ -4273,7 +4313,7 @@
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
     </row>
-    <row r="18" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>0</v>
       </c>
@@ -4330,7 +4370,7 @@
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
     </row>
-    <row r="19" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>0</v>
       </c>
@@ -4387,7 +4427,7 @@
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
     </row>
-    <row r="20" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>0</v>
       </c>
@@ -4444,7 +4484,7 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
     </row>
-    <row r="21" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>0</v>
       </c>
@@ -4501,7 +4541,7 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
     </row>
-    <row r="22" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -4558,7 +4598,7 @@
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
     </row>
-    <row r="23" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>0</v>
       </c>
@@ -4615,7 +4655,7 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
     </row>
-    <row r="24" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>0</v>
       </c>
@@ -4672,7 +4712,7 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
     </row>
-    <row r="25" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>0</v>
       </c>
@@ -4710,7 +4750,7 @@
       <c r="L25" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N25" s="7" t="s">
@@ -4729,7 +4769,7 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
     </row>
-    <row r="26" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>0</v>
       </c>
@@ -4767,7 +4807,7 @@
       <c r="L26" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M26" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N26" s="7" t="s">
@@ -4786,7 +4826,7 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
     </row>
-    <row r="27" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>0</v>
       </c>
@@ -4824,7 +4864,7 @@
       <c r="L27" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N27" s="7" t="s">
@@ -4843,7 +4883,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>0</v>
       </c>
@@ -4881,7 +4921,7 @@
       <c r="L28" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M28" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N28" s="7" t="s">
@@ -4900,7 +4940,7 @@
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
     </row>
-    <row r="29" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>0</v>
       </c>
@@ -4938,7 +4978,7 @@
       <c r="L29" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M29" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N29" s="7" t="s">
@@ -4957,7 +4997,7 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
     </row>
-    <row r="30" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>0</v>
       </c>
@@ -4995,7 +5035,7 @@
       <c r="L30" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M30" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N30" s="7" t="s">
@@ -5014,7 +5054,7 @@
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
     </row>
-    <row r="31" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>0</v>
       </c>
@@ -5052,7 +5092,7 @@
       <c r="L31" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M31" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N31" s="7" t="s">
@@ -5071,7 +5111,7 @@
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
     </row>
-    <row r="32" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>0</v>
       </c>
@@ -5128,7 +5168,7 @@
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
     </row>
-    <row r="33" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>0</v>
       </c>
@@ -5185,7 +5225,7 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
     </row>
-    <row r="34" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>0</v>
       </c>
@@ -5242,7 +5282,7 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
     </row>
-    <row r="35" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>0</v>
       </c>
@@ -5299,7 +5339,7 @@
       <c r="Y35" s="7"/>
       <c r="Z35" s="7"/>
     </row>
-    <row r="36" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>0</v>
       </c>
@@ -5356,7 +5396,7 @@
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
     </row>
-    <row r="37" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>0</v>
       </c>
@@ -5413,7 +5453,7 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
     </row>
-    <row r="38" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>0</v>
       </c>
@@ -5470,7 +5510,7 @@
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
-    <row r="39" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>0</v>
       </c>
@@ -5527,7 +5567,7 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
-    <row r="40" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>0</v>
       </c>
@@ -5584,7 +5624,7 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
-    <row r="41" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>0</v>
       </c>
@@ -5641,7 +5681,7 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
-    <row r="42" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>0</v>
       </c>
@@ -5698,7 +5738,7 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
     </row>
-    <row r="43" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>0</v>
       </c>
@@ -5755,7 +5795,7 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
     </row>
-    <row r="44" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>0</v>
       </c>
@@ -5812,7 +5852,7 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
     </row>
-    <row r="45" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>0</v>
       </c>
@@ -5869,7 +5909,7 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
     </row>
-    <row r="46" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>0</v>
       </c>
@@ -5926,7 +5966,7 @@
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
     </row>
-    <row r="47" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>0</v>
       </c>
@@ -5983,7 +6023,7 @@
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
     </row>
-    <row r="48" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>0</v>
       </c>
@@ -6040,7 +6080,7 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
     </row>
-    <row r="49" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>0</v>
       </c>
@@ -6097,7 +6137,7 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
     </row>
-    <row r="50" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>0</v>
       </c>
@@ -6154,7 +6194,7 @@
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
     </row>
-    <row r="51" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
@@ -6211,7 +6251,7 @@
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
-    <row r="52" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>0</v>
       </c>
@@ -6268,7 +6308,7 @@
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
     </row>
-    <row r="53" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>0</v>
       </c>
@@ -6306,7 +6346,7 @@
       <c r="L53" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N53" s="7" t="s">
@@ -6325,7 +6365,7 @@
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
     </row>
-    <row r="54" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>0</v>
       </c>
@@ -6363,7 +6403,7 @@
       <c r="L54" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="M54" s="11" t="s">
+      <c r="M54" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N54" s="7" t="s">
@@ -6382,7 +6422,7 @@
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
     </row>
-    <row r="55" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>0</v>
       </c>
@@ -6420,7 +6460,7 @@
       <c r="L55" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M55" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N55" s="7" t="s">
@@ -6439,7 +6479,7 @@
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
-    <row r="56" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>0</v>
       </c>
@@ -6477,7 +6517,7 @@
       <c r="L56" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="M56" s="11" t="s">
+      <c r="M56" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N56" s="7" t="s">
@@ -6496,7 +6536,7 @@
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
     </row>
-    <row r="57" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>0</v>
       </c>
@@ -6534,7 +6574,7 @@
       <c r="L57" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="M57" s="11" t="s">
+      <c r="M57" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N57" s="7" t="s">
@@ -6553,7 +6593,7 @@
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
     </row>
-    <row r="58" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>0</v>
       </c>
@@ -6591,7 +6631,7 @@
       <c r="L58" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="M58" s="11" t="s">
+      <c r="M58" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N58" s="7" t="s">
@@ -6610,7 +6650,7 @@
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
     </row>
-    <row r="59" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>0</v>
       </c>
@@ -6648,7 +6688,7 @@
       <c r="L59" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="M59" s="11" t="s">
+      <c r="M59" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N59" s="7" t="s">
@@ -6667,7 +6707,7 @@
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
     </row>
-    <row r="60" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>0</v>
       </c>
@@ -6724,7 +6764,7 @@
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
     </row>
-    <row r="61" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>0</v>
       </c>
@@ -6762,7 +6802,7 @@
       <c r="L61" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="M61" s="11" t="s">
+      <c r="M61" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N61" s="7" t="s">
@@ -6781,7 +6821,7 @@
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
     </row>
-    <row r="62" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>0</v>
       </c>
@@ -6838,7 +6878,7 @@
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
     </row>
-    <row r="63" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>0</v>
       </c>
@@ -6895,7 +6935,7 @@
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
     </row>
-    <row r="64" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
@@ -6933,7 +6973,7 @@
       <c r="L64" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="M64" s="11" t="s">
+      <c r="M64" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N64" s="7" t="s">
@@ -6952,7 +6992,7 @@
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
     </row>
-    <row r="65" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>0</v>
       </c>
@@ -6990,7 +7030,7 @@
       <c r="L65" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="M65" s="11" t="s">
+      <c r="M65" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N65" s="7" t="s">
@@ -7009,7 +7049,7 @@
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
     </row>
-    <row r="66" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>0</v>
       </c>
@@ -7047,7 +7087,7 @@
       <c r="L66" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="M66" s="11" t="s">
+      <c r="M66" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N66" s="7" t="s">
@@ -7066,7 +7106,7 @@
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
     </row>
-    <row r="67" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>0</v>
       </c>
@@ -7104,7 +7144,7 @@
       <c r="L67" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="M67" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N67" s="7" t="s">
@@ -7123,7 +7163,7 @@
       <c r="Y67" s="7"/>
       <c r="Z67" s="7"/>
     </row>
-    <row r="68" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>0</v>
       </c>
@@ -7161,7 +7201,7 @@
       <c r="L68" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="M68" s="11" t="s">
+      <c r="M68" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N68" s="7" t="s">
@@ -7180,7 +7220,7 @@
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
     </row>
-    <row r="69" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>0</v>
       </c>
@@ -7237,7 +7277,7 @@
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
     </row>
-    <row r="70" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>0</v>
       </c>
@@ -7294,7 +7334,7 @@
       <c r="Y70" s="7"/>
       <c r="Z70" s="7"/>
     </row>
-    <row r="71" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>0</v>
       </c>
@@ -7351,7 +7391,7 @@
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
     </row>
-    <row r="72" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>0</v>
       </c>
@@ -7408,7 +7448,7 @@
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
     </row>
-    <row r="73" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>0</v>
       </c>
@@ -7465,7 +7505,7 @@
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
     </row>
-    <row r="74" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>0</v>
       </c>
@@ -7503,7 +7543,7 @@
       <c r="L74" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="M74" s="11" t="s">
+      <c r="M74" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N74" s="7" t="s">
@@ -7522,7 +7562,7 @@
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
     </row>
-    <row r="75" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>0</v>
       </c>
@@ -7560,7 +7600,7 @@
       <c r="L75" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="M75" s="11" t="s">
+      <c r="M75" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N75" s="7" t="s">
@@ -7579,7 +7619,7 @@
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
     </row>
-    <row r="76" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>0</v>
       </c>
@@ -7617,7 +7657,7 @@
       <c r="L76" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="M76" s="11" t="s">
+      <c r="M76" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N76" s="7" t="s">
@@ -7636,7 +7676,7 @@
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
     </row>
-    <row r="77" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>0</v>
       </c>
@@ -7693,7 +7733,7 @@
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
     </row>
-    <row r="78" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>0</v>
       </c>
@@ -7731,7 +7771,7 @@
       <c r="L78" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="M78" s="11" t="s">
+      <c r="M78" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N78" s="7" t="s">
@@ -7750,7 +7790,7 @@
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
     </row>
-    <row r="79" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>0</v>
       </c>
@@ -7807,7 +7847,7 @@
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
     </row>
-    <row r="80" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>0</v>
       </c>
@@ -7845,7 +7885,7 @@
       <c r="L80" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="M80" s="11" t="s">
+      <c r="M80" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N80" s="7" t="s">
@@ -7864,7 +7904,7 @@
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
     </row>
-    <row r="81" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>0</v>
       </c>
@@ -7902,7 +7942,7 @@
       <c r="L81" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="M81" s="11" t="s">
+      <c r="M81" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N81" s="7" t="s">
@@ -7921,7 +7961,7 @@
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
     </row>
-    <row r="82" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>0</v>
       </c>
@@ -7959,7 +7999,7 @@
       <c r="L82" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N82" s="7" t="s">
@@ -7978,7 +8018,7 @@
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
     </row>
-    <row r="83" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>0</v>
       </c>
@@ -8016,7 +8056,7 @@
       <c r="L83" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="M83" s="11" t="s">
+      <c r="M83" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N83" s="7" t="s">
@@ -8035,7 +8075,7 @@
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
     </row>
-    <row r="84" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>0</v>
       </c>
@@ -8092,7 +8132,7 @@
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
     </row>
-    <row r="85" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>0</v>
       </c>
@@ -8149,7 +8189,7 @@
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
     </row>
-    <row r="86" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>0</v>
       </c>
@@ -8187,7 +8227,7 @@
       <c r="L86" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="M86" s="11" t="s">
+      <c r="M86" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N86" s="7" t="s">
@@ -8206,7 +8246,7 @@
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
     </row>
-    <row r="87" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>0</v>
       </c>
@@ -8244,7 +8284,7 @@
       <c r="L87" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="M87" s="11" t="s">
+      <c r="M87" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N87" s="7" t="s">
@@ -8263,7 +8303,7 @@
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
     </row>
-    <row r="88" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>0</v>
       </c>
@@ -8320,7 +8360,7 @@
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
     </row>
-    <row r="89" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>0</v>
       </c>
@@ -8377,7 +8417,7 @@
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
     </row>
-    <row r="90" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>0</v>
       </c>
@@ -8434,7 +8474,7 @@
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
     </row>
-    <row r="91" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>0</v>
       </c>
@@ -8472,7 +8512,7 @@
       <c r="L91" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="M91" s="11" t="s">
+      <c r="M91" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N91" s="7" t="s">
@@ -8491,7 +8531,7 @@
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
     </row>
-    <row r="92" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>0</v>
       </c>
@@ -8529,7 +8569,7 @@
       <c r="L92" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="M92" s="11" t="s">
+      <c r="M92" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N92" s="7" t="s">
@@ -8548,7 +8588,7 @@
       <c r="Y92" s="7"/>
       <c r="Z92" s="7"/>
     </row>
-    <row r="93" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>0</v>
       </c>
@@ -8586,7 +8626,7 @@
       <c r="L93" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="M93" s="11" t="s">
+      <c r="M93" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N93" s="7" t="s">
@@ -8605,7 +8645,7 @@
       <c r="Y93" s="7"/>
       <c r="Z93" s="7"/>
     </row>
-    <row r="94" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>0</v>
       </c>
@@ -8643,7 +8683,7 @@
       <c r="L94" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="M94" s="11" t="s">
+      <c r="M94" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N94" s="7" t="s">
@@ -8662,7 +8702,7 @@
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
     </row>
-    <row r="95" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>0</v>
       </c>
@@ -8700,7 +8740,7 @@
       <c r="L95" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="M95" s="11" t="s">
+      <c r="M95" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N95" s="7" t="s">
@@ -8719,7 +8759,7 @@
       <c r="Y95" s="7"/>
       <c r="Z95" s="7"/>
     </row>
-    <row r="96" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>0</v>
       </c>
@@ -8757,7 +8797,7 @@
       <c r="L96" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="M96" s="11" t="s">
+      <c r="M96" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N96" s="7" t="s">
@@ -8776,7 +8816,7 @@
       <c r="Y96" s="7"/>
       <c r="Z96" s="7"/>
     </row>
-    <row r="97" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>0</v>
       </c>
@@ -8833,7 +8873,7 @@
       <c r="Y97" s="7"/>
       <c r="Z97" s="7"/>
     </row>
-    <row r="98" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>0</v>
       </c>
@@ -8890,7 +8930,7 @@
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
     </row>
-    <row r="99" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>0</v>
       </c>
@@ -8947,7 +8987,7 @@
       <c r="Y99" s="7"/>
       <c r="Z99" s="7"/>
     </row>
-    <row r="100" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>0</v>
       </c>
@@ -9004,7 +9044,7 @@
       <c r="Y100" s="7"/>
       <c r="Z100" s="7"/>
     </row>
-    <row r="101" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>0</v>
       </c>
@@ -9061,7 +9101,7 @@
       <c r="Y101" s="7"/>
       <c r="Z101" s="7"/>
     </row>
-    <row r="102" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>0</v>
       </c>
@@ -9118,7 +9158,7 @@
       <c r="Y102" s="7"/>
       <c r="Z102" s="7"/>
     </row>
-    <row r="103" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>0</v>
       </c>
@@ -9175,7 +9215,7 @@
       <c r="Y103" s="7"/>
       <c r="Z103" s="7"/>
     </row>
-    <row r="104" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>0</v>
       </c>
@@ -9232,7 +9272,7 @@
       <c r="Y104" s="7"/>
       <c r="Z104" s="7"/>
     </row>
-    <row r="105" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>0</v>
       </c>
@@ -9289,7 +9329,7 @@
       <c r="Y105" s="7"/>
       <c r="Z105" s="7"/>
     </row>
-    <row r="106" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>0</v>
       </c>
@@ -9346,7 +9386,7 @@
       <c r="Y106" s="7"/>
       <c r="Z106" s="7"/>
     </row>
-    <row r="107" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>0</v>
       </c>
@@ -9403,7 +9443,7 @@
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
     </row>
-    <row r="108" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>0</v>
       </c>
@@ -9460,7 +9500,7 @@
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
     </row>
-    <row r="109" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>0</v>
       </c>
@@ -9517,7 +9557,7 @@
       <c r="Y109" s="7"/>
       <c r="Z109" s="7"/>
     </row>
-    <row r="110" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>0</v>
       </c>
@@ -9574,7 +9614,7 @@
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
     </row>
-    <row r="111" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>0</v>
       </c>
@@ -9631,7 +9671,7 @@
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
     </row>
-    <row r="112" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>0</v>
       </c>
@@ -9688,7 +9728,7 @@
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
     </row>
-    <row r="113" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>0</v>
       </c>
@@ -9745,7 +9785,7 @@
       <c r="Y113" s="7"/>
       <c r="Z113" s="7"/>
     </row>
-    <row r="114" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>0</v>
       </c>
@@ -9783,7 +9823,7 @@
       <c r="L114" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="M114" s="11" t="s">
+      <c r="M114" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N114" s="7" t="s">
@@ -9802,7 +9842,7 @@
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
     </row>
-    <row r="115" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>0</v>
       </c>
@@ -9840,7 +9880,7 @@
       <c r="L115" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="M115" s="11" t="s">
+      <c r="M115" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N115" s="7" t="s">
@@ -9859,7 +9899,7 @@
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
     </row>
-    <row r="116" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>0</v>
       </c>
@@ -9897,7 +9937,7 @@
       <c r="L116" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="M116" s="11" t="s">
+      <c r="M116" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N116" s="7" t="s">
@@ -9916,7 +9956,7 @@
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
     </row>
-    <row r="117" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>0</v>
       </c>
@@ -9954,7 +9994,7 @@
       <c r="L117" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="M117" s="11" t="s">
+      <c r="M117" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N117" s="7" t="s">
@@ -9973,7 +10013,7 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
     </row>
-    <row r="118" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>0</v>
       </c>
@@ -10030,7 +10070,7 @@
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
     </row>
-    <row r="119" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>0</v>
       </c>
@@ -10068,7 +10108,7 @@
       <c r="L119" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="M119" s="11" t="s">
+      <c r="M119" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N119" s="7" t="s">
@@ -10087,7 +10127,7 @@
       <c r="Y119" s="7"/>
       <c r="Z119" s="7"/>
     </row>
-    <row r="120" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>0</v>
       </c>
@@ -10144,7 +10184,7 @@
       <c r="Y120" s="7"/>
       <c r="Z120" s="7"/>
     </row>
-    <row r="121" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>0</v>
       </c>
@@ -10201,7 +10241,7 @@
       <c r="Y121" s="7"/>
       <c r="Z121" s="7"/>
     </row>
-    <row r="122" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>0</v>
       </c>
@@ -10239,7 +10279,7 @@
       <c r="L122" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="M122" s="11" t="s">
+      <c r="M122" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N122" s="7" t="s">
@@ -10258,7 +10298,7 @@
       <c r="Y122" s="7"/>
       <c r="Z122" s="7"/>
     </row>
-    <row r="123" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>0</v>
       </c>
@@ -10296,7 +10336,7 @@
       <c r="L123" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M123" s="11" t="s">
+      <c r="M123" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N123" s="7" t="s">
@@ -10315,7 +10355,7 @@
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
     </row>
-    <row r="124" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>0</v>
       </c>
@@ -10353,7 +10393,7 @@
       <c r="L124" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="M124" s="11" t="s">
+      <c r="M124" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N124" s="7" t="s">
@@ -10372,7 +10412,7 @@
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
     </row>
-    <row r="125" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>0</v>
       </c>
@@ -10410,7 +10450,7 @@
       <c r="L125" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="M125" s="11" t="s">
+      <c r="M125" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N125" s="7" t="s">
@@ -10429,7 +10469,7 @@
       <c r="Y125" s="7"/>
       <c r="Z125" s="7"/>
     </row>
-    <row r="126" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>0</v>
       </c>
@@ -10467,7 +10507,7 @@
       <c r="L126" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="M126" s="11" t="s">
+      <c r="M126" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N126" s="7" t="s">
@@ -10486,7 +10526,7 @@
       <c r="Y126" s="7"/>
       <c r="Z126" s="7"/>
     </row>
-    <row r="127" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>0</v>
       </c>
@@ -10524,7 +10564,7 @@
       <c r="L127" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="M127" s="11" t="s">
+      <c r="M127" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N127" s="7" t="s">
@@ -10543,7 +10583,7 @@
       <c r="Y127" s="7"/>
       <c r="Z127" s="7"/>
     </row>
-    <row r="128" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>0</v>
       </c>
@@ -10581,7 +10621,7 @@
       <c r="L128" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="M128" s="11" t="s">
+      <c r="M128" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N128" s="7" t="s">
@@ -10600,7 +10640,7 @@
       <c r="Y128" s="7"/>
       <c r="Z128" s="7"/>
     </row>
-    <row r="129" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>0</v>
       </c>
@@ -10638,7 +10678,7 @@
       <c r="L129" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M129" s="11" t="s">
+      <c r="M129" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N129" s="7" t="s">
@@ -10657,7 +10697,7 @@
       <c r="Y129" s="7"/>
       <c r="Z129" s="7"/>
     </row>
-    <row r="130" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>0</v>
       </c>
@@ -10695,7 +10735,7 @@
       <c r="L130" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M130" s="11" t="s">
+      <c r="M130" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N130" s="7" t="s">
@@ -10714,7 +10754,7 @@
       <c r="Y130" s="7"/>
       <c r="Z130" s="7"/>
     </row>
-    <row r="131" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>0</v>
       </c>
@@ -10752,7 +10792,7 @@
       <c r="L131" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M131" s="11" t="s">
+      <c r="M131" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N131" s="7" t="s">
@@ -10771,7 +10811,7 @@
       <c r="Y131" s="7"/>
       <c r="Z131" s="7"/>
     </row>
-    <row r="132" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>0</v>
       </c>
@@ -10809,7 +10849,7 @@
       <c r="L132" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M132" s="11" t="s">
+      <c r="M132" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N132" s="7" t="s">
@@ -10828,7 +10868,7 @@
       <c r="Y132" s="7"/>
       <c r="Z132" s="7"/>
     </row>
-    <row r="133" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>0</v>
       </c>
@@ -10866,7 +10906,7 @@
       <c r="L133" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M133" s="11" t="s">
+      <c r="M133" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N133" s="7" t="s">
@@ -10885,7 +10925,7 @@
       <c r="Y133" s="7"/>
       <c r="Z133" s="7"/>
     </row>
-    <row r="134" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>0</v>
       </c>
@@ -10923,7 +10963,7 @@
       <c r="L134" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M134" s="11" t="s">
+      <c r="M134" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N134" s="7" t="s">
@@ -10942,7 +10982,7 @@
       <c r="Y134" s="7"/>
       <c r="Z134" s="7"/>
     </row>
-    <row r="135" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>0</v>
       </c>
@@ -10980,7 +11020,7 @@
       <c r="L135" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M135" s="11" t="s">
+      <c r="M135" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N135" s="7" t="s">
@@ -10999,7 +11039,7 @@
       <c r="Y135" s="7"/>
       <c r="Z135" s="7"/>
     </row>
-    <row r="136" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>0</v>
       </c>
@@ -11037,7 +11077,7 @@
       <c r="L136" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M136" s="11" t="s">
+      <c r="M136" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N136" s="7" t="s">
@@ -11056,7 +11096,7 @@
       <c r="Y136" s="7"/>
       <c r="Z136" s="7"/>
     </row>
-    <row r="137" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>0</v>
       </c>
@@ -11094,7 +11134,7 @@
       <c r="L137" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M137" s="11" t="s">
+      <c r="M137" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N137" s="7" t="s">
@@ -11113,7 +11153,7 @@
       <c r="Y137" s="7"/>
       <c r="Z137" s="7"/>
     </row>
-    <row r="138" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>0</v>
       </c>
@@ -11151,7 +11191,7 @@
       <c r="L138" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M138" s="11" t="s">
+      <c r="M138" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N138" s="7" t="s">
@@ -11170,7 +11210,7 @@
       <c r="Y138" s="7"/>
       <c r="Z138" s="7"/>
     </row>
-    <row r="139" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>0</v>
       </c>
@@ -11208,7 +11248,7 @@
       <c r="L139" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M139" s="11" t="s">
+      <c r="M139" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N139" s="7" t="s">
@@ -11227,7 +11267,7 @@
       <c r="Y139" s="7"/>
       <c r="Z139" s="7"/>
     </row>
-    <row r="140" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>0</v>
       </c>
@@ -11265,7 +11305,7 @@
       <c r="L140" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M140" s="11" t="s">
+      <c r="M140" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N140" s="7" t="s">
@@ -11284,7 +11324,7 @@
       <c r="Y140" s="7"/>
       <c r="Z140" s="7"/>
     </row>
-    <row r="141" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>0</v>
       </c>
@@ -11322,7 +11362,7 @@
       <c r="L141" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M141" s="11" t="s">
+      <c r="M141" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N141" s="7" t="s">
@@ -11341,7 +11381,7 @@
       <c r="Y141" s="7"/>
       <c r="Z141" s="7"/>
     </row>
-    <row r="142" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>0</v>
       </c>
@@ -11379,7 +11419,7 @@
       <c r="L142" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M142" s="11" t="s">
+      <c r="M142" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N142" s="7" t="s">
@@ -11398,7 +11438,7 @@
       <c r="Y142" s="7"/>
       <c r="Z142" s="7"/>
     </row>
-    <row r="143" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>0</v>
       </c>
@@ -11436,7 +11476,7 @@
       <c r="L143" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M143" s="11" t="s">
+      <c r="M143" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N143" s="7" t="s">
@@ -11455,7 +11495,7 @@
       <c r="Y143" s="7"/>
       <c r="Z143" s="7"/>
     </row>
-    <row r="144" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>0</v>
       </c>
@@ -11493,7 +11533,7 @@
       <c r="L144" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M144" s="11" t="s">
+      <c r="M144" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N144" s="7" t="s">
@@ -11512,7 +11552,7 @@
       <c r="Y144" s="7"/>
       <c r="Z144" s="7"/>
     </row>
-    <row r="145" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>0</v>
       </c>
@@ -11550,7 +11590,7 @@
       <c r="L145" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="M145" s="11" t="s">
+      <c r="M145" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N145" s="7" t="s">
@@ -11569,7 +11609,7 @@
       <c r="Y145" s="7"/>
       <c r="Z145" s="7"/>
     </row>
-    <row r="146" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>0</v>
       </c>
@@ -11607,7 +11647,7 @@
       <c r="L146" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="M146" s="11" t="s">
+      <c r="M146" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N146" s="7" t="s">
@@ -11626,7 +11666,7 @@
       <c r="Y146" s="7"/>
       <c r="Z146" s="7"/>
     </row>
-    <row r="147" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>0</v>
       </c>
@@ -11683,7 +11723,7 @@
       <c r="Y147" s="7"/>
       <c r="Z147" s="7"/>
     </row>
-    <row r="148" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>0</v>
       </c>
@@ -11721,7 +11761,7 @@
       <c r="L148" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="M148" s="11" t="s">
+      <c r="M148" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N148" s="7" t="s">
@@ -11740,7 +11780,7 @@
       <c r="Y148" s="7"/>
       <c r="Z148" s="7"/>
     </row>
-    <row r="149" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>0</v>
       </c>
@@ -11797,7 +11837,7 @@
       <c r="Y149" s="7"/>
       <c r="Z149" s="7"/>
     </row>
-    <row r="150" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>0</v>
       </c>
@@ -11835,7 +11875,7 @@
       <c r="L150" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="M150" s="11" t="s">
+      <c r="M150" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N150" s="7" t="s">
@@ -11854,7 +11894,7 @@
       <c r="Y150" s="7"/>
       <c r="Z150" s="7"/>
     </row>
-    <row r="151" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>0</v>
       </c>
@@ -11911,7 +11951,7 @@
       <c r="Y151" s="7"/>
       <c r="Z151" s="7"/>
     </row>
-    <row r="152" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>0</v>
       </c>
@@ -11949,7 +11989,7 @@
       <c r="L152" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="M152" s="11" t="s">
+      <c r="M152" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N152" s="7" t="s">
@@ -11968,7 +12008,7 @@
       <c r="Y152" s="7"/>
       <c r="Z152" s="7"/>
     </row>
-    <row r="153" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>0</v>
       </c>
@@ -12006,7 +12046,7 @@
       <c r="L153" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="M153" s="11" t="s">
+      <c r="M153" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N153" s="7" t="s">
@@ -12025,7 +12065,7 @@
       <c r="Y153" s="7"/>
       <c r="Z153" s="7"/>
     </row>
-    <row r="154" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>0</v>
       </c>
@@ -12082,7 +12122,7 @@
       <c r="Y154" s="7"/>
       <c r="Z154" s="7"/>
     </row>
-    <row r="155" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>0</v>
       </c>
@@ -12120,7 +12160,7 @@
       <c r="L155" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="M155" s="11" t="s">
+      <c r="M155" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N155" s="7" t="s">
@@ -12139,7 +12179,7 @@
       <c r="Y155" s="7"/>
       <c r="Z155" s="7"/>
     </row>
-    <row r="156" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>0</v>
       </c>
@@ -12196,7 +12236,7 @@
       <c r="Y156" s="7"/>
       <c r="Z156" s="7"/>
     </row>
-    <row r="157" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>0</v>
       </c>
@@ -12253,7 +12293,7 @@
       <c r="Y157" s="7"/>
       <c r="Z157" s="7"/>
     </row>
-    <row r="158" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>0</v>
       </c>
@@ -12310,7 +12350,7 @@
       <c r="Y158" s="7"/>
       <c r="Z158" s="7"/>
     </row>
-    <row r="159" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>0</v>
       </c>
@@ -12367,7 +12407,7 @@
       <c r="Y159" s="7"/>
       <c r="Z159" s="7"/>
     </row>
-    <row r="160" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>0</v>
       </c>
@@ -12424,7 +12464,7 @@
       <c r="Y160" s="7"/>
       <c r="Z160" s="7"/>
     </row>
-    <row r="161" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>0</v>
       </c>
@@ -12481,7 +12521,7 @@
       <c r="Y161" s="7"/>
       <c r="Z161" s="7"/>
     </row>
-    <row r="162" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>0</v>
       </c>
@@ -12519,7 +12559,7 @@
       <c r="L162" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="M162" s="11" t="s">
+      <c r="M162" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N162" s="7" t="s">
@@ -12538,7 +12578,7 @@
       <c r="Y162" s="7"/>
       <c r="Z162" s="7"/>
     </row>
-    <row r="163" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>0</v>
       </c>
@@ -12576,7 +12616,7 @@
       <c r="L163" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="M163" s="11" t="s">
+      <c r="M163" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N163" s="7" t="s">
@@ -12595,7 +12635,7 @@
       <c r="Y163" s="7"/>
       <c r="Z163" s="7"/>
     </row>
-    <row r="164" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>0</v>
       </c>
@@ -12633,7 +12673,7 @@
       <c r="L164" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="M164" s="11" t="s">
+      <c r="M164" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N164" s="7" t="s">
@@ -12652,7 +12692,7 @@
       <c r="Y164" s="7"/>
       <c r="Z164" s="7"/>
     </row>
-    <row r="165" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>0</v>
       </c>
@@ -12690,7 +12730,7 @@
       <c r="L165" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="M165" s="11" t="s">
+      <c r="M165" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N165" s="7" t="s">
@@ -12709,7 +12749,7 @@
       <c r="Y165" s="7"/>
       <c r="Z165" s="7"/>
     </row>
-    <row r="166" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>0</v>
       </c>
@@ -12747,7 +12787,7 @@
       <c r="L166" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="M166" s="11" t="s">
+      <c r="M166" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N166" s="7" t="s">
@@ -12766,7 +12806,7 @@
       <c r="Y166" s="7"/>
       <c r="Z166" s="7"/>
     </row>
-    <row r="167" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>0</v>
       </c>
@@ -12823,7 +12863,7 @@
       <c r="Y167" s="7"/>
       <c r="Z167" s="7"/>
     </row>
-    <row r="168" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>0</v>
       </c>
@@ -12880,7 +12920,7 @@
       <c r="Y168" s="7"/>
       <c r="Z168" s="7"/>
     </row>
-    <row r="169" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>0</v>
       </c>
@@ -12918,7 +12958,7 @@
       <c r="L169" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="M169" s="11" t="s">
+      <c r="M169" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N169" s="7" t="s">
@@ -12937,7 +12977,7 @@
       <c r="Y169" s="7"/>
       <c r="Z169" s="7"/>
     </row>
-    <row r="170" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>0</v>
       </c>
@@ -12975,7 +13015,7 @@
       <c r="L170" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="M170" s="11" t="s">
+      <c r="M170" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N170" s="7" t="s">
@@ -12994,7 +13034,7 @@
       <c r="Y170" s="7"/>
       <c r="Z170" s="7"/>
     </row>
-    <row r="171" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>0</v>
       </c>
@@ -13051,7 +13091,7 @@
       <c r="Y171" s="7"/>
       <c r="Z171" s="7"/>
     </row>
-    <row r="172" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>0</v>
       </c>
@@ -13089,7 +13129,7 @@
       <c r="L172" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="M172" s="11" t="s">
+      <c r="M172" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N172" s="7" t="s">
@@ -13108,7 +13148,7 @@
       <c r="Y172" s="7"/>
       <c r="Z172" s="7"/>
     </row>
-    <row r="173" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>0</v>
       </c>
@@ -13165,7 +13205,7 @@
       <c r="Y173" s="7"/>
       <c r="Z173" s="7"/>
     </row>
-    <row r="174" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>0</v>
       </c>
@@ -13203,7 +13243,7 @@
       <c r="L174" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="M174" s="11" t="s">
+      <c r="M174" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N174" s="7" t="s">
@@ -13222,7 +13262,7 @@
       <c r="Y174" s="7"/>
       <c r="Z174" s="7"/>
     </row>
-    <row r="175" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>0</v>
       </c>
@@ -13260,7 +13300,7 @@
       <c r="L175" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="M175" s="11" t="s">
+      <c r="M175" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N175" s="7" t="s">
@@ -13279,7 +13319,7 @@
       <c r="Y175" s="7"/>
       <c r="Z175" s="7"/>
     </row>
-    <row r="176" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>0</v>
       </c>
@@ -13336,7 +13376,7 @@
       <c r="Y176" s="7"/>
       <c r="Z176" s="7"/>
     </row>
-    <row r="177" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>0</v>
       </c>
@@ -13374,7 +13414,7 @@
       <c r="L177" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="M177" s="11" t="s">
+      <c r="M177" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N177" s="7" t="s">
@@ -13393,7 +13433,7 @@
       <c r="Y177" s="7"/>
       <c r="Z177" s="7"/>
     </row>
-    <row r="178" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>0</v>
       </c>
@@ -13431,7 +13471,7 @@
       <c r="L178" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="M178" s="11" t="s">
+      <c r="M178" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N178" s="7" t="s">
@@ -13450,7 +13490,7 @@
       <c r="Y178" s="7"/>
       <c r="Z178" s="7"/>
     </row>
-    <row r="179" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>0</v>
       </c>
@@ -13488,7 +13528,7 @@
       <c r="L179" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="M179" s="11" t="s">
+      <c r="M179" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N179" s="7" t="s">
@@ -13507,7 +13547,7 @@
       <c r="Y179" s="7"/>
       <c r="Z179" s="7"/>
     </row>
-    <row r="180" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>0</v>
       </c>
@@ -13545,7 +13585,7 @@
       <c r="L180" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="M180" s="11" t="s">
+      <c r="M180" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N180" s="7" t="s">
@@ -13564,7 +13604,7 @@
       <c r="Y180" s="7"/>
       <c r="Z180" s="7"/>
     </row>
-    <row r="181" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>0</v>
       </c>
@@ -13602,7 +13642,7 @@
       <c r="L181" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="M181" s="11" t="s">
+      <c r="M181" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N181" s="7" t="s">
@@ -13621,7 +13661,7 @@
       <c r="Y181" s="7"/>
       <c r="Z181" s="7"/>
     </row>
-    <row r="182" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>0</v>
       </c>
@@ -13678,7 +13718,7 @@
       <c r="Y182" s="7"/>
       <c r="Z182" s="7"/>
     </row>
-    <row r="183" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>0</v>
       </c>
@@ -13735,7 +13775,7 @@
       <c r="Y183" s="7"/>
       <c r="Z183" s="7"/>
     </row>
-    <row r="184" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>0</v>
       </c>
@@ -13764,11 +13804,11 @@
         <v>13200000</v>
       </c>
       <c r="J184" s="8">
-        <v>11350857.109999999</v>
+        <v>13198526.93</v>
       </c>
       <c r="K184" s="8">
         <f t="shared" si="0"/>
-        <v>11350857.109999999</v>
+        <v>13198526.93</v>
       </c>
       <c r="L184" s="7" t="s">
         <v>168</v>
@@ -13792,7 +13832,7 @@
       <c r="Y184" s="7"/>
       <c r="Z184" s="7"/>
     </row>
-    <row r="185" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>0</v>
       </c>
@@ -13830,7 +13870,7 @@
       <c r="L185" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="M185" s="11" t="s">
+      <c r="M185" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N185" s="7" t="s">
@@ -13849,7 +13889,7 @@
       <c r="Y185" s="7"/>
       <c r="Z185" s="7"/>
     </row>
-    <row r="186" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>0</v>
       </c>
@@ -13887,7 +13927,7 @@
       <c r="L186" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="M186" s="11" t="s">
+      <c r="M186" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N186" s="7" t="s">
@@ -13906,7 +13946,7 @@
       <c r="Y186" s="7"/>
       <c r="Z186" s="7"/>
     </row>
-    <row r="187" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>0</v>
       </c>
@@ -13963,7 +14003,7 @@
       <c r="Y187" s="7"/>
       <c r="Z187" s="7"/>
     </row>
-    <row r="188" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>0</v>
       </c>
@@ -14001,7 +14041,7 @@
       <c r="L188" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="M188" s="11" t="s">
+      <c r="M188" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N188" s="7" t="s">
@@ -14020,7 +14060,7 @@
       <c r="Y188" s="7"/>
       <c r="Z188" s="7"/>
     </row>
-    <row r="189" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>0</v>
       </c>
@@ -14058,7 +14098,7 @@
       <c r="L189" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="M189" s="11" t="s">
+      <c r="M189" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N189" s="7" t="s">
@@ -14077,7 +14117,7 @@
       <c r="Y189" s="7"/>
       <c r="Z189" s="7"/>
     </row>
-    <row r="190" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>0</v>
       </c>
@@ -14134,7 +14174,7 @@
       <c r="Y190" s="7"/>
       <c r="Z190" s="7"/>
     </row>
-    <row r="191" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>0</v>
       </c>
@@ -14172,7 +14212,7 @@
       <c r="L191" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="M191" s="11" t="s">
+      <c r="M191" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N191" s="7" t="s">
@@ -14191,7 +14231,7 @@
       <c r="Y191" s="7"/>
       <c r="Z191" s="7"/>
     </row>
-    <row r="192" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>0</v>
       </c>
@@ -14229,7 +14269,7 @@
       <c r="L192" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="M192" s="11" t="s">
+      <c r="M192" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N192" s="7" t="s">
@@ -14248,7 +14288,7 @@
       <c r="Y192" s="7"/>
       <c r="Z192" s="7"/>
     </row>
-    <row r="193" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>0</v>
       </c>
@@ -14305,7 +14345,7 @@
       <c r="Y193" s="7"/>
       <c r="Z193" s="7"/>
     </row>
-    <row r="194" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>0</v>
       </c>
@@ -14343,7 +14383,7 @@
       <c r="L194" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="M194" s="11" t="s">
+      <c r="M194" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N194" s="7" t="s">
@@ -14362,7 +14402,7 @@
       <c r="Y194" s="7"/>
       <c r="Z194" s="7"/>
     </row>
-    <row r="195" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>0</v>
       </c>
@@ -14400,7 +14440,7 @@
       <c r="L195" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="M195" s="11" t="s">
+      <c r="M195" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N195" s="7" t="s">
@@ -14419,7 +14459,7 @@
       <c r="Y195" s="7"/>
       <c r="Z195" s="7"/>
     </row>
-    <row r="196" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>0</v>
       </c>
@@ -14457,7 +14497,7 @@
       <c r="L196" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="M196" s="11" t="s">
+      <c r="M196" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N196" s="7" t="s">
@@ -14476,7 +14516,7 @@
       <c r="Y196" s="7"/>
       <c r="Z196" s="7"/>
     </row>
-    <row r="197" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>0</v>
       </c>
@@ -14514,7 +14554,7 @@
       <c r="L197" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="M197" s="11" t="s">
+      <c r="M197" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N197" s="7" t="s">
@@ -14533,7 +14573,7 @@
       <c r="Y197" s="7"/>
       <c r="Z197" s="7"/>
     </row>
-    <row r="198" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>0</v>
       </c>
@@ -14571,7 +14611,7 @@
       <c r="L198" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="M198" s="11" t="s">
+      <c r="M198" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N198" s="7" t="s">
@@ -14590,7 +14630,7 @@
       <c r="Y198" s="7"/>
       <c r="Z198" s="7"/>
     </row>
-    <row r="199" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>0</v>
       </c>
@@ -14628,7 +14668,7 @@
       <c r="L199" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="M199" s="11" t="s">
+      <c r="M199" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N199" s="7" t="s">
@@ -14647,7 +14687,7 @@
       <c r="Y199" s="7"/>
       <c r="Z199" s="7"/>
     </row>
-    <row r="200" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>0</v>
       </c>
@@ -14704,7 +14744,7 @@
       <c r="Y200" s="7"/>
       <c r="Z200" s="7"/>
     </row>
-    <row r="201" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>0</v>
       </c>
@@ -14742,7 +14782,7 @@
       <c r="L201" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="M201" s="11" t="s">
+      <c r="M201" s="10" t="s">
         <v>35</v>
       </c>
       <c r="N201" s="7" t="s">
@@ -14761,7 +14801,7 @@
       <c r="Y201" s="7"/>
       <c r="Z201" s="7"/>
     </row>
-    <row r="202" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>0</v>
       </c>
@@ -14799,7 +14839,7 @@
       <c r="L202" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="M202" s="11" t="s">
+      <c r="M202" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N202" s="7" t="s">
@@ -14818,7 +14858,7 @@
       <c r="Y202" s="7"/>
       <c r="Z202" s="7"/>
     </row>
-    <row r="203" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>0</v>
       </c>
@@ -14856,7 +14896,7 @@
       <c r="L203" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="M203" s="11" t="s">
+      <c r="M203" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N203" s="7" t="s">
@@ -14875,7 +14915,7 @@
       <c r="Y203" s="7"/>
       <c r="Z203" s="7"/>
     </row>
-    <row r="204" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>0</v>
       </c>
@@ -14913,7 +14953,7 @@
       <c r="L204" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="M204" s="11" t="s">
+      <c r="M204" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N204" s="7" t="s">
@@ -14932,7 +14972,7 @@
       <c r="Y204" s="7"/>
       <c r="Z204" s="7"/>
     </row>
-    <row r="205" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>0</v>
       </c>
@@ -14970,7 +15010,7 @@
       <c r="L205" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="M205" s="11" t="s">
+      <c r="M205" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N205" s="7" t="s">
@@ -14989,7 +15029,7 @@
       <c r="Y205" s="7"/>
       <c r="Z205" s="7"/>
     </row>
-    <row r="206" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>0</v>
       </c>
@@ -15027,7 +15067,7 @@
       <c r="L206" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="M206" s="11" t="s">
+      <c r="M206" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N206" s="7" t="s">
@@ -15046,7 +15086,7 @@
       <c r="Y206" s="7"/>
       <c r="Z206" s="7"/>
     </row>
-    <row r="207" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>0</v>
       </c>
@@ -15103,7 +15143,7 @@
       <c r="Y207" s="7"/>
       <c r="Z207" s="7"/>
     </row>
-    <row r="208" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>0</v>
       </c>
@@ -15141,7 +15181,7 @@
       <c r="L208" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="M208" s="11" t="s">
+      <c r="M208" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N208" s="7" t="s">
@@ -15160,7 +15200,7 @@
       <c r="Y208" s="7"/>
       <c r="Z208" s="7"/>
     </row>
-    <row r="209" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>0</v>
       </c>
@@ -15198,7 +15238,7 @@
       <c r="L209" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="M209" s="11" t="s">
+      <c r="M209" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N209" s="7" t="s">
@@ -15217,7 +15257,7 @@
       <c r="Y209" s="7"/>
       <c r="Z209" s="7"/>
     </row>
-    <row r="210" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>0</v>
       </c>
@@ -15255,7 +15295,7 @@
       <c r="L210" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="M210" s="11" t="s">
+      <c r="M210" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N210" s="7" t="s">
@@ -15274,7 +15314,7 @@
       <c r="Y210" s="7"/>
       <c r="Z210" s="7"/>
     </row>
-    <row r="211" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>0</v>
       </c>
@@ -15331,7 +15371,7 @@
       <c r="Y211" s="7"/>
       <c r="Z211" s="7"/>
     </row>
-    <row r="212" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>0</v>
       </c>
@@ -15369,7 +15409,7 @@
       <c r="L212" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="M212" s="11" t="s">
+      <c r="M212" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N212" s="7" t="s">
@@ -15388,7 +15428,7 @@
       <c r="Y212" s="7"/>
       <c r="Z212" s="7"/>
     </row>
-    <row r="213" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>0</v>
       </c>
@@ -15445,7 +15485,7 @@
       <c r="Y213" s="7"/>
       <c r="Z213" s="7"/>
     </row>
-    <row r="214" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>0</v>
       </c>
@@ -15502,7 +15542,7 @@
       <c r="Y214" s="7"/>
       <c r="Z214" s="7"/>
     </row>
-    <row r="215" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>0</v>
       </c>
@@ -15559,7 +15599,7 @@
       <c r="Y215" s="7"/>
       <c r="Z215" s="7"/>
     </row>
-    <row r="216" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>0</v>
       </c>
@@ -15597,7 +15637,7 @@
       <c r="L216" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="M216" s="11" t="s">
+      <c r="M216" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N216" s="7" t="s">
@@ -15616,7 +15656,7 @@
       <c r="Y216" s="7"/>
       <c r="Z216" s="7"/>
     </row>
-    <row r="217" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>0</v>
       </c>
@@ -15673,7 +15713,7 @@
       <c r="Y217" s="7"/>
       <c r="Z217" s="7"/>
     </row>
-    <row r="218" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>0</v>
       </c>
@@ -15711,7 +15751,7 @@
       <c r="L218" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="M218" s="11" t="s">
+      <c r="M218" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N218" s="7" t="s">
@@ -15730,7 +15770,7 @@
       <c r="Y218" s="7"/>
       <c r="Z218" s="7"/>
     </row>
-    <row r="219" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>0</v>
       </c>
@@ -15768,7 +15808,7 @@
       <c r="L219" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="M219" s="11" t="s">
+      <c r="M219" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N219" s="7" t="s">
@@ -15787,7 +15827,7 @@
       <c r="Y219" s="7"/>
       <c r="Z219" s="7"/>
     </row>
-    <row r="220" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>0</v>
       </c>
@@ -15844,7 +15884,7 @@
       <c r="Y220" s="7"/>
       <c r="Z220" s="7"/>
     </row>
-    <row r="221" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>0</v>
       </c>
@@ -15901,7 +15941,7 @@
       <c r="Y221" s="7"/>
       <c r="Z221" s="7"/>
     </row>
-    <row r="222" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>0</v>
       </c>
@@ -15958,7 +15998,7 @@
       <c r="Y222" s="7"/>
       <c r="Z222" s="7"/>
     </row>
-    <row r="223" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>0</v>
       </c>
@@ -15996,7 +16036,7 @@
       <c r="L223" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="M223" s="11" t="s">
+      <c r="M223" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N223" s="7" t="s">
@@ -16015,7 +16055,7 @@
       <c r="Y223" s="7"/>
       <c r="Z223" s="7"/>
     </row>
-    <row r="224" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>0</v>
       </c>
@@ -16072,7 +16112,7 @@
       <c r="Y224" s="7"/>
       <c r="Z224" s="7"/>
     </row>
-    <row r="225" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>0</v>
       </c>
@@ -16129,7 +16169,7 @@
       <c r="Y225" s="7"/>
       <c r="Z225" s="7"/>
     </row>
-    <row r="226" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>0</v>
       </c>
@@ -16167,7 +16207,7 @@
       <c r="L226" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M226" s="11" t="s">
+      <c r="M226" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N226" s="7" t="s">
@@ -16186,7 +16226,7 @@
       <c r="Y226" s="7"/>
       <c r="Z226" s="7"/>
     </row>
-    <row r="227" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>0</v>
       </c>
@@ -16224,7 +16264,7 @@
       <c r="L227" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M227" s="11" t="s">
+      <c r="M227" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N227" s="7" t="s">
@@ -16243,7 +16283,7 @@
       <c r="Y227" s="7"/>
       <c r="Z227" s="7"/>
     </row>
-    <row r="228" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>0</v>
       </c>
@@ -16281,7 +16321,7 @@
       <c r="L228" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M228" s="11" t="s">
+      <c r="M228" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N228" s="7" t="s">
@@ -16300,7 +16340,7 @@
       <c r="Y228" s="7"/>
       <c r="Z228" s="7"/>
     </row>
-    <row r="229" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>0</v>
       </c>
@@ -16338,7 +16378,7 @@
       <c r="L229" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M229" s="11" t="s">
+      <c r="M229" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N229" s="7" t="s">
@@ -16357,7 +16397,7 @@
       <c r="Y229" s="7"/>
       <c r="Z229" s="7"/>
     </row>
-    <row r="230" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>0</v>
       </c>
@@ -16395,7 +16435,7 @@
       <c r="L230" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M230" s="11" t="s">
+      <c r="M230" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N230" s="7" t="s">
@@ -16414,7 +16454,7 @@
       <c r="Y230" s="7"/>
       <c r="Z230" s="7"/>
     </row>
-    <row r="231" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>0</v>
       </c>
@@ -16452,7 +16492,7 @@
       <c r="L231" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M231" s="11" t="s">
+      <c r="M231" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N231" s="7" t="s">
@@ -16471,7 +16511,7 @@
       <c r="Y231" s="7"/>
       <c r="Z231" s="7"/>
     </row>
-    <row r="232" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>0</v>
       </c>
@@ -16509,7 +16549,7 @@
       <c r="L232" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M232" s="11" t="s">
+      <c r="M232" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N232" s="7" t="s">
@@ -16528,7 +16568,7 @@
       <c r="Y232" s="7"/>
       <c r="Z232" s="7"/>
     </row>
-    <row r="233" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>0</v>
       </c>
@@ -16566,7 +16606,7 @@
       <c r="L233" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M233" s="11" t="s">
+      <c r="M233" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N233" s="7" t="s">
@@ -16585,7 +16625,7 @@
       <c r="Y233" s="7"/>
       <c r="Z233" s="7"/>
     </row>
-    <row r="234" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>0</v>
       </c>
@@ -16623,7 +16663,7 @@
       <c r="L234" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M234" s="11" t="s">
+      <c r="M234" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N234" s="7" t="s">
@@ -16642,7 +16682,7 @@
       <c r="Y234" s="7"/>
       <c r="Z234" s="7"/>
     </row>
-    <row r="235" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>0</v>
       </c>
@@ -16680,7 +16720,7 @@
       <c r="L235" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="M235" s="11" t="s">
+      <c r="M235" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N235" s="7" t="s">
@@ -16699,7 +16739,7 @@
       <c r="Y235" s="7"/>
       <c r="Z235" s="7"/>
     </row>
-    <row r="236" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>0</v>
       </c>
@@ -16737,7 +16777,7 @@
       <c r="L236" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="M236" s="11" t="s">
+      <c r="M236" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N236" s="7" t="s">
@@ -16756,7 +16796,7 @@
       <c r="Y236" s="7"/>
       <c r="Z236" s="7"/>
     </row>
-    <row r="237" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>0</v>
       </c>
@@ -16794,7 +16834,7 @@
       <c r="L237" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="M237" s="11" t="s">
+      <c r="M237" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N237" s="7" t="s">
@@ -16813,7 +16853,7 @@
       <c r="Y237" s="7"/>
       <c r="Z237" s="7"/>
     </row>
-    <row r="238" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>0</v>
       </c>
@@ -16870,7 +16910,7 @@
       <c r="Y238" s="7"/>
       <c r="Z238" s="7"/>
     </row>
-    <row r="239" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>0</v>
       </c>
@@ -16908,7 +16948,7 @@
       <c r="L239" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="M239" s="11" t="s">
+      <c r="M239" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N239" s="7" t="s">
@@ -16927,7 +16967,7 @@
       <c r="Y239" s="7"/>
       <c r="Z239" s="7"/>
     </row>
-    <row r="240" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>0</v>
       </c>
@@ -16984,7 +17024,7 @@
       <c r="Y240" s="7"/>
       <c r="Z240" s="7"/>
     </row>
-    <row r="241" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>0</v>
       </c>
@@ -17022,7 +17062,7 @@
       <c r="L241" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M241" s="11" t="s">
+      <c r="M241" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N241" s="7" t="s">
@@ -17041,7 +17081,7 @@
       <c r="Y241" s="7"/>
       <c r="Z241" s="7"/>
     </row>
-    <row r="242" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>0</v>
       </c>
@@ -17079,7 +17119,7 @@
       <c r="L242" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M242" s="11" t="s">
+      <c r="M242" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N242" s="7" t="s">
@@ -17098,7 +17138,7 @@
       <c r="Y242" s="7"/>
       <c r="Z242" s="7"/>
     </row>
-    <row r="243" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>0</v>
       </c>
@@ -17136,7 +17176,7 @@
       <c r="L243" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M243" s="11" t="s">
+      <c r="M243" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N243" s="7" t="s">
@@ -17155,7 +17195,7 @@
       <c r="Y243" s="7"/>
       <c r="Z243" s="7"/>
     </row>
-    <row r="244" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>0</v>
       </c>
@@ -17193,7 +17233,7 @@
       <c r="L244" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M244" s="11" t="s">
+      <c r="M244" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N244" s="7" t="s">
@@ -17212,7 +17252,7 @@
       <c r="Y244" s="7"/>
       <c r="Z244" s="7"/>
     </row>
-    <row r="245" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>0</v>
       </c>
@@ -17250,7 +17290,7 @@
       <c r="L245" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M245" s="11" t="s">
+      <c r="M245" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N245" s="7" t="s">
@@ -17269,7 +17309,7 @@
       <c r="Y245" s="7"/>
       <c r="Z245" s="7"/>
     </row>
-    <row r="246" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>0</v>
       </c>
@@ -17307,7 +17347,7 @@
       <c r="L246" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M246" s="11" t="s">
+      <c r="M246" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N246" s="7" t="s">
@@ -17326,7 +17366,7 @@
       <c r="Y246" s="7"/>
       <c r="Z246" s="7"/>
     </row>
-    <row r="247" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>0</v>
       </c>
@@ -17364,7 +17404,7 @@
       <c r="L247" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M247" s="11" t="s">
+      <c r="M247" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N247" s="7" t="s">
@@ -17383,7 +17423,7 @@
       <c r="Y247" s="7"/>
       <c r="Z247" s="7"/>
     </row>
-    <row r="248" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>0</v>
       </c>
@@ -17421,7 +17461,7 @@
       <c r="L248" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M248" s="11" t="s">
+      <c r="M248" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N248" s="7" t="s">
@@ -17440,7 +17480,7 @@
       <c r="Y248" s="7"/>
       <c r="Z248" s="7"/>
     </row>
-    <row r="249" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>0</v>
       </c>
@@ -17478,7 +17518,7 @@
       <c r="L249" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="M249" s="11" t="s">
+      <c r="M249" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N249" s="7" t="s">
@@ -17497,7 +17537,7 @@
       <c r="Y249" s="7"/>
       <c r="Z249" s="7"/>
     </row>
-    <row r="250" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>0</v>
       </c>
@@ -17535,7 +17575,7 @@
       <c r="L250" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M250" s="11" t="s">
+      <c r="M250" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N250" s="7" t="s">
@@ -17554,7 +17594,7 @@
       <c r="Y250" s="7"/>
       <c r="Z250" s="7"/>
     </row>
-    <row r="251" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>0</v>
       </c>
@@ -17592,7 +17632,7 @@
       <c r="L251" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M251" s="11" t="s">
+      <c r="M251" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N251" s="7" t="s">
@@ -17611,7 +17651,7 @@
       <c r="Y251" s="7"/>
       <c r="Z251" s="7"/>
     </row>
-    <row r="252" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>0</v>
       </c>
@@ -17649,7 +17689,7 @@
       <c r="L252" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="M252" s="11" t="s">
+      <c r="M252" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N252" s="7" t="s">
@@ -17668,7 +17708,7 @@
       <c r="Y252" s="7"/>
       <c r="Z252" s="7"/>
     </row>
-    <row r="253" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>0</v>
       </c>
@@ -17706,7 +17746,7 @@
       <c r="L253" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="M253" s="11" t="s">
+      <c r="M253" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N253" s="7" t="s">
@@ -17725,7 +17765,7 @@
       <c r="Y253" s="7"/>
       <c r="Z253" s="7"/>
     </row>
-    <row r="254" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>0</v>
       </c>
@@ -17763,7 +17803,7 @@
       <c r="L254" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="M254" s="11" t="s">
+      <c r="M254" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N254" s="7" t="s">
@@ -17782,7 +17822,7 @@
       <c r="Y254" s="7"/>
       <c r="Z254" s="7"/>
     </row>
-    <row r="255" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>0</v>
       </c>
@@ -17820,7 +17860,7 @@
       <c r="L255" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="M255" s="11" t="s">
+      <c r="M255" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N255" s="7" t="s">
@@ -17839,7 +17879,7 @@
       <c r="Y255" s="7"/>
       <c r="Z255" s="7"/>
     </row>
-    <row r="256" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>0</v>
       </c>
@@ -17877,7 +17917,7 @@
       <c r="L256" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="M256" s="11" t="s">
+      <c r="M256" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N256" s="7" t="s">
@@ -17896,7 +17936,7 @@
       <c r="Y256" s="7"/>
       <c r="Z256" s="7"/>
     </row>
-    <row r="257" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>0</v>
       </c>
@@ -17928,13 +17968,13 @@
         <v>15337700</v>
       </c>
       <c r="K257" s="8">
-        <f t="shared" ref="K257:K427" si="1">IF(MATCH(G257,G$2:G257,0)=ROW(G257)-ROW(G$2)+1,J257,0)</f>
+        <f t="shared" ref="K257:K417" si="1">IF(MATCH(G257,G$2:G257,0)=ROW(G257)-ROW(G$2)+1,J257,0)</f>
         <v>0</v>
       </c>
       <c r="L257" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="M257" s="11" t="s">
+      <c r="M257" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N257" s="7" t="s">
@@ -17953,7 +17993,7 @@
       <c r="Y257" s="7"/>
       <c r="Z257" s="7"/>
     </row>
-    <row r="258" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>0</v>
       </c>
@@ -17991,7 +18031,7 @@
       <c r="L258" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="M258" s="11" t="s">
+      <c r="M258" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N258" s="7" t="s">
@@ -18010,7 +18050,7 @@
       <c r="Y258" s="7"/>
       <c r="Z258" s="7"/>
     </row>
-    <row r="259" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>0</v>
       </c>
@@ -18048,7 +18088,7 @@
       <c r="L259" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="M259" s="11" t="s">
+      <c r="M259" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N259" s="7" t="s">
@@ -18067,7 +18107,7 @@
       <c r="Y259" s="7"/>
       <c r="Z259" s="7"/>
     </row>
-    <row r="260" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>0</v>
       </c>
@@ -18105,7 +18145,7 @@
       <c r="L260" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="M260" s="11" t="s">
+      <c r="M260" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N260" s="7" t="s">
@@ -18124,7 +18164,7 @@
       <c r="Y260" s="7"/>
       <c r="Z260" s="7"/>
     </row>
-    <row r="261" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>0</v>
       </c>
@@ -18181,7 +18221,7 @@
       <c r="Y261" s="7"/>
       <c r="Z261" s="7"/>
     </row>
-    <row r="262" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>0</v>
       </c>
@@ -18238,7 +18278,7 @@
       <c r="Y262" s="7"/>
       <c r="Z262" s="7"/>
     </row>
-    <row r="263" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>0</v>
       </c>
@@ -18276,7 +18316,7 @@
       <c r="L263" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M263" s="11" t="s">
+      <c r="M263" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N263" s="7" t="s">
@@ -18295,7 +18335,7 @@
       <c r="Y263" s="7"/>
       <c r="Z263" s="7"/>
     </row>
-    <row r="264" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>0</v>
       </c>
@@ -18333,7 +18373,7 @@
       <c r="L264" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M264" s="11" t="s">
+      <c r="M264" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N264" s="7" t="s">
@@ -18352,7 +18392,7 @@
       <c r="Y264" s="7"/>
       <c r="Z264" s="7"/>
     </row>
-    <row r="265" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>0</v>
       </c>
@@ -18390,7 +18430,7 @@
       <c r="L265" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M265" s="11" t="s">
+      <c r="M265" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N265" s="7" t="s">
@@ -18409,7 +18449,7 @@
       <c r="Y265" s="7"/>
       <c r="Z265" s="7"/>
     </row>
-    <row r="266" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>0</v>
       </c>
@@ -18447,7 +18487,7 @@
       <c r="L266" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M266" s="11" t="s">
+      <c r="M266" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N266" s="7" t="s">
@@ -18466,7 +18506,7 @@
       <c r="Y266" s="7"/>
       <c r="Z266" s="7"/>
     </row>
-    <row r="267" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>0</v>
       </c>
@@ -18504,7 +18544,7 @@
       <c r="L267" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M267" s="11" t="s">
+      <c r="M267" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N267" s="7" t="s">
@@ -18523,7 +18563,7 @@
       <c r="Y267" s="7"/>
       <c r="Z267" s="7"/>
     </row>
-    <row r="268" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>0</v>
       </c>
@@ -18561,7 +18601,7 @@
       <c r="L268" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="M268" s="11" t="s">
+      <c r="M268" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N268" s="7" t="s">
@@ -18580,7 +18620,7 @@
       <c r="Y268" s="7"/>
       <c r="Z268" s="7"/>
     </row>
-    <row r="269" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>0</v>
       </c>
@@ -18618,7 +18658,7 @@
       <c r="L269" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="M269" s="11" t="s">
+      <c r="M269" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N269" s="7" t="s">
@@ -18637,7 +18677,7 @@
       <c r="Y269" s="7"/>
       <c r="Z269" s="7"/>
     </row>
-    <row r="270" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>0</v>
       </c>
@@ -18675,7 +18715,7 @@
       <c r="L270" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="M270" s="11" t="s">
+      <c r="M270" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N270" s="7" t="s">
@@ -18694,7 +18734,7 @@
       <c r="Y270" s="7"/>
       <c r="Z270" s="7"/>
     </row>
-    <row r="271" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>0</v>
       </c>
@@ -18732,7 +18772,7 @@
       <c r="L271" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="M271" s="11" t="s">
+      <c r="M271" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N271" s="7" t="s">
@@ -18751,7 +18791,7 @@
       <c r="Y271" s="7"/>
       <c r="Z271" s="7"/>
     </row>
-    <row r="272" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>0</v>
       </c>
@@ -18789,7 +18829,7 @@
       <c r="L272" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="M272" s="11" t="s">
+      <c r="M272" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N272" s="7" t="s">
@@ -18808,7 +18848,7 @@
       <c r="Y272" s="7"/>
       <c r="Z272" s="7"/>
     </row>
-    <row r="273" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="273" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>0</v>
       </c>
@@ -18846,7 +18886,7 @@
       <c r="L273" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="M273" s="11" t="s">
+      <c r="M273" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N273" s="7" t="s">
@@ -18865,7 +18905,7 @@
       <c r="Y273" s="7"/>
       <c r="Z273" s="7"/>
     </row>
-    <row r="274" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="274" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>0</v>
       </c>
@@ -18903,7 +18943,7 @@
       <c r="L274" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="M274" s="11" t="s">
+      <c r="M274" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N274" s="7" t="s">
@@ -18922,7 +18962,7 @@
       <c r="Y274" s="7"/>
       <c r="Z274" s="7"/>
     </row>
-    <row r="275" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="275" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>0</v>
       </c>
@@ -18960,7 +19000,7 @@
       <c r="L275" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="M275" s="11" t="s">
+      <c r="M275" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N275" s="7" t="s">
@@ -18979,7 +19019,7 @@
       <c r="Y275" s="7"/>
       <c r="Z275" s="7"/>
     </row>
-    <row r="276" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="276" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>0</v>
       </c>
@@ -19017,7 +19057,7 @@
       <c r="L276" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="M276" s="11" t="s">
+      <c r="M276" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N276" s="7" t="s">
@@ -19036,7 +19076,7 @@
       <c r="Y276" s="7"/>
       <c r="Z276" s="7"/>
     </row>
-    <row r="277" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="277" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>0</v>
       </c>
@@ -19074,7 +19114,7 @@
       <c r="L277" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="M277" s="11" t="s">
+      <c r="M277" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N277" s="7" t="s">
@@ -19093,7 +19133,7 @@
       <c r="Y277" s="7"/>
       <c r="Z277" s="7"/>
     </row>
-    <row r="278" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="278" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>0</v>
       </c>
@@ -19150,7 +19190,7 @@
       <c r="Y278" s="7"/>
       <c r="Z278" s="7"/>
     </row>
-    <row r="279" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="279" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>0</v>
       </c>
@@ -19188,7 +19228,7 @@
       <c r="L279" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="M279" s="11" t="s">
+      <c r="M279" s="10" t="s">
         <v>4</v>
       </c>
       <c r="N279" s="7" t="s">
@@ -19207,7 +19247,7 @@
       <c r="Y279" s="7"/>
       <c r="Z279" s="7"/>
     </row>
-    <row r="280" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="280" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>0</v>
       </c>
@@ -19264,7 +19304,7 @@
       <c r="Y280" s="7"/>
       <c r="Z280" s="7"/>
     </row>
-    <row r="281" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="281" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>0</v>
       </c>
@@ -19321,7 +19361,7 @@
       <c r="Y281" s="7"/>
       <c r="Z281" s="7"/>
     </row>
-    <row r="282" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="282" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>0</v>
       </c>
@@ -19378,7 +19418,7 @@
       <c r="Y282" s="7"/>
       <c r="Z282" s="7"/>
     </row>
-    <row r="283" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="283" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>0</v>
       </c>
@@ -19416,7 +19456,7 @@
       <c r="L283" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="M283" s="11" t="s">
+      <c r="M283" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N283" s="7" t="s">
@@ -19435,7 +19475,7 @@
       <c r="Y283" s="7"/>
       <c r="Z283" s="7"/>
     </row>
-    <row r="284" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="284" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>0</v>
       </c>
@@ -19473,7 +19513,7 @@
       <c r="L284" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="M284" s="11" t="s">
+      <c r="M284" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N284" s="7" t="s">
@@ -19492,7 +19532,7 @@
       <c r="Y284" s="7"/>
       <c r="Z284" s="7"/>
     </row>
-    <row r="285" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="285" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>0</v>
       </c>
@@ -19530,7 +19570,7 @@
       <c r="L285" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="M285" s="11" t="s">
+      <c r="M285" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N285" s="7" t="s">
@@ -19549,7 +19589,7 @@
       <c r="Y285" s="7"/>
       <c r="Z285" s="7"/>
     </row>
-    <row r="286" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="286" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
         <v>0</v>
       </c>
@@ -19606,7 +19646,7 @@
       <c r="Y286" s="7"/>
       <c r="Z286" s="7"/>
     </row>
-    <row r="287" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="287" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>0</v>
       </c>
@@ -19644,7 +19684,7 @@
       <c r="L287" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="M287" s="11" t="s">
+      <c r="M287" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N287" s="7" t="s">
@@ -19663,7 +19703,7 @@
       <c r="Y287" s="7"/>
       <c r="Z287" s="7"/>
     </row>
-    <row r="288" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="288" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
         <v>0</v>
       </c>
@@ -19720,7 +19760,7 @@
       <c r="Y288" s="7"/>
       <c r="Z288" s="7"/>
     </row>
-    <row r="289" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="289" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>0</v>
       </c>
@@ -19758,7 +19798,7 @@
       <c r="L289" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="M289" s="11" t="s">
+      <c r="M289" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N289" s="7" t="s">
@@ -19777,7 +19817,7 @@
       <c r="Y289" s="7"/>
       <c r="Z289" s="7"/>
     </row>
-    <row r="290" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="290" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="7" t="s">
         <v>0</v>
       </c>
@@ -19834,7 +19874,7 @@
       <c r="Y290" s="7"/>
       <c r="Z290" s="7"/>
     </row>
-    <row r="291" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="291" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>0</v>
       </c>
@@ -19872,7 +19912,7 @@
       <c r="L291" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="M291" s="11" t="s">
+      <c r="M291" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N291" s="7" t="s">
@@ -19891,7 +19931,7 @@
       <c r="Y291" s="7"/>
       <c r="Z291" s="7"/>
     </row>
-    <row r="292" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="292" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="7" t="s">
         <v>0</v>
       </c>
@@ -19929,7 +19969,7 @@
       <c r="L292" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="M292" s="11" t="s">
+      <c r="M292" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N292" s="7" t="s">
@@ -19948,7 +19988,7 @@
       <c r="Y292" s="7"/>
       <c r="Z292" s="7"/>
     </row>
-    <row r="293" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="293" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>0</v>
       </c>
@@ -19986,7 +20026,7 @@
       <c r="L293" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="M293" s="11" t="s">
+      <c r="M293" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N293" s="7" t="s">
@@ -20005,7 +20045,7 @@
       <c r="Y293" s="7"/>
       <c r="Z293" s="7"/>
     </row>
-    <row r="294" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="294" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
         <v>0</v>
       </c>
@@ -20043,7 +20083,7 @@
       <c r="L294" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="M294" s="11" t="s">
+      <c r="M294" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N294" s="7" t="s">
@@ -20062,7 +20102,7 @@
       <c r="Y294" s="7"/>
       <c r="Z294" s="7"/>
     </row>
-    <row r="295" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="295" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>0</v>
       </c>
@@ -20100,7 +20140,7 @@
       <c r="L295" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="M295" s="11" t="s">
+      <c r="M295" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N295" s="7" t="s">
@@ -20119,7 +20159,7 @@
       <c r="Y295" s="7"/>
       <c r="Z295" s="7"/>
     </row>
-    <row r="296" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="296" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
         <v>0</v>
       </c>
@@ -20157,7 +20197,7 @@
       <c r="L296" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="M296" s="11" t="s">
+      <c r="M296" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N296" s="7" t="s">
@@ -20176,7 +20216,7 @@
       <c r="Y296" s="7"/>
       <c r="Z296" s="7"/>
     </row>
-    <row r="297" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="297" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>0</v>
       </c>
@@ -20214,7 +20254,7 @@
       <c r="L297" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="M297" s="11" t="s">
+      <c r="M297" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N297" s="7" t="s">
@@ -20233,7 +20273,7 @@
       <c r="Y297" s="7"/>
       <c r="Z297" s="7"/>
     </row>
-    <row r="298" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="298" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
         <v>0</v>
       </c>
@@ -20271,7 +20311,7 @@
       <c r="L298" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="M298" s="11" t="s">
+      <c r="M298" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N298" s="7" t="s">
@@ -20290,7 +20330,7 @@
       <c r="Y298" s="7"/>
       <c r="Z298" s="7"/>
     </row>
-    <row r="299" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="299" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>0</v>
       </c>
@@ -20328,7 +20368,7 @@
       <c r="L299" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="M299" s="11" t="s">
+      <c r="M299" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N299" s="7" t="s">
@@ -20347,7 +20387,7 @@
       <c r="Y299" s="7"/>
       <c r="Z299" s="7"/>
     </row>
-    <row r="300" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="300" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="7" t="s">
         <v>0</v>
       </c>
@@ -20385,7 +20425,7 @@
       <c r="L300" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="M300" s="11" t="s">
+      <c r="M300" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N300" s="7" t="s">
@@ -20404,7 +20444,7 @@
       <c r="Y300" s="7"/>
       <c r="Z300" s="7"/>
     </row>
-    <row r="301" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="301" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="7" t="s">
         <v>0</v>
       </c>
@@ -20442,7 +20482,7 @@
       <c r="L301" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="M301" s="11" t="s">
+      <c r="M301" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N301" s="7" t="s">
@@ -20461,7 +20501,7 @@
       <c r="Y301" s="7"/>
       <c r="Z301" s="7"/>
     </row>
-    <row r="302" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="302" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="7" t="s">
         <v>0</v>
       </c>
@@ -20518,7 +20558,7 @@
       <c r="Y302" s="7"/>
       <c r="Z302" s="7"/>
     </row>
-    <row r="303" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="303" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="7" t="s">
         <v>0</v>
       </c>
@@ -20556,7 +20596,7 @@
       <c r="L303" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="M303" s="11" t="s">
+      <c r="M303" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N303" s="7" t="s">
@@ -20575,7 +20615,7 @@
       <c r="Y303" s="7"/>
       <c r="Z303" s="7"/>
     </row>
-    <row r="304" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="304" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="7" t="s">
         <v>0</v>
       </c>
@@ -20632,7 +20672,7 @@
       <c r="Y304" s="7"/>
       <c r="Z304" s="7"/>
     </row>
-    <row r="305" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="305" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="7" t="s">
         <v>0</v>
       </c>
@@ -20689,7 +20729,7 @@
       <c r="Y305" s="7"/>
       <c r="Z305" s="7"/>
     </row>
-    <row r="306" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="306" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="7" t="s">
         <v>0</v>
       </c>
@@ -20746,7 +20786,7 @@
       <c r="Y306" s="7"/>
       <c r="Z306" s="7"/>
     </row>
-    <row r="307" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="307" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="7" t="s">
         <v>0</v>
       </c>
@@ -20803,7 +20843,7 @@
       <c r="Y307" s="7"/>
       <c r="Z307" s="7"/>
     </row>
-    <row r="308" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="308" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="7" t="s">
         <v>0</v>
       </c>
@@ -20860,7 +20900,7 @@
       <c r="Y308" s="7"/>
       <c r="Z308" s="7"/>
     </row>
-    <row r="309" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="309" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="7" t="s">
         <v>0</v>
       </c>
@@ -20917,7 +20957,7 @@
       <c r="Y309" s="7"/>
       <c r="Z309" s="7"/>
     </row>
-    <row r="310" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="310" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="7" t="s">
         <v>0</v>
       </c>
@@ -20955,7 +20995,7 @@
       <c r="L310" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="M310" s="11" t="s">
+      <c r="M310" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N310" s="7" t="s">
@@ -20974,7 +21014,7 @@
       <c r="Y310" s="7"/>
       <c r="Z310" s="7"/>
     </row>
-    <row r="311" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="311" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="7" t="s">
         <v>0</v>
       </c>
@@ -21012,7 +21052,7 @@
       <c r="L311" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="M311" s="11" t="s">
+      <c r="M311" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N311" s="7" t="s">
@@ -21031,7 +21071,7 @@
       <c r="Y311" s="7"/>
       <c r="Z311" s="7"/>
     </row>
-    <row r="312" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="312" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="7" t="s">
         <v>0</v>
       </c>
@@ -21069,7 +21109,7 @@
       <c r="L312" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="M312" s="11" t="s">
+      <c r="M312" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N312" s="7" t="s">
@@ -21088,7 +21128,7 @@
       <c r="Y312" s="7"/>
       <c r="Z312" s="7"/>
     </row>
-    <row r="313" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="313" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="7" t="s">
         <v>0</v>
       </c>
@@ -21126,7 +21166,7 @@
       <c r="L313" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="M313" s="11" t="s">
+      <c r="M313" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N313" s="7" t="s">
@@ -21145,7 +21185,7 @@
       <c r="Y313" s="7"/>
       <c r="Z313" s="7"/>
     </row>
-    <row r="314" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="314" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="7" t="s">
         <v>0</v>
       </c>
@@ -21183,7 +21223,7 @@
       <c r="L314" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="M314" s="11" t="s">
+      <c r="M314" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N314" s="7" t="s">
@@ -21202,7 +21242,7 @@
       <c r="Y314" s="7"/>
       <c r="Z314" s="7"/>
     </row>
-    <row r="315" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="315" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="7" t="s">
         <v>0</v>
       </c>
@@ -21240,7 +21280,7 @@
       <c r="L315" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="M315" s="11" t="s">
+      <c r="M315" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N315" s="7" t="s">
@@ -21259,7 +21299,7 @@
       <c r="Y315" s="7"/>
       <c r="Z315" s="7"/>
     </row>
-    <row r="316" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="316" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="7" t="s">
         <v>0</v>
       </c>
@@ -21297,7 +21337,7 @@
       <c r="L316" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="M316" s="11" t="s">
+      <c r="M316" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N316" s="7" t="s">
@@ -21316,7 +21356,7 @@
       <c r="Y316" s="7"/>
       <c r="Z316" s="7"/>
     </row>
-    <row r="317" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="317" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="7" t="s">
         <v>0</v>
       </c>
@@ -21373,7 +21413,7 @@
       <c r="Y317" s="7"/>
       <c r="Z317" s="7"/>
     </row>
-    <row r="318" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="318" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="7" t="s">
         <v>0</v>
       </c>
@@ -21430,7 +21470,7 @@
       <c r="Y318" s="7"/>
       <c r="Z318" s="7"/>
     </row>
-    <row r="319" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="319" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="7" t="s">
         <v>0</v>
       </c>
@@ -21487,7 +21527,7 @@
       <c r="Y319" s="7"/>
       <c r="Z319" s="7"/>
     </row>
-    <row r="320" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="320" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="7" t="s">
         <v>0</v>
       </c>
@@ -21544,7 +21584,7 @@
       <c r="Y320" s="7"/>
       <c r="Z320" s="7"/>
     </row>
-    <row r="321" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="321" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="7" t="s">
         <v>0</v>
       </c>
@@ -21601,7 +21641,7 @@
       <c r="Y321" s="7"/>
       <c r="Z321" s="7"/>
     </row>
-    <row r="322" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="322" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="7" t="s">
         <v>0</v>
       </c>
@@ -21658,7 +21698,7 @@
       <c r="Y322" s="7"/>
       <c r="Z322" s="7"/>
     </row>
-    <row r="323" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="323" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="7" t="s">
         <v>0</v>
       </c>
@@ -21715,7 +21755,7 @@
       <c r="Y323" s="7"/>
       <c r="Z323" s="7"/>
     </row>
-    <row r="324" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="324" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="7" t="s">
         <v>0</v>
       </c>
@@ -21753,7 +21793,7 @@
       <c r="L324" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="M324" s="11" t="s">
+      <c r="M324" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N324" s="7" t="s">
@@ -21772,7 +21812,7 @@
       <c r="Y324" s="7"/>
       <c r="Z324" s="7"/>
     </row>
-    <row r="325" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="325" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="7" t="s">
         <v>0</v>
       </c>
@@ -21829,7 +21869,7 @@
       <c r="Y325" s="7"/>
       <c r="Z325" s="7"/>
     </row>
-    <row r="326" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="326" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="7" t="s">
         <v>0</v>
       </c>
@@ -21867,7 +21907,7 @@
       <c r="L326" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="M326" s="11" t="s">
+      <c r="M326" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N326" s="7" t="s">
@@ -21886,7 +21926,7 @@
       <c r="Y326" s="7"/>
       <c r="Z326" s="7"/>
     </row>
-    <row r="327" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="327" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="7" t="s">
         <v>0</v>
       </c>
@@ -21943,7 +21983,7 @@
       <c r="Y327" s="7"/>
       <c r="Z327" s="7"/>
     </row>
-    <row r="328" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="328" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="7" t="s">
         <v>0</v>
       </c>
@@ -22000,7 +22040,7 @@
       <c r="Y328" s="7"/>
       <c r="Z328" s="7"/>
     </row>
-    <row r="329" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="329" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="7" t="s">
         <v>0</v>
       </c>
@@ -22057,7 +22097,7 @@
       <c r="Y329" s="7"/>
       <c r="Z329" s="7"/>
     </row>
-    <row r="330" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="330" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="7" t="s">
         <v>0</v>
       </c>
@@ -22095,7 +22135,7 @@
       <c r="L330" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="M330" s="11" t="s">
+      <c r="M330" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N330" s="7" t="s">
@@ -22114,7 +22154,7 @@
       <c r="Y330" s="7"/>
       <c r="Z330" s="7"/>
     </row>
-    <row r="331" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="331" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="7" t="s">
         <v>0</v>
       </c>
@@ -22152,7 +22192,7 @@
       <c r="L331" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="M331" s="11" t="s">
+      <c r="M331" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N331" s="7" t="s">
@@ -22171,7 +22211,7 @@
       <c r="Y331" s="7"/>
       <c r="Z331" s="7"/>
     </row>
-    <row r="332" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="332" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="7" t="s">
         <v>0</v>
       </c>
@@ -22228,7 +22268,7 @@
       <c r="Y332" s="7"/>
       <c r="Z332" s="7"/>
     </row>
-    <row r="333" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="333" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="7" t="s">
         <v>0</v>
       </c>
@@ -22266,7 +22306,7 @@
       <c r="L333" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="M333" s="11" t="s">
+      <c r="M333" s="10" t="s">
         <v>33</v>
       </c>
       <c r="N333" s="7" t="s">
@@ -22285,7 +22325,7 @@
       <c r="Y333" s="7"/>
       <c r="Z333" s="7"/>
     </row>
-    <row r="334" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="334" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="7" t="s">
         <v>0</v>
       </c>
@@ -22342,7 +22382,7 @@
       <c r="Y334" s="7"/>
       <c r="Z334" s="7"/>
     </row>
-    <row r="335" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="335" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="7" t="s">
         <v>0</v>
       </c>
@@ -22380,7 +22420,7 @@
       <c r="L335" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="M335" s="11" t="s">
+      <c r="M335" s="10" t="s">
         <v>41</v>
       </c>
       <c r="N335" s="7" t="s">
@@ -22399,7 +22439,7 @@
       <c r="Y335" s="7"/>
       <c r="Z335" s="7"/>
     </row>
-    <row r="336" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="336" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="7" t="s">
         <v>0</v>
       </c>
@@ -22456,7 +22496,7 @@
       <c r="Y336" s="7"/>
       <c r="Z336" s="7"/>
     </row>
-    <row r="337" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="337" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="7" t="s">
         <v>0</v>
       </c>
@@ -22513,7 +22553,7 @@
       <c r="Y337" s="7"/>
       <c r="Z337" s="7"/>
     </row>
-    <row r="338" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="338" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="7" t="s">
         <v>0</v>
       </c>
@@ -22570,7 +22610,7 @@
       <c r="Y338" s="7"/>
       <c r="Z338" s="7"/>
     </row>
-    <row r="339" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="339" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="7" t="s">
         <v>0</v>
       </c>
@@ -22627,7 +22667,7 @@
       <c r="Y339" s="7"/>
       <c r="Z339" s="7"/>
     </row>
-    <row r="340" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="340" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="7" t="s">
         <v>0</v>
       </c>
@@ -22684,7 +22724,7 @@
       <c r="Y340" s="7"/>
       <c r="Z340" s="7"/>
     </row>
-    <row r="341" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="341" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="7" t="s">
         <v>0</v>
       </c>
@@ -22741,7 +22781,7 @@
       <c r="Y341" s="7"/>
       <c r="Z341" s="7"/>
     </row>
-    <row r="342" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="342" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="7" t="s">
         <v>0</v>
       </c>
@@ -22798,7 +22838,7 @@
       <c r="Y342" s="7"/>
       <c r="Z342" s="7"/>
     </row>
-    <row r="343" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="343" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="7" t="s">
         <v>0</v>
       </c>
@@ -22855,7 +22895,7 @@
       <c r="Y343" s="7"/>
       <c r="Z343" s="7"/>
     </row>
-    <row r="344" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="344" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="7" t="s">
         <v>0</v>
       </c>
@@ -22912,7 +22952,7 @@
       <c r="Y344" s="7"/>
       <c r="Z344" s="7"/>
     </row>
-    <row r="345" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="345" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="7" t="s">
         <v>0</v>
       </c>
@@ -22969,7 +23009,7 @@
       <c r="Y345" s="7"/>
       <c r="Z345" s="7"/>
     </row>
-    <row r="346" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="346" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="7" t="s">
         <v>0</v>
       </c>
@@ -23026,7 +23066,7 @@
       <c r="Y346" s="7"/>
       <c r="Z346" s="7"/>
     </row>
-    <row r="347" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="347" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="7" t="s">
         <v>0</v>
       </c>
@@ -23083,7 +23123,7 @@
       <c r="Y347" s="7"/>
       <c r="Z347" s="7"/>
     </row>
-    <row r="348" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="348" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="7" t="s">
         <v>0</v>
       </c>
@@ -23140,7 +23180,7 @@
       <c r="Y348" s="7"/>
       <c r="Z348" s="7"/>
     </row>
-    <row r="349" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="349" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="7" t="s">
         <v>0</v>
       </c>
@@ -23197,7 +23237,7 @@
       <c r="Y349" s="7"/>
       <c r="Z349" s="7"/>
     </row>
-    <row r="350" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="350" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="7" t="s">
         <v>0</v>
       </c>
@@ -23254,7 +23294,7 @@
       <c r="Y350" s="7"/>
       <c r="Z350" s="7"/>
     </row>
-    <row r="351" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="351" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="7" t="s">
         <v>0</v>
       </c>
@@ -23311,7 +23351,7 @@
       <c r="Y351" s="7"/>
       <c r="Z351" s="7"/>
     </row>
-    <row r="352" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="352" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="7" t="s">
         <v>0</v>
       </c>
@@ -23368,7 +23408,7 @@
       <c r="Y352" s="7"/>
       <c r="Z352" s="7"/>
     </row>
-    <row r="353" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="353" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="7" t="s">
         <v>0</v>
       </c>
@@ -23425,7 +23465,7 @@
       <c r="Y353" s="7"/>
       <c r="Z353" s="7"/>
     </row>
-    <row r="354" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="354" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="7" t="s">
         <v>0</v>
       </c>
@@ -23482,7 +23522,7 @@
       <c r="Y354" s="7"/>
       <c r="Z354" s="7"/>
     </row>
-    <row r="355" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="355" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="7" t="s">
         <v>0</v>
       </c>
@@ -23539,7 +23579,7 @@
       <c r="Y355" s="7"/>
       <c r="Z355" s="7"/>
     </row>
-    <row r="356" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="356" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="7" t="s">
         <v>0</v>
       </c>
@@ -23596,7 +23636,7 @@
       <c r="Y356" s="7"/>
       <c r="Z356" s="7"/>
     </row>
-    <row r="357" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="357" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="7" t="s">
         <v>0</v>
       </c>
@@ -23653,7 +23693,7 @@
       <c r="Y357" s="7"/>
       <c r="Z357" s="7"/>
     </row>
-    <row r="358" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="358" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="7" t="s">
         <v>0</v>
       </c>
@@ -23710,7 +23750,7 @@
       <c r="Y358" s="7"/>
       <c r="Z358" s="7"/>
     </row>
-    <row r="359" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="359" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="7" t="s">
         <v>0</v>
       </c>
@@ -23767,7 +23807,7 @@
       <c r="Y359" s="7"/>
       <c r="Z359" s="7"/>
     </row>
-    <row r="360" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="360" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="7" t="s">
         <v>0</v>
       </c>
@@ -23783,10 +23823,10 @@
       <c r="E360" s="7">
         <v>39760003</v>
       </c>
-      <c r="F360" s="12">
+      <c r="F360" s="11">
         <v>2025</v>
       </c>
-      <c r="G360" s="12">
+      <c r="G360" s="11">
         <v>9478930</v>
       </c>
       <c r="H360" s="7" t="s">
@@ -23824,7 +23864,7 @@
       <c r="Y360" s="7"/>
       <c r="Z360" s="7"/>
     </row>
-    <row r="361" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="361" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="7" t="s">
         <v>0</v>
       </c>
@@ -23840,10 +23880,10 @@
       <c r="E361" s="7">
         <v>39760003</v>
       </c>
-      <c r="F361" s="12">
+      <c r="F361" s="11">
         <v>2025</v>
       </c>
-      <c r="G361" s="12">
+      <c r="G361" s="11">
         <v>9479195</v>
       </c>
       <c r="H361" s="7" t="s">
@@ -23881,7 +23921,7 @@
       <c r="Y361" s="7"/>
       <c r="Z361" s="7"/>
     </row>
-    <row r="362" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="362" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="7" t="s">
         <v>0</v>
       </c>
@@ -23938,7 +23978,7 @@
       <c r="Y362" s="7"/>
       <c r="Z362" s="7"/>
     </row>
-    <row r="363" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="363" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="7" t="s">
         <v>0</v>
       </c>
@@ -23995,7 +24035,7 @@
       <c r="Y363" s="7"/>
       <c r="Z363" s="7"/>
     </row>
-    <row r="364" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="364" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="7" t="s">
         <v>0</v>
       </c>
@@ -24052,7 +24092,7 @@
       <c r="Y364" s="7"/>
       <c r="Z364" s="7"/>
     </row>
-    <row r="365" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="365" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="7" t="s">
         <v>0</v>
       </c>
@@ -24109,7 +24149,7 @@
       <c r="Y365" s="7"/>
       <c r="Z365" s="7"/>
     </row>
-    <row r="366" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="366" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="7" t="s">
         <v>0</v>
       </c>
@@ -24166,7 +24206,7 @@
       <c r="Y366" s="7"/>
       <c r="Z366" s="7"/>
     </row>
-    <row r="367" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="367" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="7" t="s">
         <v>0</v>
       </c>
@@ -24223,7 +24263,7 @@
       <c r="Y367" s="7"/>
       <c r="Z367" s="7"/>
     </row>
-    <row r="368" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="368" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="7" t="s">
         <v>0</v>
       </c>
@@ -24280,7 +24320,7 @@
       <c r="Y368" s="7"/>
       <c r="Z368" s="7"/>
     </row>
-    <row r="369" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="369" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="7" t="s">
         <v>0</v>
       </c>
@@ -24337,7 +24377,7 @@
       <c r="Y369" s="7"/>
       <c r="Z369" s="7"/>
     </row>
-    <row r="370" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="370" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="7" t="s">
         <v>0</v>
       </c>
@@ -24394,7 +24434,7 @@
       <c r="Y370" s="7"/>
       <c r="Z370" s="7"/>
     </row>
-    <row r="371" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="371" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="7" t="s">
         <v>0</v>
       </c>
@@ -24451,7 +24491,7 @@
       <c r="Y371" s="7"/>
       <c r="Z371" s="7"/>
     </row>
-    <row r="372" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="372" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="7" t="s">
         <v>0</v>
       </c>
@@ -24508,7 +24548,7 @@
       <c r="Y372" s="7"/>
       <c r="Z372" s="7"/>
     </row>
-    <row r="373" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="373" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="7" t="s">
         <v>0</v>
       </c>
@@ -24565,7 +24605,7 @@
       <c r="Y373" s="7"/>
       <c r="Z373" s="7"/>
     </row>
-    <row r="374" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="374" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="7" t="s">
         <v>0</v>
       </c>
@@ -24622,7 +24662,7 @@
       <c r="Y374" s="7"/>
       <c r="Z374" s="7"/>
     </row>
-    <row r="375" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="375" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="7" t="s">
         <v>0</v>
       </c>
@@ -24679,7 +24719,7 @@
       <c r="Y375" s="7"/>
       <c r="Z375" s="7"/>
     </row>
-    <row r="376" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="376" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="7" t="s">
         <v>0</v>
       </c>
@@ -24736,7 +24776,7 @@
       <c r="Y376" s="7"/>
       <c r="Z376" s="7"/>
     </row>
-    <row r="377" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="377" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="7" t="s">
         <v>0</v>
       </c>
@@ -24793,7 +24833,7 @@
       <c r="Y377" s="7"/>
       <c r="Z377" s="7"/>
     </row>
-    <row r="378" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="378" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="7" t="s">
         <v>0</v>
       </c>
@@ -24850,7 +24890,7 @@
       <c r="Y378" s="7"/>
       <c r="Z378" s="7"/>
     </row>
-    <row r="379" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="379" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="7" t="s">
         <v>0</v>
       </c>
@@ -24907,7 +24947,7 @@
       <c r="Y379" s="7"/>
       <c r="Z379" s="7"/>
     </row>
-    <row r="380" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="380" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="7" t="s">
         <v>0</v>
       </c>
@@ -24964,7 +25004,7 @@
       <c r="Y380" s="7"/>
       <c r="Z380" s="7"/>
     </row>
-    <row r="381" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="381" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="7" t="s">
         <v>0</v>
       </c>
@@ -25021,7 +25061,7 @@
       <c r="Y381" s="7"/>
       <c r="Z381" s="7"/>
     </row>
-    <row r="382" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="382" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="7" t="s">
         <v>0</v>
       </c>
@@ -25078,7 +25118,7 @@
       <c r="Y382" s="7"/>
       <c r="Z382" s="7"/>
     </row>
-    <row r="383" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="383" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="7" t="s">
         <v>0</v>
       </c>
@@ -25135,7 +25175,7 @@
       <c r="Y383" s="7"/>
       <c r="Z383" s="7"/>
     </row>
-    <row r="384" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="384" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="7" t="s">
         <v>0</v>
       </c>
@@ -25192,7 +25232,7 @@
       <c r="Y384" s="7"/>
       <c r="Z384" s="7"/>
     </row>
-    <row r="385" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="385" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="7" t="s">
         <v>0</v>
       </c>
@@ -25249,7 +25289,7 @@
       <c r="Y385" s="7"/>
       <c r="Z385" s="7"/>
     </row>
-    <row r="386" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="386" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="7" t="s">
         <v>0</v>
       </c>
@@ -25306,7 +25346,7 @@
       <c r="Y386" s="7"/>
       <c r="Z386" s="7"/>
     </row>
-    <row r="387" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="387" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="7" t="s">
         <v>0</v>
       </c>
@@ -25363,7 +25403,7 @@
       <c r="Y387" s="7"/>
       <c r="Z387" s="7"/>
     </row>
-    <row r="388" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="388" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="7" t="s">
         <v>0</v>
       </c>
@@ -25420,7 +25460,7 @@
       <c r="Y388" s="7"/>
       <c r="Z388" s="7"/>
     </row>
-    <row r="389" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="389" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="7" t="s">
         <v>0</v>
       </c>
@@ -25477,7 +25517,7 @@
       <c r="Y389" s="7"/>
       <c r="Z389" s="7"/>
     </row>
-    <row r="390" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="390" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="7" t="s">
         <v>0</v>
       </c>
@@ -25534,7 +25574,7 @@
       <c r="Y390" s="7"/>
       <c r="Z390" s="7"/>
     </row>
-    <row r="391" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="391" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="7" t="s">
         <v>0</v>
       </c>
@@ -25591,7 +25631,7 @@
       <c r="Y391" s="7"/>
       <c r="Z391" s="7"/>
     </row>
-    <row r="392" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="392" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="7" t="s">
         <v>0</v>
       </c>
@@ -25648,7 +25688,7 @@
       <c r="Y392" s="7"/>
       <c r="Z392" s="7"/>
     </row>
-    <row r="393" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="393" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="7" t="s">
         <v>0</v>
       </c>
@@ -25705,7 +25745,7 @@
       <c r="Y393" s="7"/>
       <c r="Z393" s="7"/>
     </row>
-    <row r="394" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="394" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="7" t="s">
         <v>0</v>
       </c>
@@ -25762,7 +25802,7 @@
       <c r="Y394" s="7"/>
       <c r="Z394" s="7"/>
     </row>
-    <row r="395" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="395" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="7" t="s">
         <v>0</v>
       </c>
@@ -25819,7 +25859,7 @@
       <c r="Y395" s="7"/>
       <c r="Z395" s="7"/>
     </row>
-    <row r="396" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="396" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="7" t="s">
         <v>0</v>
       </c>
@@ -25876,7 +25916,7 @@
       <c r="Y396" s="7"/>
       <c r="Z396" s="7"/>
     </row>
-    <row r="397" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="397" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="7" t="s">
         <v>0</v>
       </c>
@@ -25933,7 +25973,7 @@
       <c r="Y397" s="7"/>
       <c r="Z397" s="7"/>
     </row>
-    <row r="398" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="398" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="7" t="s">
         <v>0</v>
       </c>
@@ -25990,7 +26030,7 @@
       <c r="Y398" s="7"/>
       <c r="Z398" s="7"/>
     </row>
-    <row r="399" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="399" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="7" t="s">
         <v>0</v>
       </c>
@@ -26047,7 +26087,7 @@
       <c r="Y399" s="7"/>
       <c r="Z399" s="7"/>
     </row>
-    <row r="400" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="400" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="7" t="s">
         <v>0</v>
       </c>
@@ -26104,7 +26144,7 @@
       <c r="Y400" s="7"/>
       <c r="Z400" s="7"/>
     </row>
-    <row r="401" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="401" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="7" t="s">
         <v>0</v>
       </c>
@@ -26161,7 +26201,7 @@
       <c r="Y401" s="7"/>
       <c r="Z401" s="7"/>
     </row>
-    <row r="402" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="402" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="7" t="s">
         <v>0</v>
       </c>
@@ -26218,7 +26258,7 @@
       <c r="Y402" s="7"/>
       <c r="Z402" s="7"/>
     </row>
-    <row r="403" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="403" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="7" t="s">
         <v>0</v>
       </c>
@@ -26275,7 +26315,7 @@
       <c r="Y403" s="7"/>
       <c r="Z403" s="7"/>
     </row>
-    <row r="404" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="404" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="7" t="s">
         <v>0</v>
       </c>
@@ -26332,7 +26372,7 @@
       <c r="Y404" s="7"/>
       <c r="Z404" s="7"/>
     </row>
-    <row r="405" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="405" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="7" t="s">
         <v>0</v>
       </c>
@@ -26389,7 +26429,7 @@
       <c r="Y405" s="7"/>
       <c r="Z405" s="7"/>
     </row>
-    <row r="406" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="406" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="7" t="s">
         <v>0</v>
       </c>
@@ -26446,7 +26486,7 @@
       <c r="Y406" s="7"/>
       <c r="Z406" s="7"/>
     </row>
-    <row r="407" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="407" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="7" t="s">
         <v>0</v>
       </c>
@@ -26503,7 +26543,7 @@
       <c r="Y407" s="7"/>
       <c r="Z407" s="7"/>
     </row>
-    <row r="408" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="408" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="7" t="s">
         <v>0</v>
       </c>
@@ -26560,7 +26600,7 @@
       <c r="Y408" s="7"/>
       <c r="Z408" s="7"/>
     </row>
-    <row r="409" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="409" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="7" t="s">
         <v>0</v>
       </c>
@@ -26617,7 +26657,7 @@
       <c r="Y409" s="7"/>
       <c r="Z409" s="7"/>
     </row>
-    <row r="410" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="410" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="7" t="s">
         <v>0</v>
       </c>
@@ -26674,7 +26714,7 @@
       <c r="Y410" s="7"/>
       <c r="Z410" s="7"/>
     </row>
-    <row r="411" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="411" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="7" t="s">
         <v>0</v>
       </c>
@@ -26731,7 +26771,7 @@
       <c r="Y411" s="7"/>
       <c r="Z411" s="7"/>
     </row>
-    <row r="412" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="412" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="7" t="s">
         <v>0</v>
       </c>
@@ -26788,7 +26828,7 @@
       <c r="Y412" s="7"/>
       <c r="Z412" s="7"/>
     </row>
-    <row r="413" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="413" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="7" t="s">
         <v>0</v>
       </c>
@@ -26845,7 +26885,7 @@
       <c r="Y413" s="7"/>
       <c r="Z413" s="7"/>
     </row>
-    <row r="414" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="414" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="7" t="s">
         <v>0</v>
       </c>
@@ -26902,7 +26942,7 @@
       <c r="Y414" s="7"/>
       <c r="Z414" s="7"/>
     </row>
-    <row r="415" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="415" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="7" t="s">
         <v>0</v>
       </c>
@@ -26959,7 +26999,7 @@
       <c r="Y415" s="7"/>
       <c r="Z415" s="7"/>
     </row>
-    <row r="416" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="416" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="7" t="s">
         <v>0</v>
       </c>
@@ -27016,7 +27056,7 @@
       <c r="Y416" s="7"/>
       <c r="Z416" s="7"/>
     </row>
-    <row r="417" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="417" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="7" t="s">
         <v>0</v>
       </c>
@@ -27073,7 +27113,7 @@
       <c r="Y417" s="7"/>
       <c r="Z417" s="7"/>
     </row>
-    <row r="418" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="418" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="7" t="s">
         <v>0</v>
       </c>
@@ -27102,7 +27142,7 @@
         <v>285858.40000000002</v>
       </c>
       <c r="J418" s="8">
-        <v>0</v>
+        <v>285858.40000000002</v>
       </c>
       <c r="K418" s="8"/>
       <c r="L418" s="7" t="s">
@@ -27127,7 +27167,7 @@
       <c r="Y418" s="7"/>
       <c r="Z418" s="7"/>
     </row>
-    <row r="419" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="419" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="7" t="s">
         <v>0</v>
       </c>
@@ -27181,7 +27221,7 @@
       <c r="Y419" s="7"/>
       <c r="Z419" s="7"/>
     </row>
-    <row r="420" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="420" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="7" t="s">
         <v>0</v>
       </c>
@@ -27235,7 +27275,7 @@
       <c r="Y420" s="7"/>
       <c r="Z420" s="7"/>
     </row>
-    <row r="421" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="421" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="7" t="s">
         <v>0</v>
       </c>
@@ -27289,7 +27329,7 @@
       <c r="Y421" s="7"/>
       <c r="Z421" s="7"/>
     </row>
-    <row r="422" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="422" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="7" t="s">
         <v>0</v>
       </c>
@@ -27343,7 +27383,7 @@
       <c r="Y422" s="7"/>
       <c r="Z422" s="7"/>
     </row>
-    <row r="423" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="423" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="7" t="s">
         <v>0</v>
       </c>
@@ -27397,7 +27437,7 @@
       <c r="Y423" s="7"/>
       <c r="Z423" s="7"/>
     </row>
-    <row r="424" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="424" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="7" t="s">
         <v>0</v>
       </c>
@@ -27451,7 +27491,7 @@
       <c r="Y424" s="7"/>
       <c r="Z424" s="7"/>
     </row>
-    <row r="425" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="425" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="7" t="s">
         <v>0</v>
       </c>
@@ -27505,7 +27545,7 @@
       <c r="Y425" s="7"/>
       <c r="Z425" s="7"/>
     </row>
-    <row r="426" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="426" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="7" t="s">
         <v>0</v>
       </c>
@@ -27559,7 +27599,7 @@
       <c r="Y426" s="7"/>
       <c r="Z426" s="7"/>
     </row>
-    <row r="427" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1">
+    <row r="427" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="7" t="s">
         <v>0</v>
       </c>
@@ -27613,119 +27653,223 @@
       <c r="Y427" s="7"/>
       <c r="Z427" s="7"/>
     </row>
-    <row r="428" spans="1:26" ht="15">
-      <c r="A428" s="3"/>
-      <c r="B428" s="6"/>
-      <c r="C428" s="3"/>
-      <c r="D428" s="3"/>
-      <c r="E428" s="3"/>
-      <c r="F428" s="3"/>
-      <c r="G428" s="3"/>
-      <c r="H428" s="3"/>
-      <c r="I428" s="4"/>
-      <c r="J428" s="4"/>
-      <c r="K428" s="4"/>
-      <c r="L428" s="3"/>
-      <c r="M428" s="5"/>
-      <c r="N428" s="3"/>
-      <c r="O428" s="3"/>
-      <c r="P428" s="3"/>
-      <c r="Q428" s="3"/>
-      <c r="R428" s="3"/>
-      <c r="S428" s="3"/>
-      <c r="T428" s="3"/>
-      <c r="U428" s="3"/>
-      <c r="V428" s="3"/>
-      <c r="W428" s="3"/>
-      <c r="X428" s="3"/>
-      <c r="Y428" s="3"/>
-      <c r="Z428" s="3"/>
-    </row>
-    <row r="429" spans="1:26" ht="15">
-      <c r="A429" s="3"/>
-      <c r="B429" s="6"/>
-      <c r="C429" s="3"/>
-      <c r="D429" s="3"/>
-      <c r="E429" s="3"/>
-      <c r="F429" s="3"/>
-      <c r="G429" s="3"/>
-      <c r="H429" s="3"/>
-      <c r="I429" s="4"/>
-      <c r="J429" s="4"/>
-      <c r="K429" s="4"/>
-      <c r="L429" s="3"/>
-      <c r="M429" s="5"/>
-      <c r="N429" s="3"/>
-      <c r="O429" s="3"/>
-      <c r="P429" s="3"/>
-      <c r="Q429" s="3"/>
-      <c r="R429" s="3"/>
-      <c r="S429" s="3"/>
-      <c r="T429" s="3"/>
-      <c r="U429" s="3"/>
-      <c r="V429" s="3"/>
-      <c r="W429" s="3"/>
-      <c r="X429" s="3"/>
-      <c r="Y429" s="3"/>
-      <c r="Z429" s="3"/>
-    </row>
-    <row r="430" spans="1:26" ht="15">
-      <c r="A430" s="3"/>
-      <c r="B430" s="6"/>
-      <c r="C430" s="3"/>
-      <c r="D430" s="3"/>
-      <c r="E430" s="3"/>
-      <c r="F430" s="3"/>
-      <c r="G430" s="3"/>
-      <c r="H430" s="3"/>
-      <c r="I430" s="4"/>
-      <c r="J430" s="4"/>
-      <c r="K430" s="4"/>
-      <c r="L430" s="3"/>
-      <c r="M430" s="5"/>
-      <c r="N430" s="3"/>
-      <c r="O430" s="3"/>
-      <c r="P430" s="3"/>
-      <c r="Q430" s="3"/>
-      <c r="R430" s="3"/>
-      <c r="S430" s="3"/>
-      <c r="T430" s="3"/>
-      <c r="U430" s="3"/>
-      <c r="V430" s="3"/>
-      <c r="W430" s="3"/>
-      <c r="X430" s="3"/>
-      <c r="Y430" s="3"/>
-      <c r="Z430" s="3"/>
-    </row>
-    <row r="431" spans="1:26" ht="15">
-      <c r="A431" s="3"/>
-      <c r="B431" s="6"/>
-      <c r="C431" s="3"/>
-      <c r="D431" s="3"/>
-      <c r="E431" s="3"/>
-      <c r="F431" s="3"/>
-      <c r="G431" s="3"/>
-      <c r="H431" s="3"/>
-      <c r="I431" s="4"/>
-      <c r="J431" s="4"/>
-      <c r="K431" s="4"/>
-      <c r="L431" s="3"/>
-      <c r="M431" s="5"/>
-      <c r="N431" s="3"/>
-      <c r="O431" s="3"/>
-      <c r="P431" s="3"/>
-      <c r="Q431" s="3"/>
-      <c r="R431" s="3"/>
-      <c r="S431" s="3"/>
-      <c r="T431" s="3"/>
-      <c r="U431" s="3"/>
-      <c r="V431" s="3"/>
-      <c r="W431" s="3"/>
-      <c r="X431" s="3"/>
-      <c r="Y431" s="3"/>
-      <c r="Z431" s="3"/>
-    </row>
-    <row r="432" spans="1:26" ht="15">
+    <row r="428" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A428" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E428" s="7">
+        <v>37310006</v>
+      </c>
+      <c r="F428" s="7">
+        <v>2024</v>
+      </c>
+      <c r="G428" s="7">
+        <v>9447765</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="I428" s="8">
+        <v>257850</v>
+      </c>
+      <c r="J428" s="8">
+        <v>0</v>
+      </c>
+      <c r="K428" s="8"/>
+      <c r="L428" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="M428" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N428" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="O428" s="7"/>
+      <c r="P428" s="7"/>
+      <c r="Q428" s="7"/>
+      <c r="R428" s="7"/>
+      <c r="S428" s="7"/>
+      <c r="T428" s="7"/>
+      <c r="U428" s="7"/>
+      <c r="V428" s="7"/>
+      <c r="W428" s="7"/>
+      <c r="X428" s="7"/>
+      <c r="Y428" s="7"/>
+      <c r="Z428" s="7"/>
+    </row>
+    <row r="429" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E429" s="7">
+        <v>27690006</v>
+      </c>
+      <c r="F429" s="7">
+        <v>2024</v>
+      </c>
+      <c r="G429" s="7">
+        <v>9447767</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="I429" s="8">
+        <v>286500</v>
+      </c>
+      <c r="J429" s="8">
+        <v>0</v>
+      </c>
+      <c r="K429" s="8"/>
+      <c r="L429" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="M429" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N429" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="O429" s="7"/>
+      <c r="P429" s="7"/>
+      <c r="Q429" s="7"/>
+      <c r="R429" s="7"/>
+      <c r="S429" s="7"/>
+      <c r="T429" s="7"/>
+      <c r="U429" s="7"/>
+      <c r="V429" s="7"/>
+      <c r="W429" s="7"/>
+      <c r="X429" s="7"/>
+      <c r="Y429" s="7"/>
+      <c r="Z429" s="7"/>
+    </row>
+    <row r="430" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E430" s="7">
+        <v>71140007</v>
+      </c>
+      <c r="F430" s="7">
+        <v>2024</v>
+      </c>
+      <c r="G430" s="7">
+        <v>9447766</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="I430" s="8">
+        <v>6380409</v>
+      </c>
+      <c r="J430" s="8">
+        <v>0</v>
+      </c>
+      <c r="K430" s="8"/>
+      <c r="L430" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="M430" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N430" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="O430" s="7"/>
+      <c r="P430" s="7"/>
+      <c r="Q430" s="7"/>
+      <c r="R430" s="7"/>
+      <c r="S430" s="7"/>
+      <c r="T430" s="7"/>
+      <c r="U430" s="7"/>
+      <c r="V430" s="7"/>
+      <c r="W430" s="7"/>
+      <c r="X430" s="7"/>
+      <c r="Y430" s="7"/>
+      <c r="Z430" s="7"/>
+    </row>
+    <row r="431" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D431" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E431" s="7">
+        <v>44460021</v>
+      </c>
+      <c r="F431" s="7">
+        <v>2025</v>
+      </c>
+      <c r="G431" s="7">
+        <v>9501837</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="I431" s="8">
+        <v>595840</v>
+      </c>
+      <c r="J431" s="8">
+        <v>0</v>
+      </c>
+      <c r="K431" s="8"/>
+      <c r="L431" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="M431" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N431" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O431" s="7"/>
+      <c r="P431" s="7"/>
+      <c r="Q431" s="7"/>
+      <c r="R431" s="7"/>
+      <c r="S431" s="7"/>
+      <c r="T431" s="7"/>
+      <c r="U431" s="7"/>
+      <c r="V431" s="7"/>
+      <c r="W431" s="7"/>
+      <c r="X431" s="7"/>
+      <c r="Y431" s="7"/>
+      <c r="Z431" s="7"/>
+    </row>
+    <row r="432" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A432" s="3"/>
       <c r="B432" s="6"/>
       <c r="C432" s="3"/>
@@ -27753,7 +27897,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="3"/>
     </row>
-    <row r="433" spans="1:26" ht="15">
+    <row r="433" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A433" s="3"/>
       <c r="B433" s="6"/>
       <c r="C433" s="3"/>
@@ -27781,7 +27925,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="3"/>
     </row>
-    <row r="434" spans="1:26" ht="15">
+    <row r="434" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="6"/>
       <c r="C434" s="3"/>
@@ -27809,7 +27953,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="3"/>
     </row>
-    <row r="435" spans="1:26" ht="15">
+    <row r="435" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A435" s="3"/>
       <c r="B435" s="6"/>
       <c r="C435" s="3"/>
@@ -27837,7 +27981,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="3"/>
     </row>
-    <row r="436" spans="1:26" ht="15">
+    <row r="436" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A436" s="3"/>
       <c r="B436" s="6"/>
       <c r="C436" s="3"/>
@@ -27865,7 +28009,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="3"/>
     </row>
-    <row r="437" spans="1:26" ht="15">
+    <row r="437" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A437" s="3"/>
       <c r="B437" s="6"/>
       <c r="C437" s="3"/>
@@ -27893,7 +28037,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="3"/>
     </row>
-    <row r="438" spans="1:26" ht="15">
+    <row r="438" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A438" s="3"/>
       <c r="B438" s="6"/>
       <c r="C438" s="3"/>
@@ -27921,7 +28065,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="3"/>
     </row>
-    <row r="439" spans="1:26" ht="15">
+    <row r="439" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A439" s="3"/>
       <c r="B439" s="6"/>
       <c r="C439" s="3"/>
@@ -27949,7 +28093,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="3"/>
     </row>
-    <row r="440" spans="1:26" ht="15">
+    <row r="440" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A440" s="3"/>
       <c r="B440" s="6"/>
       <c r="C440" s="3"/>
@@ -27977,7 +28121,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="3"/>
     </row>
-    <row r="441" spans="1:26" ht="15">
+    <row r="441" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A441" s="3"/>
       <c r="B441" s="6"/>
       <c r="C441" s="3"/>
@@ -28005,7 +28149,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="3"/>
     </row>
-    <row r="442" spans="1:26" ht="15">
+    <row r="442" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A442" s="3"/>
       <c r="B442" s="6"/>
       <c r="C442" s="3"/>
@@ -28033,7 +28177,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="3"/>
     </row>
-    <row r="443" spans="1:26" ht="15">
+    <row r="443" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A443" s="3"/>
       <c r="B443" s="6"/>
       <c r="C443" s="3"/>
@@ -28061,7 +28205,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="3"/>
     </row>
-    <row r="444" spans="1:26" ht="15">
+    <row r="444" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A444" s="3"/>
       <c r="B444" s="6"/>
       <c r="C444" s="3"/>
@@ -28089,7 +28233,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="3"/>
     </row>
-    <row r="445" spans="1:26" ht="15">
+    <row r="445" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A445" s="3"/>
       <c r="B445" s="6"/>
       <c r="C445" s="3"/>
@@ -28117,7 +28261,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="3"/>
     </row>
-    <row r="446" spans="1:26" ht="15">
+    <row r="446" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A446" s="3"/>
       <c r="B446" s="6"/>
       <c r="C446" s="3"/>
@@ -28145,7 +28289,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="3"/>
     </row>
-    <row r="447" spans="1:26" ht="15">
+    <row r="447" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A447" s="3"/>
       <c r="B447" s="6"/>
       <c r="C447" s="3"/>
@@ -28173,7 +28317,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="3"/>
     </row>
-    <row r="448" spans="1:26" ht="15">
+    <row r="448" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A448" s="3"/>
       <c r="B448" s="6"/>
       <c r="C448" s="3"/>
@@ -28201,7 +28345,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="3"/>
     </row>
-    <row r="449" spans="1:26" ht="15">
+    <row r="449" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A449" s="3"/>
       <c r="B449" s="6"/>
       <c r="C449" s="3"/>
@@ -28229,7 +28373,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="3"/>
     </row>
-    <row r="450" spans="1:26" ht="15">
+    <row r="450" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A450" s="3"/>
       <c r="B450" s="6"/>
       <c r="C450" s="3"/>
@@ -28257,7 +28401,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="3"/>
     </row>
-    <row r="451" spans="1:26" ht="15">
+    <row r="451" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A451" s="3"/>
       <c r="B451" s="6"/>
       <c r="C451" s="3"/>
@@ -28285,7 +28429,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="3"/>
     </row>
-    <row r="452" spans="1:26" ht="15">
+    <row r="452" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A452" s="3"/>
       <c r="B452" s="6"/>
       <c r="C452" s="3"/>
@@ -28313,7 +28457,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="3"/>
     </row>
-    <row r="453" spans="1:26" ht="15">
+    <row r="453" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A453" s="3"/>
       <c r="B453" s="6"/>
       <c r="C453" s="3"/>
@@ -28341,7 +28485,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="3"/>
     </row>
-    <row r="454" spans="1:26" ht="15">
+    <row r="454" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A454" s="3"/>
       <c r="B454" s="6"/>
       <c r="C454" s="3"/>
@@ -28369,7 +28513,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="3"/>
     </row>
-    <row r="455" spans="1:26" ht="15">
+    <row r="455" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A455" s="3"/>
       <c r="B455" s="6"/>
       <c r="C455" s="3"/>
@@ -28397,7 +28541,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="3"/>
     </row>
-    <row r="456" spans="1:26" ht="15">
+    <row r="456" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A456" s="3"/>
       <c r="B456" s="6"/>
       <c r="C456" s="3"/>
@@ -28425,7 +28569,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="3"/>
     </row>
-    <row r="457" spans="1:26" ht="15">
+    <row r="457" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A457" s="3"/>
       <c r="B457" s="6"/>
       <c r="C457" s="3"/>
@@ -28453,7 +28597,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="3"/>
     </row>
-    <row r="458" spans="1:26" ht="15">
+    <row r="458" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A458" s="3"/>
       <c r="B458" s="6"/>
       <c r="C458" s="3"/>
@@ -28481,7 +28625,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="3"/>
     </row>
-    <row r="459" spans="1:26" ht="15">
+    <row r="459" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A459" s="3"/>
       <c r="B459" s="6"/>
       <c r="C459" s="3"/>
@@ -28509,7 +28653,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="3"/>
     </row>
-    <row r="460" spans="1:26" ht="15">
+    <row r="460" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A460" s="3"/>
       <c r="B460" s="6"/>
       <c r="C460" s="3"/>
@@ -28537,7 +28681,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="3"/>
     </row>
-    <row r="461" spans="1:26" ht="15">
+    <row r="461" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A461" s="3"/>
       <c r="B461" s="6"/>
       <c r="C461" s="3"/>
@@ -28565,7 +28709,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="3"/>
     </row>
-    <row r="462" spans="1:26" ht="15">
+    <row r="462" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A462" s="3"/>
       <c r="B462" s="6"/>
       <c r="C462" s="3"/>
@@ -28593,7 +28737,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="3"/>
     </row>
-    <row r="463" spans="1:26" ht="15">
+    <row r="463" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A463" s="3"/>
       <c r="B463" s="6"/>
       <c r="C463" s="3"/>
@@ -28621,7 +28765,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="3"/>
     </row>
-    <row r="464" spans="1:26" ht="15">
+    <row r="464" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A464" s="3"/>
       <c r="B464" s="6"/>
       <c r="C464" s="3"/>
@@ -28649,7 +28793,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="3"/>
     </row>
-    <row r="465" spans="1:26" ht="15">
+    <row r="465" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A465" s="3"/>
       <c r="B465" s="6"/>
       <c r="C465" s="3"/>
@@ -28677,7 +28821,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="3"/>
     </row>
-    <row r="466" spans="1:26" ht="15">
+    <row r="466" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A466" s="3"/>
       <c r="B466" s="6"/>
       <c r="C466" s="3"/>
@@ -28705,7 +28849,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="3"/>
     </row>
-    <row r="467" spans="1:26" ht="15">
+    <row r="467" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A467" s="3"/>
       <c r="B467" s="6"/>
       <c r="C467" s="3"/>
@@ -28733,7 +28877,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="3"/>
     </row>
-    <row r="468" spans="1:26" ht="15">
+    <row r="468" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A468" s="3"/>
       <c r="B468" s="6"/>
       <c r="C468" s="3"/>
@@ -28761,7 +28905,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="3"/>
     </row>
-    <row r="469" spans="1:26" ht="15">
+    <row r="469" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A469" s="3"/>
       <c r="B469" s="6"/>
       <c r="C469" s="3"/>
@@ -28789,7 +28933,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="3"/>
     </row>
-    <row r="470" spans="1:26" ht="15">
+    <row r="470" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A470" s="3"/>
       <c r="B470" s="6"/>
       <c r="C470" s="3"/>
@@ -28817,7 +28961,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="3"/>
     </row>
-    <row r="471" spans="1:26" ht="15">
+    <row r="471" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A471" s="3"/>
       <c r="B471" s="6"/>
       <c r="C471" s="3"/>
@@ -28845,7 +28989,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="3"/>
     </row>
-    <row r="472" spans="1:26" ht="15">
+    <row r="472" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A472" s="3"/>
       <c r="B472" s="6"/>
       <c r="C472" s="3"/>
@@ -28873,7 +29017,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="3"/>
     </row>
-    <row r="473" spans="1:26" ht="15">
+    <row r="473" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A473" s="3"/>
       <c r="B473" s="6"/>
       <c r="C473" s="3"/>
@@ -28901,7 +29045,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="3"/>
     </row>
-    <row r="474" spans="1:26" ht="15">
+    <row r="474" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A474" s="3"/>
       <c r="B474" s="6"/>
       <c r="C474" s="3"/>
@@ -28929,7 +29073,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="3"/>
     </row>
-    <row r="475" spans="1:26" ht="15">
+    <row r="475" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A475" s="3"/>
       <c r="B475" s="6"/>
       <c r="C475" s="3"/>
@@ -28957,7 +29101,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="3"/>
     </row>
-    <row r="476" spans="1:26" ht="15">
+    <row r="476" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A476" s="3"/>
       <c r="B476" s="6"/>
       <c r="C476" s="3"/>
@@ -28985,7 +29129,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="3"/>
     </row>
-    <row r="477" spans="1:26" ht="15">
+    <row r="477" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A477" s="3"/>
       <c r="B477" s="6"/>
       <c r="C477" s="3"/>
@@ -29013,7 +29157,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="3"/>
     </row>
-    <row r="478" spans="1:26" ht="15">
+    <row r="478" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A478" s="3"/>
       <c r="B478" s="6"/>
       <c r="C478" s="3"/>
@@ -29041,7 +29185,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="3"/>
     </row>
-    <row r="479" spans="1:26" ht="15">
+    <row r="479" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A479" s="3"/>
       <c r="B479" s="6"/>
       <c r="C479" s="3"/>
@@ -29069,7 +29213,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="3"/>
     </row>
-    <row r="480" spans="1:26" ht="15">
+    <row r="480" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A480" s="3"/>
       <c r="B480" s="6"/>
       <c r="C480" s="3"/>
@@ -29097,7 +29241,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="3"/>
     </row>
-    <row r="481" spans="1:26" ht="15">
+    <row r="481" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A481" s="3"/>
       <c r="B481" s="6"/>
       <c r="C481" s="3"/>
@@ -29125,7 +29269,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="3"/>
     </row>
-    <row r="482" spans="1:26" ht="15">
+    <row r="482" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A482" s="3"/>
       <c r="B482" s="6"/>
       <c r="C482" s="3"/>
@@ -29153,7 +29297,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="3"/>
     </row>
-    <row r="483" spans="1:26" ht="15">
+    <row r="483" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A483" s="3"/>
       <c r="B483" s="6"/>
       <c r="C483" s="3"/>
@@ -29181,7 +29325,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="3"/>
     </row>
-    <row r="484" spans="1:26" ht="15">
+    <row r="484" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A484" s="3"/>
       <c r="B484" s="6"/>
       <c r="C484" s="3"/>
@@ -29209,7 +29353,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="3"/>
     </row>
-    <row r="485" spans="1:26" ht="15">
+    <row r="485" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A485" s="3"/>
       <c r="B485" s="6"/>
       <c r="C485" s="3"/>
@@ -29237,7 +29381,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="3"/>
     </row>
-    <row r="486" spans="1:26" ht="15">
+    <row r="486" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A486" s="3"/>
       <c r="B486" s="6"/>
       <c r="C486" s="3"/>
@@ -29265,7 +29409,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="3"/>
     </row>
-    <row r="487" spans="1:26" ht="15">
+    <row r="487" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A487" s="3"/>
       <c r="B487" s="6"/>
       <c r="C487" s="3"/>
@@ -29293,7 +29437,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="3"/>
     </row>
-    <row r="488" spans="1:26" ht="15">
+    <row r="488" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A488" s="3"/>
       <c r="B488" s="6"/>
       <c r="C488" s="3"/>
@@ -29321,7 +29465,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="3"/>
     </row>
-    <row r="489" spans="1:26" ht="15">
+    <row r="489" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A489" s="3"/>
       <c r="B489" s="6"/>
       <c r="C489" s="3"/>
@@ -29349,7 +29493,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="3"/>
     </row>
-    <row r="490" spans="1:26" ht="15">
+    <row r="490" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A490" s="3"/>
       <c r="B490" s="6"/>
       <c r="C490" s="3"/>
@@ -29377,7 +29521,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="3"/>
     </row>
-    <row r="491" spans="1:26" ht="15">
+    <row r="491" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A491" s="3"/>
       <c r="B491" s="6"/>
       <c r="C491" s="3"/>
@@ -29405,7 +29549,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="3"/>
     </row>
-    <row r="492" spans="1:26" ht="15">
+    <row r="492" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A492" s="3"/>
       <c r="B492" s="6"/>
       <c r="C492" s="3"/>
@@ -29433,7 +29577,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="3"/>
     </row>
-    <row r="493" spans="1:26" ht="15">
+    <row r="493" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A493" s="3"/>
       <c r="B493" s="6"/>
       <c r="C493" s="3"/>
@@ -29461,7 +29605,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="3"/>
     </row>
-    <row r="494" spans="1:26" ht="15">
+    <row r="494" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A494" s="3"/>
       <c r="B494" s="6"/>
       <c r="C494" s="3"/>
@@ -29489,7 +29633,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="3"/>
     </row>
-    <row r="495" spans="1:26" ht="15">
+    <row r="495" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A495" s="3"/>
       <c r="B495" s="6"/>
       <c r="C495" s="3"/>
@@ -29517,7 +29661,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="3"/>
     </row>
-    <row r="496" spans="1:26" ht="15">
+    <row r="496" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A496" s="3"/>
       <c r="B496" s="6"/>
       <c r="C496" s="3"/>
@@ -29545,7 +29689,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="3"/>
     </row>
-    <row r="497" spans="1:26" ht="15">
+    <row r="497" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A497" s="3"/>
       <c r="B497" s="6"/>
       <c r="C497" s="3"/>
@@ -29573,7 +29717,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="3"/>
     </row>
-    <row r="498" spans="1:26" ht="15">
+    <row r="498" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A498" s="3"/>
       <c r="B498" s="6"/>
       <c r="C498" s="3"/>
@@ -29601,7 +29745,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="3"/>
     </row>
-    <row r="499" spans="1:26" ht="15">
+    <row r="499" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A499" s="3"/>
       <c r="B499" s="6"/>
       <c r="C499" s="3"/>
@@ -29629,7 +29773,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="3"/>
     </row>
-    <row r="500" spans="1:26" ht="15">
+    <row r="500" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A500" s="3"/>
       <c r="B500" s="6"/>
       <c r="C500" s="3"/>
@@ -29657,7 +29801,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="3"/>
     </row>
-    <row r="501" spans="1:26" ht="15">
+    <row r="501" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A501" s="3"/>
       <c r="B501" s="6"/>
       <c r="C501" s="3"/>
@@ -29685,7 +29829,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="3"/>
     </row>
-    <row r="502" spans="1:26" ht="15">
+    <row r="502" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A502" s="3"/>
       <c r="B502" s="6"/>
       <c r="C502" s="3"/>
@@ -29713,7 +29857,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="3"/>
     </row>
-    <row r="503" spans="1:26" ht="15">
+    <row r="503" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A503" s="3"/>
       <c r="B503" s="6"/>
       <c r="C503" s="3"/>
@@ -29741,7 +29885,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="3"/>
     </row>
-    <row r="504" spans="1:26" ht="15">
+    <row r="504" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A504" s="3"/>
       <c r="B504" s="6"/>
       <c r="C504" s="3"/>
@@ -29769,7 +29913,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="3"/>
     </row>
-    <row r="505" spans="1:26" ht="15">
+    <row r="505" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A505" s="3"/>
       <c r="B505" s="6"/>
       <c r="C505" s="3"/>
@@ -29797,7 +29941,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="3"/>
     </row>
-    <row r="506" spans="1:26" ht="15">
+    <row r="506" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A506" s="3"/>
       <c r="B506" s="6"/>
       <c r="C506" s="3"/>
@@ -29825,7 +29969,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="3"/>
     </row>
-    <row r="507" spans="1:26" ht="15">
+    <row r="507" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A507" s="3"/>
       <c r="B507" s="6"/>
       <c r="C507" s="3"/>
@@ -29853,7 +29997,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="3"/>
     </row>
-    <row r="508" spans="1:26" ht="15">
+    <row r="508" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A508" s="3"/>
       <c r="B508" s="6"/>
       <c r="C508" s="3"/>
@@ -29881,7 +30025,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="3"/>
     </row>
-    <row r="509" spans="1:26" ht="15">
+    <row r="509" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A509" s="3"/>
       <c r="B509" s="6"/>
       <c r="C509" s="3"/>
@@ -29909,7 +30053,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="3"/>
     </row>
-    <row r="510" spans="1:26" ht="15">
+    <row r="510" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A510" s="3"/>
       <c r="B510" s="6"/>
       <c r="C510" s="3"/>
@@ -29937,7 +30081,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="3"/>
     </row>
-    <row r="511" spans="1:26" ht="15">
+    <row r="511" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A511" s="3"/>
       <c r="B511" s="6"/>
       <c r="C511" s="3"/>
@@ -29965,7 +30109,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="3"/>
     </row>
-    <row r="512" spans="1:26" ht="15">
+    <row r="512" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A512" s="3"/>
       <c r="B512" s="6"/>
       <c r="C512" s="3"/>
@@ -29993,7 +30137,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="3"/>
     </row>
-    <row r="513" spans="1:26" ht="15">
+    <row r="513" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A513" s="3"/>
       <c r="B513" s="6"/>
       <c r="C513" s="3"/>
@@ -30021,7 +30165,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="3"/>
     </row>
-    <row r="514" spans="1:26" ht="15">
+    <row r="514" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A514" s="3"/>
       <c r="B514" s="6"/>
       <c r="C514" s="3"/>
@@ -30049,7 +30193,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="3"/>
     </row>
-    <row r="515" spans="1:26" ht="15">
+    <row r="515" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A515" s="3"/>
       <c r="B515" s="6"/>
       <c r="C515" s="3"/>
@@ -30077,7 +30221,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="3"/>
     </row>
-    <row r="516" spans="1:26" ht="15">
+    <row r="516" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A516" s="3"/>
       <c r="B516" s="6"/>
       <c r="C516" s="3"/>
@@ -30105,7 +30249,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="3"/>
     </row>
-    <row r="517" spans="1:26" ht="15">
+    <row r="517" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
       <c r="B517" s="6"/>
       <c r="C517" s="3"/>
@@ -30133,7 +30277,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="3"/>
     </row>
-    <row r="518" spans="1:26" ht="15">
+    <row r="518" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A518" s="3"/>
       <c r="B518" s="6"/>
       <c r="C518" s="3"/>
@@ -30161,7 +30305,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="3"/>
     </row>
-    <row r="519" spans="1:26" ht="15">
+    <row r="519" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A519" s="3"/>
       <c r="B519" s="6"/>
       <c r="C519" s="3"/>
@@ -30189,7 +30333,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="3"/>
     </row>
-    <row r="520" spans="1:26" ht="15">
+    <row r="520" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A520" s="3"/>
       <c r="B520" s="6"/>
       <c r="C520" s="3"/>
@@ -30217,7 +30361,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="3"/>
     </row>
-    <row r="521" spans="1:26" ht="15">
+    <row r="521" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A521" s="3"/>
       <c r="B521" s="6"/>
       <c r="C521" s="3"/>
@@ -30245,7 +30389,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="3"/>
     </row>
-    <row r="522" spans="1:26" ht="15">
+    <row r="522" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A522" s="3"/>
       <c r="B522" s="6"/>
       <c r="C522" s="3"/>
@@ -30273,7 +30417,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="3"/>
     </row>
-    <row r="523" spans="1:26" ht="15">
+    <row r="523" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A523" s="3"/>
       <c r="B523" s="6"/>
       <c r="C523" s="3"/>
@@ -30301,7 +30445,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="3"/>
     </row>
-    <row r="524" spans="1:26" ht="15">
+    <row r="524" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A524" s="3"/>
       <c r="B524" s="6"/>
       <c r="C524" s="3"/>
@@ -30329,7 +30473,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="3"/>
     </row>
-    <row r="525" spans="1:26" ht="15">
+    <row r="525" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A525" s="3"/>
       <c r="B525" s="6"/>
       <c r="C525" s="3"/>
@@ -30357,7 +30501,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="3"/>
     </row>
-    <row r="526" spans="1:26" ht="15">
+    <row r="526" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A526" s="3"/>
       <c r="B526" s="6"/>
       <c r="C526" s="3"/>
@@ -30385,7 +30529,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="3"/>
     </row>
-    <row r="527" spans="1:26" ht="15">
+    <row r="527" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A527" s="3"/>
       <c r="B527" s="6"/>
       <c r="C527" s="3"/>
@@ -30413,7 +30557,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="3"/>
     </row>
-    <row r="528" spans="1:26" ht="15">
+    <row r="528" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A528" s="3"/>
       <c r="B528" s="6"/>
       <c r="C528" s="3"/>
@@ -30441,7 +30585,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="3"/>
     </row>
-    <row r="529" spans="1:26" ht="15">
+    <row r="529" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A529" s="3"/>
       <c r="B529" s="6"/>
       <c r="C529" s="3"/>
@@ -30469,7 +30613,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="3"/>
     </row>
-    <row r="530" spans="1:26" ht="15">
+    <row r="530" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A530" s="3"/>
       <c r="B530" s="6"/>
       <c r="C530" s="3"/>
@@ -30497,7 +30641,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="3"/>
     </row>
-    <row r="531" spans="1:26" ht="15">
+    <row r="531" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A531" s="3"/>
       <c r="B531" s="6"/>
       <c r="C531" s="3"/>
@@ -30525,7 +30669,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="3"/>
     </row>
-    <row r="532" spans="1:26" ht="15">
+    <row r="532" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A532" s="3"/>
       <c r="B532" s="6"/>
       <c r="C532" s="3"/>
@@ -30553,7 +30697,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="3"/>
     </row>
-    <row r="533" spans="1:26" ht="15">
+    <row r="533" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A533" s="3"/>
       <c r="B533" s="6"/>
       <c r="C533" s="3"/>
@@ -30581,7 +30725,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="3"/>
     </row>
-    <row r="534" spans="1:26" ht="15">
+    <row r="534" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A534" s="3"/>
       <c r="B534" s="6"/>
       <c r="C534" s="3"/>
@@ -30609,7 +30753,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="3"/>
     </row>
-    <row r="535" spans="1:26" ht="15">
+    <row r="535" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A535" s="3"/>
       <c r="B535" s="6"/>
       <c r="C535" s="3"/>
@@ -30637,7 +30781,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="3"/>
     </row>
-    <row r="536" spans="1:26" ht="15">
+    <row r="536" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A536" s="3"/>
       <c r="B536" s="6"/>
       <c r="C536" s="3"/>
@@ -30665,7 +30809,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="3"/>
     </row>
-    <row r="537" spans="1:26" ht="15">
+    <row r="537" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A537" s="3"/>
       <c r="B537" s="6"/>
       <c r="C537" s="3"/>
@@ -30693,7 +30837,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="3"/>
     </row>
-    <row r="538" spans="1:26" ht="15">
+    <row r="538" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A538" s="3"/>
       <c r="B538" s="6"/>
       <c r="C538" s="3"/>
@@ -30721,7 +30865,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="3"/>
     </row>
-    <row r="539" spans="1:26" ht="15">
+    <row r="539" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A539" s="3"/>
       <c r="B539" s="6"/>
       <c r="C539" s="3"/>
@@ -30749,7 +30893,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="3"/>
     </row>
-    <row r="540" spans="1:26" ht="15">
+    <row r="540" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A540" s="3"/>
       <c r="B540" s="6"/>
       <c r="C540" s="3"/>
@@ -30777,7 +30921,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="3"/>
     </row>
-    <row r="541" spans="1:26" ht="15">
+    <row r="541" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="6"/>
       <c r="C541" s="3"/>
@@ -30805,7 +30949,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="3"/>
     </row>
-    <row r="542" spans="1:26" ht="15">
+    <row r="542" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A542" s="3"/>
       <c r="B542" s="6"/>
       <c r="C542" s="3"/>
@@ -30833,7 +30977,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="3"/>
     </row>
-    <row r="543" spans="1:26" ht="15">
+    <row r="543" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A543" s="3"/>
       <c r="B543" s="6"/>
       <c r="C543" s="3"/>
@@ -30861,7 +31005,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="3"/>
     </row>
-    <row r="544" spans="1:26" ht="15">
+    <row r="544" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A544" s="3"/>
       <c r="B544" s="6"/>
       <c r="C544" s="3"/>
@@ -30889,7 +31033,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="3"/>
     </row>
-    <row r="545" spans="1:26" ht="15">
+    <row r="545" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A545" s="3"/>
       <c r="B545" s="6"/>
       <c r="C545" s="3"/>
@@ -30917,7 +31061,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="3"/>
     </row>
-    <row r="546" spans="1:26" ht="15">
+    <row r="546" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A546" s="3"/>
       <c r="B546" s="6"/>
       <c r="C546" s="3"/>
@@ -30945,7 +31089,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="3"/>
     </row>
-    <row r="547" spans="1:26" ht="15">
+    <row r="547" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A547" s="3"/>
       <c r="B547" s="6"/>
       <c r="C547" s="3"/>
@@ -30973,7 +31117,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="3"/>
     </row>
-    <row r="548" spans="1:26" ht="15">
+    <row r="548" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A548" s="3"/>
       <c r="B548" s="6"/>
       <c r="C548" s="3"/>
@@ -31001,7 +31145,7 @@
       <c r="Y548" s="3"/>
       <c r="Z548" s="3"/>
     </row>
-    <row r="549" spans="1:26" ht="15">
+    <row r="549" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A549" s="3"/>
       <c r="B549" s="6"/>
       <c r="C549" s="3"/>
@@ -31029,7 +31173,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="3"/>
     </row>
-    <row r="550" spans="1:26" ht="15">
+    <row r="550" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A550" s="3"/>
       <c r="B550" s="6"/>
       <c r="C550" s="3"/>
@@ -31057,7 +31201,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="3"/>
     </row>
-    <row r="551" spans="1:26" ht="15">
+    <row r="551" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A551" s="3"/>
       <c r="B551" s="6"/>
       <c r="C551" s="3"/>
@@ -31085,7 +31229,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="3"/>
     </row>
-    <row r="552" spans="1:26" ht="15">
+    <row r="552" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A552" s="3"/>
       <c r="B552" s="6"/>
       <c r="C552" s="3"/>
@@ -31113,7 +31257,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="3"/>
     </row>
-    <row r="553" spans="1:26" ht="15">
+    <row r="553" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A553" s="3"/>
       <c r="B553" s="6"/>
       <c r="C553" s="3"/>
@@ -31141,7 +31285,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="3"/>
     </row>
-    <row r="554" spans="1:26" ht="15">
+    <row r="554" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A554" s="3"/>
       <c r="B554" s="6"/>
       <c r="C554" s="3"/>
@@ -31169,7 +31313,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="3"/>
     </row>
-    <row r="555" spans="1:26" ht="15">
+    <row r="555" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A555" s="3"/>
       <c r="B555" s="6"/>
       <c r="C555" s="3"/>
@@ -31197,7 +31341,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="3"/>
     </row>
-    <row r="556" spans="1:26" ht="15">
+    <row r="556" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A556" s="3"/>
       <c r="B556" s="6"/>
       <c r="C556" s="3"/>
@@ -31225,7 +31369,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="3"/>
     </row>
-    <row r="557" spans="1:26" ht="15">
+    <row r="557" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A557" s="3"/>
       <c r="B557" s="6"/>
       <c r="C557" s="3"/>
@@ -31253,7 +31397,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="3"/>
     </row>
-    <row r="558" spans="1:26" ht="15">
+    <row r="558" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A558" s="3"/>
       <c r="B558" s="6"/>
       <c r="C558" s="3"/>
@@ -31281,7 +31425,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="3"/>
     </row>
-    <row r="559" spans="1:26" ht="15">
+    <row r="559" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A559" s="3"/>
       <c r="B559" s="6"/>
       <c r="C559" s="3"/>
@@ -31309,7 +31453,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="3"/>
     </row>
-    <row r="560" spans="1:26" ht="15">
+    <row r="560" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A560" s="3"/>
       <c r="B560" s="6"/>
       <c r="C560" s="3"/>
@@ -31337,7 +31481,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="3"/>
     </row>
-    <row r="561" spans="1:26" ht="15">
+    <row r="561" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A561" s="3"/>
       <c r="B561" s="6"/>
       <c r="C561" s="3"/>
@@ -31365,7 +31509,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="3"/>
     </row>
-    <row r="562" spans="1:26" ht="15">
+    <row r="562" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A562" s="3"/>
       <c r="B562" s="6"/>
       <c r="C562" s="3"/>
@@ -31393,7 +31537,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="3"/>
     </row>
-    <row r="563" spans="1:26" ht="15">
+    <row r="563" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A563" s="3"/>
       <c r="B563" s="6"/>
       <c r="C563" s="3"/>
@@ -31421,7 +31565,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="3"/>
     </row>
-    <row r="564" spans="1:26" ht="15">
+    <row r="564" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A564" s="3"/>
       <c r="B564" s="6"/>
       <c r="C564" s="3"/>
@@ -31449,7 +31593,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="3"/>
     </row>
-    <row r="565" spans="1:26" ht="15">
+    <row r="565" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A565" s="3"/>
       <c r="B565" s="6"/>
       <c r="C565" s="3"/>
@@ -31477,7 +31621,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="3"/>
     </row>
-    <row r="566" spans="1:26" ht="15">
+    <row r="566" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A566" s="3"/>
       <c r="B566" s="6"/>
       <c r="C566" s="3"/>
@@ -31505,7 +31649,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="3"/>
     </row>
-    <row r="567" spans="1:26" ht="15">
+    <row r="567" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A567" s="3"/>
       <c r="B567" s="6"/>
       <c r="C567" s="3"/>
@@ -31533,7 +31677,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="3"/>
     </row>
-    <row r="568" spans="1:26" ht="15">
+    <row r="568" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A568" s="3"/>
       <c r="B568" s="6"/>
       <c r="C568" s="3"/>
@@ -31561,7 +31705,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="3"/>
     </row>
-    <row r="569" spans="1:26" ht="15">
+    <row r="569" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A569" s="3"/>
       <c r="B569" s="6"/>
       <c r="C569" s="3"/>
@@ -31589,7 +31733,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="3"/>
     </row>
-    <row r="570" spans="1:26" ht="15">
+    <row r="570" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A570" s="3"/>
       <c r="B570" s="6"/>
       <c r="C570" s="3"/>
@@ -31617,7 +31761,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="3"/>
     </row>
-    <row r="571" spans="1:26" ht="15">
+    <row r="571" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A571" s="3"/>
       <c r="B571" s="6"/>
       <c r="C571" s="3"/>
@@ -31645,7 +31789,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="3"/>
     </row>
-    <row r="572" spans="1:26" ht="15">
+    <row r="572" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A572" s="3"/>
       <c r="B572" s="6"/>
       <c r="C572" s="3"/>
@@ -31673,7 +31817,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="3"/>
     </row>
-    <row r="573" spans="1:26" ht="15">
+    <row r="573" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A573" s="3"/>
       <c r="B573" s="6"/>
       <c r="C573" s="3"/>
@@ -31701,7 +31845,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="3"/>
     </row>
-    <row r="574" spans="1:26" ht="15">
+    <row r="574" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A574" s="3"/>
       <c r="B574" s="6"/>
       <c r="C574" s="3"/>
@@ -31729,7 +31873,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="3"/>
     </row>
-    <row r="575" spans="1:26" ht="15">
+    <row r="575" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A575" s="3"/>
       <c r="B575" s="6"/>
       <c r="C575" s="3"/>
@@ -31757,7 +31901,7 @@
       <c r="Y575" s="3"/>
       <c r="Z575" s="3"/>
     </row>
-    <row r="576" spans="1:26" ht="15">
+    <row r="576" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A576" s="3"/>
       <c r="B576" s="6"/>
       <c r="C576" s="3"/>
@@ -31785,7 +31929,7 @@
       <c r="Y576" s="3"/>
       <c r="Z576" s="3"/>
     </row>
-    <row r="577" spans="1:26" ht="15">
+    <row r="577" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A577" s="3"/>
       <c r="B577" s="6"/>
       <c r="C577" s="3"/>
@@ -31813,7 +31957,7 @@
       <c r="Y577" s="3"/>
       <c r="Z577" s="3"/>
     </row>
-    <row r="578" spans="1:26" ht="15">
+    <row r="578" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A578" s="3"/>
       <c r="B578" s="6"/>
       <c r="C578" s="3"/>
@@ -31841,7 +31985,7 @@
       <c r="Y578" s="3"/>
       <c r="Z578" s="3"/>
     </row>
-    <row r="579" spans="1:26" ht="15">
+    <row r="579" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A579" s="3"/>
       <c r="B579" s="6"/>
       <c r="C579" s="3"/>
@@ -31869,7 +32013,7 @@
       <c r="Y579" s="3"/>
       <c r="Z579" s="3"/>
     </row>
-    <row r="580" spans="1:26" ht="15">
+    <row r="580" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A580" s="3"/>
       <c r="B580" s="6"/>
       <c r="C580" s="3"/>
@@ -31897,7 +32041,7 @@
       <c r="Y580" s="3"/>
       <c r="Z580" s="3"/>
     </row>
-    <row r="581" spans="1:26" ht="15">
+    <row r="581" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A581" s="3"/>
       <c r="B581" s="6"/>
       <c r="C581" s="3"/>
@@ -31925,7 +32069,7 @@
       <c r="Y581" s="3"/>
       <c r="Z581" s="3"/>
     </row>
-    <row r="582" spans="1:26" ht="15">
+    <row r="582" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A582" s="3"/>
       <c r="B582" s="6"/>
       <c r="C582" s="3"/>
@@ -31953,7 +32097,7 @@
       <c r="Y582" s="3"/>
       <c r="Z582" s="3"/>
     </row>
-    <row r="583" spans="1:26" ht="15">
+    <row r="583" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A583" s="3"/>
       <c r="B583" s="6"/>
       <c r="C583" s="3"/>
@@ -31981,7 +32125,7 @@
       <c r="Y583" s="3"/>
       <c r="Z583" s="3"/>
     </row>
-    <row r="584" spans="1:26" ht="15">
+    <row r="584" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A584" s="3"/>
       <c r="B584" s="6"/>
       <c r="C584" s="3"/>
@@ -32009,7 +32153,7 @@
       <c r="Y584" s="3"/>
       <c r="Z584" s="3"/>
     </row>
-    <row r="585" spans="1:26" ht="15">
+    <row r="585" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A585" s="3"/>
       <c r="B585" s="6"/>
       <c r="C585" s="3"/>
@@ -32037,7 +32181,7 @@
       <c r="Y585" s="3"/>
       <c r="Z585" s="3"/>
     </row>
-    <row r="586" spans="1:26" ht="15">
+    <row r="586" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A586" s="3"/>
       <c r="B586" s="6"/>
       <c r="C586" s="3"/>
@@ -32065,7 +32209,7 @@
       <c r="Y586" s="3"/>
       <c r="Z586" s="3"/>
     </row>
-    <row r="587" spans="1:26" ht="15">
+    <row r="587" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A587" s="3"/>
       <c r="B587" s="6"/>
       <c r="C587" s="3"/>
@@ -32093,7 +32237,7 @@
       <c r="Y587" s="3"/>
       <c r="Z587" s="3"/>
     </row>
-    <row r="588" spans="1:26" ht="15">
+    <row r="588" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A588" s="3"/>
       <c r="B588" s="6"/>
       <c r="C588" s="3"/>
@@ -32121,7 +32265,7 @@
       <c r="Y588" s="3"/>
       <c r="Z588" s="3"/>
     </row>
-    <row r="589" spans="1:26" ht="15">
+    <row r="589" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A589" s="3"/>
       <c r="B589" s="6"/>
       <c r="C589" s="3"/>
@@ -32149,7 +32293,7 @@
       <c r="Y589" s="3"/>
       <c r="Z589" s="3"/>
     </row>
-    <row r="590" spans="1:26" ht="15">
+    <row r="590" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A590" s="3"/>
       <c r="B590" s="6"/>
       <c r="C590" s="3"/>
@@ -32177,7 +32321,7 @@
       <c r="Y590" s="3"/>
       <c r="Z590" s="3"/>
     </row>
-    <row r="591" spans="1:26" ht="15">
+    <row r="591" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A591" s="3"/>
       <c r="B591" s="6"/>
       <c r="C591" s="3"/>
@@ -32205,7 +32349,7 @@
       <c r="Y591" s="3"/>
       <c r="Z591" s="3"/>
     </row>
-    <row r="592" spans="1:26" ht="15">
+    <row r="592" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A592" s="3"/>
       <c r="B592" s="6"/>
       <c r="C592" s="3"/>
@@ -32233,7 +32377,7 @@
       <c r="Y592" s="3"/>
       <c r="Z592" s="3"/>
     </row>
-    <row r="593" spans="1:26" ht="15">
+    <row r="593" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A593" s="3"/>
       <c r="B593" s="6"/>
       <c r="C593" s="3"/>
@@ -32261,7 +32405,7 @@
       <c r="Y593" s="3"/>
       <c r="Z593" s="3"/>
     </row>
-    <row r="594" spans="1:26" ht="15">
+    <row r="594" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A594" s="3"/>
       <c r="B594" s="6"/>
       <c r="C594" s="3"/>
@@ -32289,7 +32433,7 @@
       <c r="Y594" s="3"/>
       <c r="Z594" s="3"/>
     </row>
-    <row r="595" spans="1:26" ht="15">
+    <row r="595" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A595" s="3"/>
       <c r="B595" s="6"/>
       <c r="C595" s="3"/>
@@ -32317,7 +32461,7 @@
       <c r="Y595" s="3"/>
       <c r="Z595" s="3"/>
     </row>
-    <row r="596" spans="1:26" ht="15">
+    <row r="596" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A596" s="3"/>
       <c r="B596" s="6"/>
       <c r="C596" s="3"/>
@@ -32345,7 +32489,7 @@
       <c r="Y596" s="3"/>
       <c r="Z596" s="3"/>
     </row>
-    <row r="597" spans="1:26" ht="15">
+    <row r="597" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A597" s="3"/>
       <c r="B597" s="6"/>
       <c r="C597" s="3"/>
@@ -32373,7 +32517,7 @@
       <c r="Y597" s="3"/>
       <c r="Z597" s="3"/>
     </row>
-    <row r="598" spans="1:26" ht="15">
+    <row r="598" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="6"/>
       <c r="C598" s="3"/>
@@ -32401,7 +32545,7 @@
       <c r="Y598" s="3"/>
       <c r="Z598" s="3"/>
     </row>
-    <row r="599" spans="1:26" ht="15">
+    <row r="599" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A599" s="3"/>
       <c r="B599" s="6"/>
       <c r="C599" s="3"/>
@@ -32429,7 +32573,7 @@
       <c r="Y599" s="3"/>
       <c r="Z599" s="3"/>
     </row>
-    <row r="600" spans="1:26" ht="15">
+    <row r="600" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A600" s="3"/>
       <c r="B600" s="6"/>
       <c r="C600" s="3"/>
@@ -32457,7 +32601,7 @@
       <c r="Y600" s="3"/>
       <c r="Z600" s="3"/>
     </row>
-    <row r="601" spans="1:26" ht="15">
+    <row r="601" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A601" s="3"/>
       <c r="B601" s="6"/>
       <c r="C601" s="3"/>
@@ -32485,7 +32629,7 @@
       <c r="Y601" s="3"/>
       <c r="Z601" s="3"/>
     </row>
-    <row r="602" spans="1:26" ht="15">
+    <row r="602" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="6"/>
       <c r="C602" s="3"/>
@@ -32513,7 +32657,7 @@
       <c r="Y602" s="3"/>
       <c r="Z602" s="3"/>
     </row>
-    <row r="603" spans="1:26" ht="15">
+    <row r="603" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A603" s="3"/>
       <c r="B603" s="6"/>
       <c r="C603" s="3"/>
@@ -32541,7 +32685,7 @@
       <c r="Y603" s="3"/>
       <c r="Z603" s="3"/>
     </row>
-    <row r="604" spans="1:26" ht="15">
+    <row r="604" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A604" s="3"/>
       <c r="B604" s="6"/>
       <c r="C604" s="3"/>
@@ -32569,7 +32713,7 @@
       <c r="Y604" s="3"/>
       <c r="Z604" s="3"/>
     </row>
-    <row r="605" spans="1:26" ht="15">
+    <row r="605" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A605" s="3"/>
       <c r="B605" s="6"/>
       <c r="C605" s="3"/>
@@ -32597,7 +32741,7 @@
       <c r="Y605" s="3"/>
       <c r="Z605" s="3"/>
     </row>
-    <row r="606" spans="1:26" ht="15">
+    <row r="606" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A606" s="3"/>
       <c r="B606" s="6"/>
       <c r="C606" s="3"/>
@@ -32625,7 +32769,7 @@
       <c r="Y606" s="3"/>
       <c r="Z606" s="3"/>
     </row>
-    <row r="607" spans="1:26" ht="15">
+    <row r="607" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A607" s="3"/>
       <c r="B607" s="6"/>
       <c r="C607" s="3"/>
@@ -32653,7 +32797,7 @@
       <c r="Y607" s="3"/>
       <c r="Z607" s="3"/>
     </row>
-    <row r="608" spans="1:26" ht="15">
+    <row r="608" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A608" s="3"/>
       <c r="B608" s="6"/>
       <c r="C608" s="3"/>
@@ -32681,7 +32825,7 @@
       <c r="Y608" s="3"/>
       <c r="Z608" s="3"/>
     </row>
-    <row r="609" spans="1:26" ht="15">
+    <row r="609" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A609" s="3"/>
       <c r="B609" s="6"/>
       <c r="C609" s="3"/>
@@ -32709,7 +32853,7 @@
       <c r="Y609" s="3"/>
       <c r="Z609" s="3"/>
     </row>
-    <row r="610" spans="1:26" ht="15">
+    <row r="610" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A610" s="3"/>
       <c r="B610" s="6"/>
       <c r="C610" s="3"/>
@@ -32737,7 +32881,7 @@
       <c r="Y610" s="3"/>
       <c r="Z610" s="3"/>
     </row>
-    <row r="611" spans="1:26" ht="15">
+    <row r="611" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A611" s="3"/>
       <c r="B611" s="6"/>
       <c r="C611" s="3"/>
@@ -32765,7 +32909,7 @@
       <c r="Y611" s="3"/>
       <c r="Z611" s="3"/>
     </row>
-    <row r="612" spans="1:26" ht="15">
+    <row r="612" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A612" s="3"/>
       <c r="B612" s="6"/>
       <c r="C612" s="3"/>
@@ -32793,7 +32937,7 @@
       <c r="Y612" s="3"/>
       <c r="Z612" s="3"/>
     </row>
-    <row r="613" spans="1:26" ht="15">
+    <row r="613" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A613" s="3"/>
       <c r="B613" s="6"/>
       <c r="C613" s="3"/>
@@ -32821,7 +32965,7 @@
       <c r="Y613" s="3"/>
       <c r="Z613" s="3"/>
     </row>
-    <row r="614" spans="1:26" ht="15">
+    <row r="614" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A614" s="3"/>
       <c r="B614" s="6"/>
       <c r="C614" s="3"/>
@@ -32849,7 +32993,7 @@
       <c r="Y614" s="3"/>
       <c r="Z614" s="3"/>
     </row>
-    <row r="615" spans="1:26" ht="15">
+    <row r="615" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A615" s="3"/>
       <c r="B615" s="6"/>
       <c r="C615" s="3"/>
@@ -32877,7 +33021,7 @@
       <c r="Y615" s="3"/>
       <c r="Z615" s="3"/>
     </row>
-    <row r="616" spans="1:26" ht="15">
+    <row r="616" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A616" s="3"/>
       <c r="B616" s="6"/>
       <c r="C616" s="3"/>
@@ -32905,7 +33049,7 @@
       <c r="Y616" s="3"/>
       <c r="Z616" s="3"/>
     </row>
-    <row r="617" spans="1:26" ht="15">
+    <row r="617" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A617" s="3"/>
       <c r="B617" s="6"/>
       <c r="C617" s="3"/>
@@ -32933,7 +33077,7 @@
       <c r="Y617" s="3"/>
       <c r="Z617" s="3"/>
     </row>
-    <row r="618" spans="1:26" ht="15">
+    <row r="618" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A618" s="3"/>
       <c r="B618" s="6"/>
       <c r="C618" s="3"/>
@@ -32961,7 +33105,7 @@
       <c r="Y618" s="3"/>
       <c r="Z618" s="3"/>
     </row>
-    <row r="619" spans="1:26" ht="15">
+    <row r="619" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A619" s="3"/>
       <c r="B619" s="6"/>
       <c r="C619" s="3"/>
@@ -32989,7 +33133,7 @@
       <c r="Y619" s="3"/>
       <c r="Z619" s="3"/>
     </row>
-    <row r="620" spans="1:26" ht="15">
+    <row r="620" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A620" s="3"/>
       <c r="B620" s="6"/>
       <c r="C620" s="3"/>
@@ -33017,7 +33161,7 @@
       <c r="Y620" s="3"/>
       <c r="Z620" s="3"/>
     </row>
-    <row r="621" spans="1:26" ht="15">
+    <row r="621" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A621" s="3"/>
       <c r="B621" s="6"/>
       <c r="C621" s="3"/>
@@ -33045,7 +33189,7 @@
       <c r="Y621" s="3"/>
       <c r="Z621" s="3"/>
     </row>
-    <row r="622" spans="1:26" ht="15">
+    <row r="622" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A622" s="3"/>
       <c r="B622" s="6"/>
       <c r="C622" s="3"/>
@@ -33073,7 +33217,7 @@
       <c r="Y622" s="3"/>
       <c r="Z622" s="3"/>
     </row>
-    <row r="623" spans="1:26" ht="15">
+    <row r="623" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A623" s="3"/>
       <c r="B623" s="6"/>
       <c r="C623" s="3"/>
@@ -33101,7 +33245,7 @@
       <c r="Y623" s="3"/>
       <c r="Z623" s="3"/>
     </row>
-    <row r="624" spans="1:26" ht="15">
+    <row r="624" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A624" s="3"/>
       <c r="B624" s="6"/>
       <c r="C624" s="3"/>
@@ -33129,7 +33273,7 @@
       <c r="Y624" s="3"/>
       <c r="Z624" s="3"/>
     </row>
-    <row r="625" spans="1:26" ht="15">
+    <row r="625" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A625" s="3"/>
       <c r="B625" s="6"/>
       <c r="C625" s="3"/>
@@ -33157,7 +33301,7 @@
       <c r="Y625" s="3"/>
       <c r="Z625" s="3"/>
     </row>
-    <row r="626" spans="1:26" ht="15">
+    <row r="626" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A626" s="3"/>
       <c r="B626" s="6"/>
       <c r="C626" s="3"/>
@@ -33185,7 +33329,7 @@
       <c r="Y626" s="3"/>
       <c r="Z626" s="3"/>
     </row>
-    <row r="627" spans="1:26" ht="15">
+    <row r="627" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A627" s="3"/>
       <c r="B627" s="6"/>
       <c r="C627" s="3"/>
@@ -33213,7 +33357,7 @@
       <c r="Y627" s="3"/>
       <c r="Z627" s="3"/>
     </row>
-    <row r="628" spans="1:26" ht="15">
+    <row r="628" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A628" s="3"/>
       <c r="B628" s="6"/>
       <c r="C628" s="3"/>
@@ -33241,7 +33385,7 @@
       <c r="Y628" s="3"/>
       <c r="Z628" s="3"/>
     </row>
-    <row r="629" spans="1:26" ht="15">
+    <row r="629" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A629" s="3"/>
       <c r="B629" s="6"/>
       <c r="C629" s="3"/>
@@ -33269,7 +33413,7 @@
       <c r="Y629" s="3"/>
       <c r="Z629" s="3"/>
     </row>
-    <row r="630" spans="1:26" ht="15">
+    <row r="630" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A630" s="3"/>
       <c r="B630" s="6"/>
       <c r="C630" s="3"/>
@@ -33297,7 +33441,7 @@
       <c r="Y630" s="3"/>
       <c r="Z630" s="3"/>
     </row>
-    <row r="631" spans="1:26" ht="15">
+    <row r="631" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A631" s="3"/>
       <c r="B631" s="6"/>
       <c r="C631" s="3"/>
@@ -33325,7 +33469,7 @@
       <c r="Y631" s="3"/>
       <c r="Z631" s="3"/>
     </row>
-    <row r="632" spans="1:26" ht="15">
+    <row r="632" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A632" s="3"/>
       <c r="B632" s="6"/>
       <c r="C632" s="3"/>
@@ -33353,7 +33497,7 @@
       <c r="Y632" s="3"/>
       <c r="Z632" s="3"/>
     </row>
-    <row r="633" spans="1:26" ht="15">
+    <row r="633" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A633" s="3"/>
       <c r="B633" s="6"/>
       <c r="C633" s="3"/>
@@ -33381,7 +33525,7 @@
       <c r="Y633" s="3"/>
       <c r="Z633" s="3"/>
     </row>
-    <row r="634" spans="1:26" ht="15">
+    <row r="634" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A634" s="3"/>
       <c r="B634" s="6"/>
       <c r="C634" s="3"/>
@@ -33409,7 +33553,7 @@
       <c r="Y634" s="3"/>
       <c r="Z634" s="3"/>
     </row>
-    <row r="635" spans="1:26" ht="15">
+    <row r="635" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A635" s="3"/>
       <c r="B635" s="6"/>
       <c r="C635" s="3"/>
@@ -33437,7 +33581,7 @@
       <c r="Y635" s="3"/>
       <c r="Z635" s="3"/>
     </row>
-    <row r="636" spans="1:26" ht="15">
+    <row r="636" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A636" s="3"/>
       <c r="B636" s="6"/>
       <c r="C636" s="3"/>
@@ -33465,7 +33609,7 @@
       <c r="Y636" s="3"/>
       <c r="Z636" s="3"/>
     </row>
-    <row r="637" spans="1:26" ht="15">
+    <row r="637" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A637" s="3"/>
       <c r="B637" s="6"/>
       <c r="C637" s="3"/>
@@ -33493,7 +33637,7 @@
       <c r="Y637" s="3"/>
       <c r="Z637" s="3"/>
     </row>
-    <row r="638" spans="1:26" ht="15">
+    <row r="638" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A638" s="3"/>
       <c r="B638" s="6"/>
       <c r="C638" s="3"/>
@@ -33521,7 +33665,7 @@
       <c r="Y638" s="3"/>
       <c r="Z638" s="3"/>
     </row>
-    <row r="639" spans="1:26" ht="15">
+    <row r="639" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A639" s="3"/>
       <c r="B639" s="6"/>
       <c r="C639" s="3"/>
@@ -33549,7 +33693,7 @@
       <c r="Y639" s="3"/>
       <c r="Z639" s="3"/>
     </row>
-    <row r="640" spans="1:26" ht="15">
+    <row r="640" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A640" s="3"/>
       <c r="B640" s="6"/>
       <c r="C640" s="3"/>
@@ -33577,7 +33721,7 @@
       <c r="Y640" s="3"/>
       <c r="Z640" s="3"/>
     </row>
-    <row r="641" spans="1:26" ht="15">
+    <row r="641" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A641" s="3"/>
       <c r="B641" s="6"/>
       <c r="C641" s="3"/>
@@ -33605,7 +33749,7 @@
       <c r="Y641" s="3"/>
       <c r="Z641" s="3"/>
     </row>
-    <row r="642" spans="1:26" ht="15">
+    <row r="642" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A642" s="3"/>
       <c r="B642" s="6"/>
       <c r="C642" s="3"/>
@@ -33633,7 +33777,7 @@
       <c r="Y642" s="3"/>
       <c r="Z642" s="3"/>
     </row>
-    <row r="643" spans="1:26" ht="15">
+    <row r="643" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A643" s="3"/>
       <c r="B643" s="6"/>
       <c r="C643" s="3"/>
@@ -33661,7 +33805,7 @@
       <c r="Y643" s="3"/>
       <c r="Z643" s="3"/>
     </row>
-    <row r="644" spans="1:26" ht="15">
+    <row r="644" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A644" s="3"/>
       <c r="B644" s="6"/>
       <c r="C644" s="3"/>
@@ -33689,7 +33833,7 @@
       <c r="Y644" s="3"/>
       <c r="Z644" s="3"/>
     </row>
-    <row r="645" spans="1:26" ht="15">
+    <row r="645" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A645" s="3"/>
       <c r="B645" s="6"/>
       <c r="C645" s="3"/>
@@ -33717,7 +33861,7 @@
       <c r="Y645" s="3"/>
       <c r="Z645" s="3"/>
     </row>
-    <row r="646" spans="1:26" ht="15">
+    <row r="646" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A646" s="3"/>
       <c r="B646" s="6"/>
       <c r="C646" s="3"/>
@@ -33745,7 +33889,7 @@
       <c r="Y646" s="3"/>
       <c r="Z646" s="3"/>
     </row>
-    <row r="647" spans="1:26" ht="15">
+    <row r="647" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A647" s="3"/>
       <c r="B647" s="6"/>
       <c r="C647" s="3"/>
@@ -33773,7 +33917,7 @@
       <c r="Y647" s="3"/>
       <c r="Z647" s="3"/>
     </row>
-    <row r="648" spans="1:26" ht="15">
+    <row r="648" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A648" s="3"/>
       <c r="B648" s="6"/>
       <c r="C648" s="3"/>
@@ -33801,7 +33945,7 @@
       <c r="Y648" s="3"/>
       <c r="Z648" s="3"/>
     </row>
-    <row r="649" spans="1:26" ht="15">
+    <row r="649" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A649" s="3"/>
       <c r="B649" s="6"/>
       <c r="C649" s="3"/>
@@ -33829,7 +33973,7 @@
       <c r="Y649" s="3"/>
       <c r="Z649" s="3"/>
     </row>
-    <row r="650" spans="1:26" ht="15">
+    <row r="650" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A650" s="3"/>
       <c r="B650" s="6"/>
       <c r="C650" s="3"/>
@@ -33857,7 +34001,7 @@
       <c r="Y650" s="3"/>
       <c r="Z650" s="3"/>
     </row>
-    <row r="651" spans="1:26" ht="15">
+    <row r="651" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A651" s="3"/>
       <c r="B651" s="6"/>
       <c r="C651" s="3"/>
@@ -33885,7 +34029,7 @@
       <c r="Y651" s="3"/>
       <c r="Z651" s="3"/>
     </row>
-    <row r="652" spans="1:26" ht="15">
+    <row r="652" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A652" s="3"/>
       <c r="B652" s="6"/>
       <c r="C652" s="3"/>
@@ -33913,7 +34057,7 @@
       <c r="Y652" s="3"/>
       <c r="Z652" s="3"/>
     </row>
-    <row r="653" spans="1:26" ht="15">
+    <row r="653" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A653" s="3"/>
       <c r="B653" s="6"/>
       <c r="C653" s="3"/>
@@ -33941,7 +34085,7 @@
       <c r="Y653" s="3"/>
       <c r="Z653" s="3"/>
     </row>
-    <row r="654" spans="1:26" ht="15">
+    <row r="654" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A654" s="3"/>
       <c r="B654" s="6"/>
       <c r="C654" s="3"/>
@@ -33969,7 +34113,7 @@
       <c r="Y654" s="3"/>
       <c r="Z654" s="3"/>
     </row>
-    <row r="655" spans="1:26" ht="15">
+    <row r="655" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A655" s="3"/>
       <c r="B655" s="6"/>
       <c r="C655" s="3"/>
@@ -33997,7 +34141,7 @@
       <c r="Y655" s="3"/>
       <c r="Z655" s="3"/>
     </row>
-    <row r="656" spans="1:26" ht="15">
+    <row r="656" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A656" s="3"/>
       <c r="B656" s="6"/>
       <c r="C656" s="3"/>
@@ -34025,7 +34169,7 @@
       <c r="Y656" s="3"/>
       <c r="Z656" s="3"/>
     </row>
-    <row r="657" spans="1:26" ht="15">
+    <row r="657" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A657" s="3"/>
       <c r="B657" s="6"/>
       <c r="C657" s="3"/>
@@ -34053,7 +34197,7 @@
       <c r="Y657" s="3"/>
       <c r="Z657" s="3"/>
     </row>
-    <row r="658" spans="1:26" ht="15">
+    <row r="658" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A658" s="3"/>
       <c r="B658" s="6"/>
       <c r="C658" s="3"/>
@@ -34081,7 +34225,7 @@
       <c r="Y658" s="3"/>
       <c r="Z658" s="3"/>
     </row>
-    <row r="659" spans="1:26" ht="15">
+    <row r="659" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A659" s="3"/>
       <c r="B659" s="6"/>
       <c r="C659" s="3"/>
@@ -34109,7 +34253,7 @@
       <c r="Y659" s="3"/>
       <c r="Z659" s="3"/>
     </row>
-    <row r="660" spans="1:26" ht="15">
+    <row r="660" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A660" s="3"/>
       <c r="B660" s="6"/>
       <c r="C660" s="3"/>
@@ -34137,7 +34281,7 @@
       <c r="Y660" s="3"/>
       <c r="Z660" s="3"/>
     </row>
-    <row r="661" spans="1:26" ht="15">
+    <row r="661" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A661" s="3"/>
       <c r="B661" s="6"/>
       <c r="C661" s="3"/>
@@ -34165,7 +34309,7 @@
       <c r="Y661" s="3"/>
       <c r="Z661" s="3"/>
     </row>
-    <row r="662" spans="1:26" ht="15">
+    <row r="662" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A662" s="3"/>
       <c r="B662" s="6"/>
       <c r="C662" s="3"/>
@@ -34193,7 +34337,7 @@
       <c r="Y662" s="3"/>
       <c r="Z662" s="3"/>
     </row>
-    <row r="663" spans="1:26" ht="15">
+    <row r="663" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A663" s="3"/>
       <c r="B663" s="6"/>
       <c r="C663" s="3"/>
@@ -34221,7 +34365,7 @@
       <c r="Y663" s="3"/>
       <c r="Z663" s="3"/>
     </row>
-    <row r="664" spans="1:26" ht="15">
+    <row r="664" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A664" s="3"/>
       <c r="B664" s="6"/>
       <c r="C664" s="3"/>
@@ -34249,7 +34393,7 @@
       <c r="Y664" s="3"/>
       <c r="Z664" s="3"/>
     </row>
-    <row r="665" spans="1:26" ht="15">
+    <row r="665" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A665" s="3"/>
       <c r="B665" s="6"/>
       <c r="C665" s="3"/>
@@ -34277,7 +34421,7 @@
       <c r="Y665" s="3"/>
       <c r="Z665" s="3"/>
     </row>
-    <row r="666" spans="1:26" ht="15">
+    <row r="666" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A666" s="3"/>
       <c r="B666" s="6"/>
       <c r="C666" s="3"/>
@@ -34305,7 +34449,7 @@
       <c r="Y666" s="3"/>
       <c r="Z666" s="3"/>
     </row>
-    <row r="667" spans="1:26" ht="15">
+    <row r="667" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A667" s="3"/>
       <c r="B667" s="6"/>
       <c r="C667" s="3"/>
@@ -34333,7 +34477,7 @@
       <c r="Y667" s="3"/>
       <c r="Z667" s="3"/>
     </row>
-    <row r="668" spans="1:26" ht="15">
+    <row r="668" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A668" s="3"/>
       <c r="B668" s="6"/>
       <c r="C668" s="3"/>
@@ -34361,7 +34505,7 @@
       <c r="Y668" s="3"/>
       <c r="Z668" s="3"/>
     </row>
-    <row r="669" spans="1:26" ht="15">
+    <row r="669" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A669" s="3"/>
       <c r="B669" s="6"/>
       <c r="C669" s="3"/>
@@ -34389,7 +34533,7 @@
       <c r="Y669" s="3"/>
       <c r="Z669" s="3"/>
     </row>
-    <row r="670" spans="1:26" ht="15">
+    <row r="670" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A670" s="3"/>
       <c r="B670" s="6"/>
       <c r="C670" s="3"/>
@@ -34417,7 +34561,7 @@
       <c r="Y670" s="3"/>
       <c r="Z670" s="3"/>
     </row>
-    <row r="671" spans="1:26" ht="15">
+    <row r="671" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A671" s="3"/>
       <c r="B671" s="6"/>
       <c r="C671" s="3"/>
@@ -34445,7 +34589,7 @@
       <c r="Y671" s="3"/>
       <c r="Z671" s="3"/>
     </row>
-    <row r="672" spans="1:26" ht="15">
+    <row r="672" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A672" s="3"/>
       <c r="B672" s="6"/>
       <c r="C672" s="3"/>
@@ -34473,7 +34617,7 @@
       <c r="Y672" s="3"/>
       <c r="Z672" s="3"/>
     </row>
-    <row r="673" spans="1:26" ht="15">
+    <row r="673" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A673" s="3"/>
       <c r="B673" s="6"/>
       <c r="C673" s="3"/>
@@ -34501,7 +34645,7 @@
       <c r="Y673" s="3"/>
       <c r="Z673" s="3"/>
     </row>
-    <row r="674" spans="1:26" ht="15">
+    <row r="674" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A674" s="3"/>
       <c r="B674" s="6"/>
       <c r="C674" s="3"/>
@@ -34529,7 +34673,7 @@
       <c r="Y674" s="3"/>
       <c r="Z674" s="3"/>
     </row>
-    <row r="675" spans="1:26" ht="15">
+    <row r="675" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A675" s="3"/>
       <c r="B675" s="6"/>
       <c r="C675" s="3"/>
@@ -34557,7 +34701,7 @@
       <c r="Y675" s="3"/>
       <c r="Z675" s="3"/>
     </row>
-    <row r="676" spans="1:26" ht="15">
+    <row r="676" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A676" s="3"/>
       <c r="B676" s="6"/>
       <c r="C676" s="3"/>
@@ -34585,7 +34729,7 @@
       <c r="Y676" s="3"/>
       <c r="Z676" s="3"/>
     </row>
-    <row r="677" spans="1:26" ht="15">
+    <row r="677" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A677" s="3"/>
       <c r="B677" s="6"/>
       <c r="C677" s="3"/>
@@ -34613,7 +34757,7 @@
       <c r="Y677" s="3"/>
       <c r="Z677" s="3"/>
     </row>
-    <row r="678" spans="1:26" ht="15">
+    <row r="678" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A678" s="3"/>
       <c r="B678" s="6"/>
       <c r="C678" s="3"/>
@@ -34641,7 +34785,7 @@
       <c r="Y678" s="3"/>
       <c r="Z678" s="3"/>
     </row>
-    <row r="679" spans="1:26" ht="15">
+    <row r="679" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A679" s="3"/>
       <c r="B679" s="6"/>
       <c r="C679" s="3"/>
@@ -34669,7 +34813,7 @@
       <c r="Y679" s="3"/>
       <c r="Z679" s="3"/>
     </row>
-    <row r="680" spans="1:26" ht="15">
+    <row r="680" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A680" s="3"/>
       <c r="B680" s="6"/>
       <c r="C680" s="3"/>
@@ -34697,7 +34841,7 @@
       <c r="Y680" s="3"/>
       <c r="Z680" s="3"/>
     </row>
-    <row r="681" spans="1:26" ht="15">
+    <row r="681" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A681" s="3"/>
       <c r="B681" s="6"/>
       <c r="C681" s="3"/>
@@ -34725,7 +34869,7 @@
       <c r="Y681" s="3"/>
       <c r="Z681" s="3"/>
     </row>
-    <row r="682" spans="1:26" ht="15">
+    <row r="682" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A682" s="3"/>
       <c r="B682" s="6"/>
       <c r="C682" s="3"/>
@@ -34753,7 +34897,7 @@
       <c r="Y682" s="3"/>
       <c r="Z682" s="3"/>
     </row>
-    <row r="683" spans="1:26" ht="15">
+    <row r="683" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A683" s="3"/>
       <c r="B683" s="6"/>
       <c r="C683" s="3"/>
@@ -34781,7 +34925,7 @@
       <c r="Y683" s="3"/>
       <c r="Z683" s="3"/>
     </row>
-    <row r="684" spans="1:26" ht="15">
+    <row r="684" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A684" s="3"/>
       <c r="B684" s="6"/>
       <c r="C684" s="3"/>
@@ -34809,7 +34953,7 @@
       <c r="Y684" s="3"/>
       <c r="Z684" s="3"/>
     </row>
-    <row r="685" spans="1:26" ht="15">
+    <row r="685" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A685" s="3"/>
       <c r="B685" s="6"/>
       <c r="C685" s="3"/>
@@ -34837,7 +34981,7 @@
       <c r="Y685" s="3"/>
       <c r="Z685" s="3"/>
     </row>
-    <row r="686" spans="1:26" ht="15">
+    <row r="686" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A686" s="3"/>
       <c r="B686" s="6"/>
       <c r="C686" s="3"/>
@@ -34865,7 +35009,7 @@
       <c r="Y686" s="3"/>
       <c r="Z686" s="3"/>
     </row>
-    <row r="687" spans="1:26" ht="15">
+    <row r="687" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A687" s="3"/>
       <c r="B687" s="6"/>
       <c r="C687" s="3"/>
@@ -34893,7 +35037,7 @@
       <c r="Y687" s="3"/>
       <c r="Z687" s="3"/>
     </row>
-    <row r="688" spans="1:26" ht="15">
+    <row r="688" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A688" s="3"/>
       <c r="B688" s="6"/>
       <c r="C688" s="3"/>
@@ -34921,7 +35065,7 @@
       <c r="Y688" s="3"/>
       <c r="Z688" s="3"/>
     </row>
-    <row r="689" spans="1:26" ht="15">
+    <row r="689" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A689" s="3"/>
       <c r="B689" s="6"/>
       <c r="C689" s="3"/>
@@ -34949,7 +35093,7 @@
       <c r="Y689" s="3"/>
       <c r="Z689" s="3"/>
     </row>
-    <row r="690" spans="1:26" ht="15">
+    <row r="690" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A690" s="3"/>
       <c r="B690" s="6"/>
       <c r="C690" s="3"/>
@@ -34977,7 +35121,7 @@
       <c r="Y690" s="3"/>
       <c r="Z690" s="3"/>
     </row>
-    <row r="691" spans="1:26" ht="15">
+    <row r="691" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A691" s="3"/>
       <c r="B691" s="6"/>
       <c r="C691" s="3"/>
@@ -35005,7 +35149,7 @@
       <c r="Y691" s="3"/>
       <c r="Z691" s="3"/>
     </row>
-    <row r="692" spans="1:26" ht="15">
+    <row r="692" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A692" s="3"/>
       <c r="B692" s="6"/>
       <c r="C692" s="3"/>
@@ -35033,7 +35177,7 @@
       <c r="Y692" s="3"/>
       <c r="Z692" s="3"/>
     </row>
-    <row r="693" spans="1:26" ht="15">
+    <row r="693" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A693" s="3"/>
       <c r="B693" s="6"/>
       <c r="C693" s="3"/>
@@ -35061,7 +35205,7 @@
       <c r="Y693" s="3"/>
       <c r="Z693" s="3"/>
     </row>
-    <row r="694" spans="1:26" ht="15">
+    <row r="694" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A694" s="3"/>
       <c r="B694" s="6"/>
       <c r="C694" s="3"/>
@@ -35089,7 +35233,7 @@
       <c r="Y694" s="3"/>
       <c r="Z694" s="3"/>
     </row>
-    <row r="695" spans="1:26" ht="15">
+    <row r="695" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A695" s="3"/>
       <c r="B695" s="6"/>
       <c r="C695" s="3"/>
@@ -35117,7 +35261,7 @@
       <c r="Y695" s="3"/>
       <c r="Z695" s="3"/>
     </row>
-    <row r="696" spans="1:26" ht="15">
+    <row r="696" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A696" s="3"/>
       <c r="B696" s="6"/>
       <c r="C696" s="3"/>
@@ -35145,7 +35289,7 @@
       <c r="Y696" s="3"/>
       <c r="Z696" s="3"/>
     </row>
-    <row r="697" spans="1:26" ht="15">
+    <row r="697" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A697" s="3"/>
       <c r="B697" s="6"/>
       <c r="C697" s="3"/>
@@ -35173,7 +35317,7 @@
       <c r="Y697" s="3"/>
       <c r="Z697" s="3"/>
     </row>
-    <row r="698" spans="1:26" ht="15">
+    <row r="698" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A698" s="3"/>
       <c r="B698" s="6"/>
       <c r="C698" s="3"/>
@@ -35201,7 +35345,7 @@
       <c r="Y698" s="3"/>
       <c r="Z698" s="3"/>
     </row>
-    <row r="699" spans="1:26" ht="15">
+    <row r="699" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A699" s="3"/>
       <c r="B699" s="6"/>
       <c r="C699" s="3"/>
@@ -35229,7 +35373,7 @@
       <c r="Y699" s="3"/>
       <c r="Z699" s="3"/>
     </row>
-    <row r="700" spans="1:26" ht="15">
+    <row r="700" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A700" s="3"/>
       <c r="B700" s="6"/>
       <c r="C700" s="3"/>
@@ -35257,7 +35401,7 @@
       <c r="Y700" s="3"/>
       <c r="Z700" s="3"/>
     </row>
-    <row r="701" spans="1:26" ht="15">
+    <row r="701" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A701" s="3"/>
       <c r="B701" s="6"/>
       <c r="C701" s="3"/>
@@ -35285,7 +35429,7 @@
       <c r="Y701" s="3"/>
       <c r="Z701" s="3"/>
     </row>
-    <row r="702" spans="1:26" ht="15">
+    <row r="702" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A702" s="3"/>
       <c r="B702" s="6"/>
       <c r="C702" s="3"/>
@@ -35313,7 +35457,7 @@
       <c r="Y702" s="3"/>
       <c r="Z702" s="3"/>
     </row>
-    <row r="703" spans="1:26" ht="15">
+    <row r="703" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A703" s="3"/>
       <c r="B703" s="6"/>
       <c r="C703" s="3"/>
@@ -35341,7 +35485,7 @@
       <c r="Y703" s="3"/>
       <c r="Z703" s="3"/>
     </row>
-    <row r="704" spans="1:26" ht="15">
+    <row r="704" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A704" s="3"/>
       <c r="B704" s="6"/>
       <c r="C704" s="3"/>
@@ -35369,7 +35513,7 @@
       <c r="Y704" s="3"/>
       <c r="Z704" s="3"/>
     </row>
-    <row r="705" spans="1:26" ht="15">
+    <row r="705" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A705" s="3"/>
       <c r="B705" s="6"/>
       <c r="C705" s="3"/>
@@ -35397,7 +35541,7 @@
       <c r="Y705" s="3"/>
       <c r="Z705" s="3"/>
     </row>
-    <row r="706" spans="1:26" ht="15">
+    <row r="706" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A706" s="3"/>
       <c r="B706" s="6"/>
       <c r="C706" s="3"/>
@@ -35425,7 +35569,7 @@
       <c r="Y706" s="3"/>
       <c r="Z706" s="3"/>
     </row>
-    <row r="707" spans="1:26" ht="15">
+    <row r="707" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A707" s="3"/>
       <c r="B707" s="6"/>
       <c r="C707" s="3"/>
@@ -35453,7 +35597,7 @@
       <c r="Y707" s="3"/>
       <c r="Z707" s="3"/>
     </row>
-    <row r="708" spans="1:26" ht="15">
+    <row r="708" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A708" s="3"/>
       <c r="B708" s="6"/>
       <c r="C708" s="3"/>
@@ -35481,7 +35625,7 @@
       <c r="Y708" s="3"/>
       <c r="Z708" s="3"/>
     </row>
-    <row r="709" spans="1:26" ht="15">
+    <row r="709" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A709" s="3"/>
       <c r="B709" s="6"/>
       <c r="C709" s="3"/>
@@ -35509,7 +35653,7 @@
       <c r="Y709" s="3"/>
       <c r="Z709" s="3"/>
     </row>
-    <row r="710" spans="1:26" ht="15">
+    <row r="710" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A710" s="3"/>
       <c r="B710" s="6"/>
       <c r="C710" s="3"/>
@@ -35537,7 +35681,7 @@
       <c r="Y710" s="3"/>
       <c r="Z710" s="3"/>
     </row>
-    <row r="711" spans="1:26" ht="15">
+    <row r="711" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A711" s="3"/>
       <c r="B711" s="6"/>
       <c r="C711" s="3"/>
@@ -35565,7 +35709,7 @@
       <c r="Y711" s="3"/>
       <c r="Z711" s="3"/>
     </row>
-    <row r="712" spans="1:26" ht="15">
+    <row r="712" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A712" s="3"/>
       <c r="B712" s="6"/>
       <c r="C712" s="3"/>
@@ -35593,7 +35737,7 @@
       <c r="Y712" s="3"/>
       <c r="Z712" s="3"/>
     </row>
-    <row r="713" spans="1:26" ht="15">
+    <row r="713" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A713" s="3"/>
       <c r="B713" s="6"/>
       <c r="C713" s="3"/>
@@ -35621,7 +35765,7 @@
       <c r="Y713" s="3"/>
       <c r="Z713" s="3"/>
     </row>
-    <row r="714" spans="1:26" ht="15">
+    <row r="714" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A714" s="3"/>
       <c r="B714" s="6"/>
       <c r="C714" s="3"/>
@@ -35649,7 +35793,7 @@
       <c r="Y714" s="3"/>
       <c r="Z714" s="3"/>
     </row>
-    <row r="715" spans="1:26" ht="15">
+    <row r="715" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A715" s="3"/>
       <c r="B715" s="6"/>
       <c r="C715" s="3"/>
@@ -35677,7 +35821,7 @@
       <c r="Y715" s="3"/>
       <c r="Z715" s="3"/>
     </row>
-    <row r="716" spans="1:26" ht="15">
+    <row r="716" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A716" s="3"/>
       <c r="B716" s="6"/>
       <c r="C716" s="3"/>
@@ -35705,7 +35849,7 @@
       <c r="Y716" s="3"/>
       <c r="Z716" s="3"/>
     </row>
-    <row r="717" spans="1:26" ht="15">
+    <row r="717" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A717" s="3"/>
       <c r="B717" s="6"/>
       <c r="C717" s="3"/>
@@ -35733,7 +35877,7 @@
       <c r="Y717" s="3"/>
       <c r="Z717" s="3"/>
     </row>
-    <row r="718" spans="1:26" ht="15">
+    <row r="718" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A718" s="3"/>
       <c r="B718" s="6"/>
       <c r="C718" s="3"/>
@@ -35761,7 +35905,7 @@
       <c r="Y718" s="3"/>
       <c r="Z718" s="3"/>
     </row>
-    <row r="719" spans="1:26" ht="15">
+    <row r="719" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A719" s="3"/>
       <c r="B719" s="6"/>
       <c r="C719" s="3"/>
@@ -35789,7 +35933,7 @@
       <c r="Y719" s="3"/>
       <c r="Z719" s="3"/>
     </row>
-    <row r="720" spans="1:26" ht="15">
+    <row r="720" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A720" s="3"/>
       <c r="B720" s="6"/>
       <c r="C720" s="3"/>
@@ -35817,7 +35961,7 @@
       <c r="Y720" s="3"/>
       <c r="Z720" s="3"/>
     </row>
-    <row r="721" spans="1:26" ht="15">
+    <row r="721" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A721" s="3"/>
       <c r="B721" s="6"/>
       <c r="C721" s="3"/>
@@ -35845,7 +35989,7 @@
       <c r="Y721" s="3"/>
       <c r="Z721" s="3"/>
     </row>
-    <row r="722" spans="1:26" ht="15">
+    <row r="722" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A722" s="3"/>
       <c r="B722" s="6"/>
       <c r="C722" s="3"/>
@@ -35873,7 +36017,7 @@
       <c r="Y722" s="3"/>
       <c r="Z722" s="3"/>
     </row>
-    <row r="723" spans="1:26" ht="15">
+    <row r="723" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A723" s="3"/>
       <c r="B723" s="6"/>
       <c r="C723" s="3"/>
@@ -35901,7 +36045,7 @@
       <c r="Y723" s="3"/>
       <c r="Z723" s="3"/>
     </row>
-    <row r="724" spans="1:26" ht="15">
+    <row r="724" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A724" s="3"/>
       <c r="B724" s="6"/>
       <c r="C724" s="3"/>
@@ -35929,7 +36073,7 @@
       <c r="Y724" s="3"/>
       <c r="Z724" s="3"/>
     </row>
-    <row r="725" spans="1:26" ht="15">
+    <row r="725" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A725" s="3"/>
       <c r="B725" s="6"/>
       <c r="C725" s="3"/>
@@ -35957,7 +36101,7 @@
       <c r="Y725" s="3"/>
       <c r="Z725" s="3"/>
     </row>
-    <row r="726" spans="1:26" ht="15">
+    <row r="726" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A726" s="3"/>
       <c r="B726" s="6"/>
       <c r="C726" s="3"/>
@@ -35985,7 +36129,7 @@
       <c r="Y726" s="3"/>
       <c r="Z726" s="3"/>
     </row>
-    <row r="727" spans="1:26" ht="15">
+    <row r="727" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A727" s="3"/>
       <c r="B727" s="6"/>
       <c r="C727" s="3"/>
@@ -36013,7 +36157,7 @@
       <c r="Y727" s="3"/>
       <c r="Z727" s="3"/>
     </row>
-    <row r="728" spans="1:26" ht="15">
+    <row r="728" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A728" s="3"/>
       <c r="B728" s="6"/>
       <c r="C728" s="3"/>
@@ -36041,7 +36185,7 @@
       <c r="Y728" s="3"/>
       <c r="Z728" s="3"/>
     </row>
-    <row r="729" spans="1:26" ht="15">
+    <row r="729" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A729" s="3"/>
       <c r="B729" s="6"/>
       <c r="C729" s="3"/>
@@ -36069,7 +36213,7 @@
       <c r="Y729" s="3"/>
       <c r="Z729" s="3"/>
     </row>
-    <row r="730" spans="1:26" ht="15">
+    <row r="730" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A730" s="3"/>
       <c r="B730" s="6"/>
       <c r="C730" s="3"/>
@@ -36097,7 +36241,7 @@
       <c r="Y730" s="3"/>
       <c r="Z730" s="3"/>
     </row>
-    <row r="731" spans="1:26" ht="15">
+    <row r="731" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A731" s="3"/>
       <c r="B731" s="6"/>
       <c r="C731" s="3"/>
@@ -36125,7 +36269,7 @@
       <c r="Y731" s="3"/>
       <c r="Z731" s="3"/>
     </row>
-    <row r="732" spans="1:26" ht="15">
+    <row r="732" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A732" s="3"/>
       <c r="B732" s="6"/>
       <c r="C732" s="3"/>
@@ -36153,7 +36297,7 @@
       <c r="Y732" s="3"/>
       <c r="Z732" s="3"/>
     </row>
-    <row r="733" spans="1:26" ht="15">
+    <row r="733" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A733" s="3"/>
       <c r="B733" s="6"/>
       <c r="C733" s="3"/>
@@ -36181,7 +36325,7 @@
       <c r="Y733" s="3"/>
       <c r="Z733" s="3"/>
     </row>
-    <row r="734" spans="1:26" ht="15">
+    <row r="734" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A734" s="3"/>
       <c r="B734" s="6"/>
       <c r="C734" s="3"/>
@@ -36209,7 +36353,7 @@
       <c r="Y734" s="3"/>
       <c r="Z734" s="3"/>
     </row>
-    <row r="735" spans="1:26" ht="15">
+    <row r="735" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A735" s="3"/>
       <c r="B735" s="6"/>
       <c r="C735" s="3"/>
@@ -36237,7 +36381,7 @@
       <c r="Y735" s="3"/>
       <c r="Z735" s="3"/>
     </row>
-    <row r="736" spans="1:26" ht="15">
+    <row r="736" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A736" s="3"/>
       <c r="B736" s="6"/>
       <c r="C736" s="3"/>
@@ -36265,7 +36409,7 @@
       <c r="Y736" s="3"/>
       <c r="Z736" s="3"/>
     </row>
-    <row r="737" spans="1:26" ht="15">
+    <row r="737" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A737" s="3"/>
       <c r="B737" s="6"/>
       <c r="C737" s="3"/>
@@ -36293,7 +36437,7 @@
       <c r="Y737" s="3"/>
       <c r="Z737" s="3"/>
     </row>
-    <row r="738" spans="1:26" ht="15">
+    <row r="738" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A738" s="3"/>
       <c r="B738" s="6"/>
       <c r="C738" s="3"/>
@@ -36321,7 +36465,7 @@
       <c r="Y738" s="3"/>
       <c r="Z738" s="3"/>
     </row>
-    <row r="739" spans="1:26" ht="15">
+    <row r="739" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A739" s="3"/>
       <c r="B739" s="6"/>
       <c r="C739" s="3"/>
@@ -36349,7 +36493,7 @@
       <c r="Y739" s="3"/>
       <c r="Z739" s="3"/>
     </row>
-    <row r="740" spans="1:26" ht="15">
+    <row r="740" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A740" s="3"/>
       <c r="B740" s="6"/>
       <c r="C740" s="3"/>
@@ -36377,7 +36521,7 @@
       <c r="Y740" s="3"/>
       <c r="Z740" s="3"/>
     </row>
-    <row r="741" spans="1:26" ht="15">
+    <row r="741" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A741" s="3"/>
       <c r="B741" s="6"/>
       <c r="C741" s="3"/>
@@ -36405,7 +36549,7 @@
       <c r="Y741" s="3"/>
       <c r="Z741" s="3"/>
     </row>
-    <row r="742" spans="1:26" ht="15">
+    <row r="742" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A742" s="3"/>
       <c r="B742" s="6"/>
       <c r="C742" s="3"/>
@@ -36433,7 +36577,7 @@
       <c r="Y742" s="3"/>
       <c r="Z742" s="3"/>
     </row>
-    <row r="743" spans="1:26" ht="15">
+    <row r="743" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A743" s="3"/>
       <c r="B743" s="6"/>
       <c r="C743" s="3"/>
@@ -36461,7 +36605,7 @@
       <c r="Y743" s="3"/>
       <c r="Z743" s="3"/>
     </row>
-    <row r="744" spans="1:26" ht="15">
+    <row r="744" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A744" s="3"/>
       <c r="B744" s="6"/>
       <c r="C744" s="3"/>
@@ -36489,7 +36633,7 @@
       <c r="Y744" s="3"/>
       <c r="Z744" s="3"/>
     </row>
-    <row r="745" spans="1:26" ht="15">
+    <row r="745" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A745" s="3"/>
       <c r="B745" s="6"/>
       <c r="C745" s="3"/>
@@ -36517,7 +36661,7 @@
       <c r="Y745" s="3"/>
       <c r="Z745" s="3"/>
     </row>
-    <row r="746" spans="1:26" ht="15">
+    <row r="746" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A746" s="3"/>
       <c r="B746" s="6"/>
       <c r="C746" s="3"/>
@@ -36545,7 +36689,7 @@
       <c r="Y746" s="3"/>
       <c r="Z746" s="3"/>
     </row>
-    <row r="747" spans="1:26" ht="15">
+    <row r="747" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A747" s="3"/>
       <c r="B747" s="6"/>
       <c r="C747" s="3"/>
@@ -36573,7 +36717,7 @@
       <c r="Y747" s="3"/>
       <c r="Z747" s="3"/>
     </row>
-    <row r="748" spans="1:26" ht="15">
+    <row r="748" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A748" s="3"/>
       <c r="B748" s="6"/>
       <c r="C748" s="3"/>
@@ -36601,7 +36745,7 @@
       <c r="Y748" s="3"/>
       <c r="Z748" s="3"/>
     </row>
-    <row r="749" spans="1:26" ht="15">
+    <row r="749" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A749" s="3"/>
       <c r="B749" s="6"/>
       <c r="C749" s="3"/>
@@ -36629,7 +36773,7 @@
       <c r="Y749" s="3"/>
       <c r="Z749" s="3"/>
     </row>
-    <row r="750" spans="1:26" ht="15">
+    <row r="750" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A750" s="3"/>
       <c r="B750" s="6"/>
       <c r="C750" s="3"/>
@@ -36657,7 +36801,7 @@
       <c r="Y750" s="3"/>
       <c r="Z750" s="3"/>
     </row>
-    <row r="751" spans="1:26" ht="15">
+    <row r="751" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A751" s="3"/>
       <c r="B751" s="6"/>
       <c r="C751" s="3"/>
@@ -36685,7 +36829,7 @@
       <c r="Y751" s="3"/>
       <c r="Z751" s="3"/>
     </row>
-    <row r="752" spans="1:26" ht="15">
+    <row r="752" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A752" s="3"/>
       <c r="B752" s="6"/>
       <c r="C752" s="3"/>
@@ -36713,7 +36857,7 @@
       <c r="Y752" s="3"/>
       <c r="Z752" s="3"/>
     </row>
-    <row r="753" spans="1:26" ht="15">
+    <row r="753" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A753" s="3"/>
       <c r="B753" s="6"/>
       <c r="C753" s="3"/>
@@ -36741,7 +36885,7 @@
       <c r="Y753" s="3"/>
       <c r="Z753" s="3"/>
     </row>
-    <row r="754" spans="1:26" ht="15">
+    <row r="754" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A754" s="3"/>
       <c r="B754" s="6"/>
       <c r="C754" s="3"/>
@@ -36769,7 +36913,7 @@
       <c r="Y754" s="3"/>
       <c r="Z754" s="3"/>
     </row>
-    <row r="755" spans="1:26" ht="15">
+    <row r="755" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A755" s="3"/>
       <c r="B755" s="6"/>
       <c r="C755" s="3"/>
@@ -36797,7 +36941,7 @@
       <c r="Y755" s="3"/>
       <c r="Z755" s="3"/>
     </row>
-    <row r="756" spans="1:26" ht="15">
+    <row r="756" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A756" s="3"/>
       <c r="B756" s="6"/>
       <c r="C756" s="3"/>
@@ -36825,7 +36969,7 @@
       <c r="Y756" s="3"/>
       <c r="Z756" s="3"/>
     </row>
-    <row r="757" spans="1:26" ht="15">
+    <row r="757" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A757" s="3"/>
       <c r="B757" s="6"/>
       <c r="C757" s="3"/>
@@ -36853,7 +36997,7 @@
       <c r="Y757" s="3"/>
       <c r="Z757" s="3"/>
     </row>
-    <row r="758" spans="1:26" ht="15">
+    <row r="758" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A758" s="3"/>
       <c r="B758" s="6"/>
       <c r="C758" s="3"/>
@@ -36881,7 +37025,7 @@
       <c r="Y758" s="3"/>
       <c r="Z758" s="3"/>
     </row>
-    <row r="759" spans="1:26" ht="15">
+    <row r="759" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A759" s="3"/>
       <c r="B759" s="6"/>
       <c r="C759" s="3"/>
@@ -36909,7 +37053,7 @@
       <c r="Y759" s="3"/>
       <c r="Z759" s="3"/>
     </row>
-    <row r="760" spans="1:26" ht="15">
+    <row r="760" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A760" s="3"/>
       <c r="B760" s="6"/>
       <c r="C760" s="3"/>
@@ -36937,7 +37081,7 @@
       <c r="Y760" s="3"/>
       <c r="Z760" s="3"/>
     </row>
-    <row r="761" spans="1:26" ht="15">
+    <row r="761" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A761" s="3"/>
       <c r="B761" s="6"/>
       <c r="C761" s="3"/>
@@ -36965,7 +37109,7 @@
       <c r="Y761" s="3"/>
       <c r="Z761" s="3"/>
     </row>
-    <row r="762" spans="1:26" ht="15">
+    <row r="762" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A762" s="3"/>
       <c r="B762" s="6"/>
       <c r="C762" s="3"/>
@@ -36993,7 +37137,7 @@
       <c r="Y762" s="3"/>
       <c r="Z762" s="3"/>
     </row>
-    <row r="763" spans="1:26" ht="15">
+    <row r="763" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A763" s="3"/>
       <c r="B763" s="6"/>
       <c r="C763" s="3"/>
@@ -37021,7 +37165,7 @@
       <c r="Y763" s="3"/>
       <c r="Z763" s="3"/>
     </row>
-    <row r="764" spans="1:26" ht="15">
+    <row r="764" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A764" s="3"/>
       <c r="B764" s="6"/>
       <c r="C764" s="3"/>
@@ -37049,7 +37193,7 @@
       <c r="Y764" s="3"/>
       <c r="Z764" s="3"/>
     </row>
-    <row r="765" spans="1:26" ht="15">
+    <row r="765" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A765" s="3"/>
       <c r="B765" s="6"/>
       <c r="C765" s="3"/>
@@ -37077,7 +37221,7 @@
       <c r="Y765" s="3"/>
       <c r="Z765" s="3"/>
     </row>
-    <row r="766" spans="1:26" ht="15">
+    <row r="766" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A766" s="3"/>
       <c r="B766" s="6"/>
       <c r="C766" s="3"/>
@@ -37105,7 +37249,7 @@
       <c r="Y766" s="3"/>
       <c r="Z766" s="3"/>
     </row>
-    <row r="767" spans="1:26" ht="15">
+    <row r="767" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A767" s="3"/>
       <c r="B767" s="6"/>
       <c r="C767" s="3"/>
@@ -37133,7 +37277,7 @@
       <c r="Y767" s="3"/>
       <c r="Z767" s="3"/>
     </row>
-    <row r="768" spans="1:26" ht="15">
+    <row r="768" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A768" s="3"/>
       <c r="B768" s="6"/>
       <c r="C768" s="3"/>
@@ -37161,7 +37305,7 @@
       <c r="Y768" s="3"/>
       <c r="Z768" s="3"/>
     </row>
-    <row r="769" spans="1:26" ht="15">
+    <row r="769" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A769" s="3"/>
       <c r="B769" s="6"/>
       <c r="C769" s="3"/>
@@ -37189,7 +37333,7 @@
       <c r="Y769" s="3"/>
       <c r="Z769" s="3"/>
     </row>
-    <row r="770" spans="1:26" ht="15">
+    <row r="770" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A770" s="3"/>
       <c r="B770" s="6"/>
       <c r="C770" s="3"/>
@@ -37217,7 +37361,7 @@
       <c r="Y770" s="3"/>
       <c r="Z770" s="3"/>
     </row>
-    <row r="771" spans="1:26" ht="15">
+    <row r="771" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A771" s="3"/>
       <c r="B771" s="6"/>
       <c r="C771" s="3"/>
@@ -37245,7 +37389,7 @@
       <c r="Y771" s="3"/>
       <c r="Z771" s="3"/>
     </row>
-    <row r="772" spans="1:26" ht="15">
+    <row r="772" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A772" s="3"/>
       <c r="B772" s="6"/>
       <c r="C772" s="3"/>
@@ -37273,7 +37417,7 @@
       <c r="Y772" s="3"/>
       <c r="Z772" s="3"/>
     </row>
-    <row r="773" spans="1:26" ht="15">
+    <row r="773" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A773" s="3"/>
       <c r="B773" s="6"/>
       <c r="C773" s="3"/>
@@ -37301,7 +37445,7 @@
       <c r="Y773" s="3"/>
       <c r="Z773" s="3"/>
     </row>
-    <row r="774" spans="1:26" ht="15">
+    <row r="774" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A774" s="3"/>
       <c r="B774" s="6"/>
       <c r="C774" s="3"/>
@@ -37329,7 +37473,7 @@
       <c r="Y774" s="3"/>
       <c r="Z774" s="3"/>
     </row>
-    <row r="775" spans="1:26" ht="15">
+    <row r="775" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A775" s="3"/>
       <c r="B775" s="6"/>
       <c r="C775" s="3"/>
@@ -37357,7 +37501,7 @@
       <c r="Y775" s="3"/>
       <c r="Z775" s="3"/>
     </row>
-    <row r="776" spans="1:26" ht="15">
+    <row r="776" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A776" s="3"/>
       <c r="B776" s="6"/>
       <c r="C776" s="3"/>
@@ -37385,7 +37529,7 @@
       <c r="Y776" s="3"/>
       <c r="Z776" s="3"/>
     </row>
-    <row r="777" spans="1:26" ht="15">
+    <row r="777" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A777" s="3"/>
       <c r="B777" s="6"/>
       <c r="C777" s="3"/>
@@ -37413,7 +37557,7 @@
       <c r="Y777" s="3"/>
       <c r="Z777" s="3"/>
     </row>
-    <row r="778" spans="1:26" ht="15">
+    <row r="778" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A778" s="3"/>
       <c r="B778" s="6"/>
       <c r="C778" s="3"/>
@@ -37441,7 +37585,7 @@
       <c r="Y778" s="3"/>
       <c r="Z778" s="3"/>
     </row>
-    <row r="779" spans="1:26" ht="15">
+    <row r="779" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A779" s="3"/>
       <c r="B779" s="6"/>
       <c r="C779" s="3"/>
@@ -37469,7 +37613,7 @@
       <c r="Y779" s="3"/>
       <c r="Z779" s="3"/>
     </row>
-    <row r="780" spans="1:26" ht="15">
+    <row r="780" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A780" s="3"/>
       <c r="B780" s="6"/>
       <c r="C780" s="3"/>
@@ -37497,7 +37641,7 @@
       <c r="Y780" s="3"/>
       <c r="Z780" s="3"/>
     </row>
-    <row r="781" spans="1:26" ht="15">
+    <row r="781" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A781" s="3"/>
       <c r="B781" s="6"/>
       <c r="C781" s="3"/>
@@ -37525,7 +37669,7 @@
       <c r="Y781" s="3"/>
       <c r="Z781" s="3"/>
     </row>
-    <row r="782" spans="1:26" ht="15">
+    <row r="782" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="6"/>
       <c r="C782" s="3"/>
@@ -37553,7 +37697,7 @@
       <c r="Y782" s="3"/>
       <c r="Z782" s="3"/>
     </row>
-    <row r="783" spans="1:26" ht="15">
+    <row r="783" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A783" s="3"/>
       <c r="B783" s="6"/>
       <c r="C783" s="3"/>
@@ -37581,7 +37725,7 @@
       <c r="Y783" s="3"/>
       <c r="Z783" s="3"/>
     </row>
-    <row r="784" spans="1:26" ht="15">
+    <row r="784" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A784" s="3"/>
       <c r="B784" s="6"/>
       <c r="C784" s="3"/>
@@ -37609,7 +37753,7 @@
       <c r="Y784" s="3"/>
       <c r="Z784" s="3"/>
     </row>
-    <row r="785" spans="1:26" ht="15">
+    <row r="785" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A785" s="3"/>
       <c r="B785" s="6"/>
       <c r="C785" s="3"/>
@@ -37637,7 +37781,7 @@
       <c r="Y785" s="3"/>
       <c r="Z785" s="3"/>
     </row>
-    <row r="786" spans="1:26" ht="15">
+    <row r="786" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A786" s="3"/>
       <c r="B786" s="6"/>
       <c r="C786" s="3"/>
@@ -37665,7 +37809,7 @@
       <c r="Y786" s="3"/>
       <c r="Z786" s="3"/>
     </row>
-    <row r="787" spans="1:26" ht="15">
+    <row r="787" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A787" s="3"/>
       <c r="B787" s="6"/>
       <c r="C787" s="3"/>
@@ -37693,7 +37837,7 @@
       <c r="Y787" s="3"/>
       <c r="Z787" s="3"/>
     </row>
-    <row r="788" spans="1:26" ht="15">
+    <row r="788" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A788" s="3"/>
       <c r="B788" s="6"/>
       <c r="C788" s="3"/>
@@ -37721,7 +37865,7 @@
       <c r="Y788" s="3"/>
       <c r="Z788" s="3"/>
     </row>
-    <row r="789" spans="1:26" ht="15">
+    <row r="789" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A789" s="3"/>
       <c r="B789" s="6"/>
       <c r="C789" s="3"/>
@@ -37749,7 +37893,7 @@
       <c r="Y789" s="3"/>
       <c r="Z789" s="3"/>
     </row>
-    <row r="790" spans="1:26" ht="15">
+    <row r="790" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A790" s="3"/>
       <c r="B790" s="6"/>
       <c r="C790" s="3"/>
@@ -37777,7 +37921,7 @@
       <c r="Y790" s="3"/>
       <c r="Z790" s="3"/>
     </row>
-    <row r="791" spans="1:26" ht="15">
+    <row r="791" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A791" s="3"/>
       <c r="B791" s="6"/>
       <c r="C791" s="3"/>
@@ -37805,7 +37949,7 @@
       <c r="Y791" s="3"/>
       <c r="Z791" s="3"/>
     </row>
-    <row r="792" spans="1:26" ht="15">
+    <row r="792" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A792" s="3"/>
       <c r="B792" s="6"/>
       <c r="C792" s="3"/>
@@ -37833,7 +37977,7 @@
       <c r="Y792" s="3"/>
       <c r="Z792" s="3"/>
     </row>
-    <row r="793" spans="1:26" ht="15">
+    <row r="793" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A793" s="3"/>
       <c r="B793" s="6"/>
       <c r="C793" s="3"/>
@@ -37861,7 +38005,7 @@
       <c r="Y793" s="3"/>
       <c r="Z793" s="3"/>
     </row>
-    <row r="794" spans="1:26" ht="15">
+    <row r="794" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A794" s="3"/>
       <c r="B794" s="6"/>
       <c r="C794" s="3"/>
@@ -37889,7 +38033,7 @@
       <c r="Y794" s="3"/>
       <c r="Z794" s="3"/>
     </row>
-    <row r="795" spans="1:26" ht="15">
+    <row r="795" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A795" s="3"/>
       <c r="B795" s="6"/>
       <c r="C795" s="3"/>
@@ -37917,7 +38061,7 @@
       <c r="Y795" s="3"/>
       <c r="Z795" s="3"/>
     </row>
-    <row r="796" spans="1:26" ht="15">
+    <row r="796" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A796" s="3"/>
       <c r="B796" s="6"/>
       <c r="C796" s="3"/>
@@ -37945,7 +38089,7 @@
       <c r="Y796" s="3"/>
       <c r="Z796" s="3"/>
     </row>
-    <row r="797" spans="1:26" ht="15">
+    <row r="797" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A797" s="3"/>
       <c r="B797" s="6"/>
       <c r="C797" s="3"/>
@@ -37973,7 +38117,7 @@
       <c r="Y797" s="3"/>
       <c r="Z797" s="3"/>
     </row>
-    <row r="798" spans="1:26" ht="15">
+    <row r="798" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A798" s="3"/>
       <c r="B798" s="6"/>
       <c r="C798" s="3"/>
@@ -38001,7 +38145,7 @@
       <c r="Y798" s="3"/>
       <c r="Z798" s="3"/>
     </row>
-    <row r="799" spans="1:26" ht="15">
+    <row r="799" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A799" s="3"/>
       <c r="B799" s="6"/>
       <c r="C799" s="3"/>
@@ -38029,7 +38173,7 @@
       <c r="Y799" s="3"/>
       <c r="Z799" s="3"/>
     </row>
-    <row r="800" spans="1:26" ht="15">
+    <row r="800" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A800" s="3"/>
       <c r="B800" s="6"/>
       <c r="C800" s="3"/>
@@ -38057,7 +38201,7 @@
       <c r="Y800" s="3"/>
       <c r="Z800" s="3"/>
     </row>
-    <row r="801" spans="1:26" ht="15">
+    <row r="801" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A801" s="3"/>
       <c r="B801" s="6"/>
       <c r="C801" s="3"/>
@@ -38085,7 +38229,7 @@
       <c r="Y801" s="3"/>
       <c r="Z801" s="3"/>
     </row>
-    <row r="802" spans="1:26" ht="15">
+    <row r="802" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A802" s="3"/>
       <c r="B802" s="6"/>
       <c r="C802" s="3"/>
@@ -38113,7 +38257,7 @@
       <c r="Y802" s="3"/>
       <c r="Z802" s="3"/>
     </row>
-    <row r="803" spans="1:26" ht="15">
+    <row r="803" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A803" s="3"/>
       <c r="B803" s="6"/>
       <c r="C803" s="3"/>
@@ -38141,7 +38285,7 @@
       <c r="Y803" s="3"/>
       <c r="Z803" s="3"/>
     </row>
-    <row r="804" spans="1:26" ht="15">
+    <row r="804" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A804" s="3"/>
       <c r="B804" s="6"/>
       <c r="C804" s="3"/>
@@ -38169,7 +38313,7 @@
       <c r="Y804" s="3"/>
       <c r="Z804" s="3"/>
     </row>
-    <row r="805" spans="1:26" ht="15">
+    <row r="805" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A805" s="3"/>
       <c r="B805" s="6"/>
       <c r="C805" s="3"/>
@@ -38197,7 +38341,7 @@
       <c r="Y805" s="3"/>
       <c r="Z805" s="3"/>
     </row>
-    <row r="806" spans="1:26" ht="15">
+    <row r="806" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A806" s="3"/>
       <c r="B806" s="6"/>
       <c r="C806" s="3"/>
@@ -38225,7 +38369,7 @@
       <c r="Y806" s="3"/>
       <c r="Z806" s="3"/>
     </row>
-    <row r="807" spans="1:26" ht="15">
+    <row r="807" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A807" s="3"/>
       <c r="B807" s="6"/>
       <c r="C807" s="3"/>
@@ -38253,7 +38397,7 @@
       <c r="Y807" s="3"/>
       <c r="Z807" s="3"/>
     </row>
-    <row r="808" spans="1:26" ht="15">
+    <row r="808" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A808" s="3"/>
       <c r="B808" s="6"/>
       <c r="C808" s="3"/>
@@ -38281,7 +38425,7 @@
       <c r="Y808" s="3"/>
       <c r="Z808" s="3"/>
     </row>
-    <row r="809" spans="1:26" ht="15">
+    <row r="809" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A809" s="3"/>
       <c r="B809" s="6"/>
       <c r="C809" s="3"/>
@@ -38309,7 +38453,7 @@
       <c r="Y809" s="3"/>
       <c r="Z809" s="3"/>
     </row>
-    <row r="810" spans="1:26" ht="15">
+    <row r="810" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A810" s="3"/>
       <c r="B810" s="6"/>
       <c r="C810" s="3"/>
@@ -38337,7 +38481,7 @@
       <c r="Y810" s="3"/>
       <c r="Z810" s="3"/>
     </row>
-    <row r="811" spans="1:26" ht="15">
+    <row r="811" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A811" s="3"/>
       <c r="B811" s="6"/>
       <c r="C811" s="3"/>
@@ -38365,7 +38509,7 @@
       <c r="Y811" s="3"/>
       <c r="Z811" s="3"/>
     </row>
-    <row r="812" spans="1:26" ht="15">
+    <row r="812" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A812" s="3"/>
       <c r="B812" s="6"/>
       <c r="C812" s="3"/>
@@ -38393,7 +38537,7 @@
       <c r="Y812" s="3"/>
       <c r="Z812" s="3"/>
     </row>
-    <row r="813" spans="1:26" ht="15">
+    <row r="813" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A813" s="3"/>
       <c r="B813" s="6"/>
       <c r="C813" s="3"/>
